--- a/patent.xlsx
+++ b/patent.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktadh\Downloads\Research\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UPES\Research Paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A235122-CE2C-423E-B819-E3A34BB72950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A47F3A-C1B8-48F6-BCE5-D79A06F3B864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F00DE57-17D5-44C0-9358-E5EFB0815E0D}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5785" uniqueCount="2881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6879" uniqueCount="3395">
   <si>
     <t>Patent ID</t>
   </si>
@@ -8990,9 +8990,6 @@
     <t>Jan 02, 2025</t>
   </si>
   <si>
-    <t>PATENTED</t>
-  </si>
-  <si>
     <t>An ophthalmological apparatus (1) for treating eye tissue (3) with laser pulses (P) comprises a laser source (100, an optical projection system (20) for projecting the laser pulses (P) onto the eye tissue (30), and a coupling part (12) for attaching mechanically to the optical projection system (20) an ophthalmological patient interface device (27) which is in contact with the eye (3) during treatment. The ophthalmological apparatus (1) further comprises a detector (13) for determining a device identifier (22) associated with the ophthalmological patient interface device (27), and a control module (14) for controlling the ophthalmological apparatus (1) using the device identifier (22). The detector makes it possible to use and detect different types of ophthalmological patient interface devices (27) and to adapt automatically the treatment of the eye tissue (30), dePending on the ophthalmological patient interface device (27) that is presently attached to the ophthalmological apparatus (1).</t>
   </si>
   <si>
@@ -9065,9 +9062,6 @@
     <t>Partial European Search Report issued Feb. 11, 2014 for corresponding European Patent Application No. 12 00 5283.;;Partial European Search Report issued Jan. 31, 2014 for corresponding European Patent Application No. 12005288.1.;;Extended European Search report issued Jun. 11, 2014 in corresponding European Patent Application No. 12005283.2.</t>
   </si>
   <si>
-    <t>Barot et al. Prodrug Strategies. Ocular Drug Delivery Med. Chem. 8(4):753-768 (2012).;;Co-pending U.S. Appl. No. 18/369,737, inventor Horn; Gerald, filed on Sep. 18, 2023.;;Krise et al. A novel prodrug approach for tertiary amines. 2. Physicochemical and in vitro enzymatic evaluation of selected N-phosphonooxymethyl prodrugs. J Pham Sci 88(9):922-927 (1999).;;Mäntylä et al. Design, synthesis and in vitro evaluation of novel water-soluble prodrugs of buparvaquone. Eur J Pharm Sci 23(2):151-158 (2004).;;Pramanik et al. A new route to cevimeline. Tetrahedron Letters 54(24):3043-3045 (2013).;;PubChem CID-22416839, Dec. 5, 2007.;;U.S. Appl. No. 17/988,366 Office Action dated Jan. 8, 2024.;;U.S. Appl. No. 18/239,072 Office Action dated Nov. 21, 2023.;;PCT/US2024/024819 International Search Report and Written Opinion dated Jul. 15, 2024.;;Akorn Incorporated MSDS: Tropicacyl (R); Rev. 11-11 (date unknown).;;Berge et al. Pharmaceutical Salts. Journal of Pharmaceutical Sciences 66(1):1-19 (Jan. 1977).;;Bijsluiter: Glaucocare. Available at https://consumed.nl/bijsluiters/glaucocare. Machine Translation Provided.;;CAS printout for Mashkovskii, The Relation Between the Chemical Structure and Pharmacological Activity of Some Esters of 3-Hydroxyquinuclidine (Quinuclidine-3-ol), Proc. Intern. Pharmacol., 7:359-366 (1961).;;Chung et al., The effect of dioptric blur on reading performance. Vision Res47(12):1584-94 (2007).;;Cowan et al., Clinical evaluation of a new mydriatic-mydrilate. Br J Ophthalmol 46(12):730-6 (1962).;;Davidson., General medicine and visual side effects. Br Med J 1(6166):821 (1979).;;Drance et al., Dose response of human intraocular pressure to aceclidine. Arch Ophthalmol 88(4):394-6 (1972).;;Edwards., Behaviour of the fellow eye in acute angle-closure glaucoma. Br J Ophthalmol 66(9):576-9 (1982).;;Edwards et al., Effect of brimonidine tartrate 0.15% on night-vision difficulty and contrast testing after refractive surgery, J Cataract Refract Surg. 34(9):1538-41 (2008).;;Ehlert et al. The interaction of the enantiomers of aceclidine with subtypes of the muscarinic receptor. J Pharmacol Exp Ther 279(3):1335-1344 (1996).;;Fechner et al., Accomodative effects of aceclidine in the treatment of glaucoma. Amer J Ophth. 79 (1):104-106 (1975).;;Francois et al. Ultrasonographic study of the effect of different miotics on the eye components. Ophthalmologica 175(6):328-338 (1977).;;Fricke et al. Global Prevalence of Presbyopia and Vision Impairment from Uncorrected Presbyopia: Systematic Review, Meta-analysis, and Modelling. Ophthalmology 125(10):1492-1499 (2018).;;Gardiner., ABC of Ophthalmology: accidents and first aid. Br Med J 2(6148):1347-50 (1978).;;Gardiner., ABC of Ophthalmology: Methods of examination. Br Med J 2(6152):1622-6 (1978).;;Glaucadrine, poudre et solvant pour collyre en solution, boite de 1 acon de lyophilisat + acon le solvant de 10 ml GI. Available at Http://www.doctissimo.fr/medicament-GLAUCADRINE.htm Machine Translation Provided.;;Glaunorm toma all'Indice farmaci. Available at http://www.anibaldi.eu/farmaci/schedetecniche/GLAUNORM.html. (last updated Dec. 15, 2012) Machine Translation Provided.;;Grünberger et al., The pupillary response test as a method to differentiate various types of dementia. Neuropsychiatr 23(1):52-57 (2009).;;Hoyng et al., The combination of guanethidine 3% and adrenaline 0.5% in 1 eyedrop (GA) in glaucoma treatment. Br J Ophthalmol 63(1):56-62 (1979).;;Ishikawa et al. Selectivity of muscarinic agonists including (+/−)-aceclidine and antimuscarinics on the human intraocular muscles. J Ocul Pharmacol Ther 14(4):363-373 (1998).;;Josefa Valcarcel, Glaucostat(R) 2% colirio. Machine Translation Provided.;;Kaufman et al. Presbyopia and Glaucoma: Two Diseases, One Pathophysiology? The 2017 Friedenwald Lecture. Invest Ophthalmol Vis Sci 60(5):1801-1812 (2019).;;Kibbe. Handbook of Pharmaceutical Excipients. 3rd Edition, American Pharmaceutical Association and Pharmaceutical Press (pp. 416-419) (2000).;;Latanoprost Label (2006).;;Lubrizol Pharmaceutical Bulletin 21 (Lubrizol Advanced Materials, Inc.) May 31, 2011.;;Mayama et al. Myopia and advanced-stage open-angle glaucoma. Ophthalmology 109(11):2072-2077 (2002).;;Mayo Clinic: Tropicamide (Opthalmic Route), 2015, http://www.mayoclinic.org/drugs-supplements/tropicamide-ophthalmic-route/description/drg-20066481.;;Mohan et al., Optimal dosage of cyclopentolate 1% for cycloplegic refraction in hypermetropes with brown irides. Indian J Ophthalmol 59(6):514-6 (2011).;;Muller and R.P. Dessing (Eds.) 4th Edition, European Drug Index, European Society of Clinical Pharmacy, Jeutscher Apotheker Verlag Suttgart (p. 550) (1997).;;Nayak et al., A comparison of cycloplegic and manifest refractions on the NR-1000F (an objective Auto Refractometer). Br J Ophthalmol 71(1):73-5 (1987).;;Park., The comparison of mydriatic effect between two drugs of different mechanism. Korean J Ophthalmol 23(1):40-2 (2009).;;PCT/US2014/052256 International Search Report and Written Opinion dated Dec. 18, 2014.;;PCT/US2016/036687 International Search Report and Written Opinion dated Sep. 9, 2016.;;PCT/US2016/036692 International Search Report and Written Opinion dated Sep. 22, 2016.;;PCT/US2016/036694 International Search Report and Written Opinion dated Oct. 26, 2016.;;PCT/US2017/021244 International Search Report and Written Opinion dated May 22, 2017.;;PCT/US2019/055116 International Search Report and Written Opinion dated Dec. 19, 2019.;;PCT/US2019/063923 International Invitation to Pay Additional Fees dated Feb. 3, 2020.;;PCT/US2019/063923 International Search Report and Written Opinion dated Apr. 23, 2020.;;PCT/US2021/029536 International Search Report and Written Opinion dated Aug. 9, 2021.;;PCT/US2022/026435 International Invitation to Pay Additional Fees dated Jul. 5, 2022.;;PCT/US2022/026435 International Search Report and Written Opinion dated Sep. 28, 2022.;;PCT/US2022/050028 International Search Report and Written Opinion dated Mar. 2, 2023.;;Primožič et al. Influence of the acyl moiety on the hydrolysis of quinuclidinium esters catalyzed by butyrylcholinesterase. Croatica Chemica Acta 84(2):245-249 (2011).;;Prospectus/Technical Sheet for Glaucostat Josefa Valcarecel Glaucostat® 2% colirio (2000).;;PubChem 233021624 deposited on Feb. 12, 2015 (Feb. 12, 2015).;;PubChem 427198483 deposited Aug. 13, 2020 (Aug. 13, 2020).;;PubChem-CID-22416839, Create Date: Dec. 5, 2007.;;Romano., Double-blind cross-over comparison of aceclidine and pilocarpine in open-angle glaucoma. Br J Ophthalmol 54(8):510-21 (1970).;;Smith et al., Subsensitivity to cholinoceptor stimulation of the human iris sphincter in situ following acute and chronic administration of cholinomimetic miotic drugs. Br J Pharmacol 69(3):513-8 (1980).;;Stella. Prodrugs: Some Thoughts and Current Issues. J Pharm Sci 99(12):4755-4765 (2010).;;Tataru et al., Antiglaucoma pharmacotherapy. J Med Life 5(3):247-51 (2012).;;Trinavarat et al., Effective pupil dilatation with a mixture of 0.75% tropicamide and 2.5% phenylephrine: A randomized controlled trial. Indian J Ophthalmol 57(5):351-4 (2009).;;U.S. Appl. No. 14/223,639 Office Action dated Jan. 5, 2015.;;U.S. Appl. No. 14/223,639 Office Action dated Sep. 30, 2014.;;U.S. Appl. No. 14/742,903 Office Action dated Dec. 2, 2015.;;U.S. Appl. No. 14/742,903 Office Action dated Jul. 17, 2015.;;U.S. Appl. No. 14/742,921 Office Action dated Jul. 15, 2015.;;U.S. Appl. No. 14/860,770 Office Action dated Dec. 13, 2016.;;U.S. Appl. No. 14/860,777 Office Action dated Mar. 9, 2017.;;U.S. Appl. No. 15/073,089 Office Action dated May 8, 2017.;;U.S. Appl. No. 15/073,089 Office Action dated Nov. 30, 2016.;;U.S. Appl. No. 15/073,139 Office Action dated Dec. 1, 2016.;;U.S. Appl. No. 15/235,431 Office Action dated Mar. 9, 2018.;;U.S. Appl. No. 15/864,703 Office Action dated Apr. 8, 2019.;;U.S. Appl. No. 15/864,703 Office Action dated Feb. 11, 2019.;;U.S. Appl. No. 15/864,703 Office Action dated Mar. 26, 2018.;;U.S. Appl. No. 15/956,931 Office Action dated Oct. 2, 2018.;;U.S. Appl. No. 15/956,936 Office Action dated Feb. 11, 2019.;;U.S. Appl. No. 15/956,936 Office Action dated Sep. 28, 2018.;;U.S. Appl. No. 16/106,730 Office Action dated Jun. 11, 2021.;;U.S. Appl. No. 16/106,730 Office Action dated Jun. 2, 2020.;;U.S. Appl. No. 16/106,730 Office Action dated Oct. 19, 2020.;;U.S. Appl. No. 16/156,276 Office Action dated Jun. 26, 2020.;;U.S. Appl. No. 16/156,276 Office Action dated Oct. 22, 2020.;;U.S. Appl. No. 16/700,088 Office Action dated May 28, 2021.;;U.S. Appl. No. 16/700,088 Office Action dated Nov. 2, 2021.;;U.S. Appl. No. 16/747,070 Office Action dated Jun. 25, 2021.;;U.S. Appl. No. 16/747,070 Office Action dated Oct. 30, 2020.;;U.S. Appl. No. 16/796,364 Office Action dated Apr. 30, 2021.;;U.S. Appl. No. 16/796,364 Office Action dated Dec. 30, 2020.;;U.S. Appl. No. 16/796,364 Office Action dated Jun. 11, 2021.;;U.S. Appl. No. 16/881,570 Office Action dated Oct. 7, 2020.;;U.S. Appl. No. 17/069,155 Office Action dated Aug. 19, 2021.;;U.S. Appl. No. 17/242,398 Office Action dated Apr. 27, 2023.;;U.S. Appl. No. 17/242,398 Office Action dated Oct. 14, 2022.;;U.S. Appl. No. 17/502,066 Office Action dated Jun. 22, 2023.;;U.S. Appl. No. 17/502,066 Office Action dated Mar. 31, 2022.;;U.S. Appl. No. 17/502,066 Office Action dated Nov. 14, 2022.;;U.S. Appl. No. 17/552,622 Office Action dated Feb. 9, 2023.;;U.S. Appl. No. 17/552,654 Office Action dated Apr. 20, 2022.;;U.S. Appl. No. 17/552,654 Office Action dated Dec. 2, 2022.;;U.S. Appl. No. 17/988,366 Office Action dated Jul. 19, 2023.;;Varma et al. Concentration of Latanoprost Ophthalmic Solution after 4 to 6 Weeks' Use in an Eye Clinic Setting. Invest Ophthalmol Vis Sci. 47(1):222-225 (2006).;;Ward et al., 1,2,5-Thiadiazole analogues of aceclidine as potent ml muscarinic agonists. J Med Chem 41(3):379-392 (1988).;;Wood et al., Pupil dilatation does affect some aspects of daytime driving performance. Br J Ophthalmol (11):1387-90 (2003).;;Zhang et al. Reactive impurities in large and small molecule pharmaceutical excipients—A review. TrAC Trends in Analytical Chemistry 101:34-42 (2018).;;Aceclidine (Hydrochloride) Item No. 1790. Product Information. Cayman Chemical Company (1 pg) (Dec. 2, 2022).;;Charman, W. Neil. Pinholes and presbyopia: solution or sideshow? Ophthalmic Physiol Opt 39(1):1-10 (2019).;;Co-pending U.S. Appl. No. 18/763,722, inventors Horn; Gerald et al., filed on Jul. 3, 2024.;;Co-pending U.S. Appl. No. 18/765,066, inventors Horn; Gerald et al., filed on Jul. 5, 2024.;;Co-pending U.S. Appl. No. 18/765,156, inventors Horn; Gerald et al., filed on Jul. 5, 2024.;;Co-pending U.S. Appl. No. 18/766,429, inventors Horn; Gerald et al., filed on Jul. 8, 2024.;;Drug information Q&amp;A “Q29. What is the expiry date of drugs and how to store them properly?”, Japan Pharmaceutical Manufacturers Association [online], Mar. 2014, [retrieved on Mar. 25, 2024], Retrieved from the Internet: URL: https://www.jpma.or.jp/about_medicine/guide/med_qa/q29.html (English translation provided).;;Jiao, Jim. Polyoxyethylated nonionic surfactants and their applications in topical ocular drug delivery. Advanced Drug Delivery Reviewed 60:1663-1673 (2008).;;Randazzo et al., Pharmacological management of night vision disturbances after refractive surgery Results of a randomized clinical trial. J Cataract Refract Surg 31(9):1764-1772 (2005).;;Santvliet, et al. Determinants of Eye Drop Size. Survey of Ophthamology 49(2):197-213 (2004).;;U.S. Appl. No. 17/502,066 Office Action dated Mar. 27, 2024.;;U.S. Appl. No. 17/730,376 Office Action dated Jul. 17, 2024.;;U.S. Appl. No. 17/988,366 Office Action dated Apr. 29, 2024.;;U.S. Appl. No. 18/239,045 Office Action dated Jan. 26, 2024.;;U.S. Appl. No. 18/239,072 Office Action dated Mar. 27, 2024.;;U.S. Appl. No. 18/241,733 Office Action dated Jan. 30, 2024.;;U.S. Appl. No. 18/369,737 Office Action dated Jun. 6, 2024.;;U.S. Appl. No. 18/465,918 Office Action dated Feb. 1, 2024.;;Xu, Renfeng et al. Effect of Target Luminance on Optimum Pupil Diameter for Presbyopic Eyes. Optom Vis Sci 93(11):1409-1419 (2016).</t>
-  </si>
-  <si>
     <t>International Patent Application No. PCT/EP2009/053453, English Translation of International Preliminary Report on Patentability Chapter II (IPEA/409), dated Jan. 13, 2011, 5 pages (corresponds to U.S. Appl. No. 12/935,861).;;Von Deffer H. et al., "Infrared Diagnosis in Ophthalmology," vol. 96, No. 20, May 25, 1978, pp. 1053-1057, Germany.</t>
   </si>
   <si>
@@ -9117,6 +9111,1554 @@
   </si>
   <si>
     <t>Joerg, L. Loehrer, F. Machine Translation of DE10029153. Obtained from the European Patent Office March 22, 2015.</t>
+  </si>
+  <si>
+    <t>UA U200609012 U</t>
+  </si>
+  <si>
+    <t>UA U201001409 U</t>
+  </si>
+  <si>
+    <t>RU 95108306 A</t>
+  </si>
+  <si>
+    <t>UA U200800814 U</t>
+  </si>
+  <si>
+    <t>UA U200712770 U</t>
+  </si>
+  <si>
+    <t>US 2004/0030259 W</t>
+  </si>
+  <si>
+    <t>US 13103208 A</t>
+  </si>
+  <si>
+    <t>UA 94042103 A</t>
+  </si>
+  <si>
+    <t>UA A201305416 A</t>
+  </si>
+  <si>
+    <t>UA 200153113 A</t>
+  </si>
+  <si>
+    <t>RU 96108687 A</t>
+  </si>
+  <si>
+    <t>US 201314401496 A</t>
+  </si>
+  <si>
+    <t>US 2013/0041466 W</t>
+  </si>
+  <si>
+    <t>RU 2003132604 A</t>
+  </si>
+  <si>
+    <t>UA A200703509 A</t>
+  </si>
+  <si>
+    <t>US 68639407 A</t>
+  </si>
+  <si>
+    <t>UA 200074557 A</t>
+  </si>
+  <si>
+    <t>US 201113169836 A</t>
+  </si>
+  <si>
+    <t>MD S20230017 A</t>
+  </si>
+  <si>
+    <t>RU 2002132514 A</t>
+  </si>
+  <si>
+    <t>US 20107808 A</t>
+  </si>
+  <si>
+    <t>US 54779704 A</t>
+  </si>
+  <si>
+    <t>US 8459302 A</t>
+  </si>
+  <si>
+    <t>RU 2004120056 A</t>
+  </si>
+  <si>
+    <t>RU 2010124504 A</t>
+  </si>
+  <si>
+    <t>IB 2020056724 W</t>
+  </si>
+  <si>
+    <t>RU 2019136749 A</t>
+  </si>
+  <si>
+    <t>IB 2019060017 W</t>
+  </si>
+  <si>
+    <t>CN 201980090849 A</t>
+  </si>
+  <si>
+    <t>RU 2017118939 A</t>
+  </si>
+  <si>
+    <t>US 2015/0049197 W</t>
+  </si>
+  <si>
+    <t>RU 2017124069 A</t>
+  </si>
+  <si>
+    <t>US 27514808 A</t>
+  </si>
+  <si>
+    <t>RU 2018143006 A</t>
+  </si>
+  <si>
+    <t>RU 2016151953 A</t>
+  </si>
+  <si>
+    <t>US 2010/0050054 W</t>
+  </si>
+  <si>
+    <t>US 38312309 A</t>
+  </si>
+  <si>
+    <t>US 202117146301 A</t>
+  </si>
+  <si>
+    <t>RU 2020143623 A</t>
+  </si>
+  <si>
+    <t>US 23962799 D</t>
+  </si>
+  <si>
+    <t>IN 2022050828 W</t>
+  </si>
+  <si>
+    <t>US 37685406 A</t>
+  </si>
+  <si>
+    <t>RU 2018137608 A</t>
+  </si>
+  <si>
+    <t>US 75498104 A</t>
+  </si>
+  <si>
+    <t>US 32797306 A</t>
+  </si>
+  <si>
+    <t>US 202118030689 A</t>
+  </si>
+  <si>
+    <t>US 25522905 A</t>
+  </si>
+  <si>
+    <t>US 2021/0054204 W</t>
+  </si>
+  <si>
+    <t>US 2017/0043153 W</t>
+  </si>
+  <si>
+    <t>EP 14858675 A</t>
+  </si>
+  <si>
+    <t>US 9908705 W</t>
+  </si>
+  <si>
+    <t>US 201113281107 A</t>
+  </si>
+  <si>
+    <t>US 27975002 A</t>
+  </si>
+  <si>
+    <t>RU 2021130312 A</t>
+  </si>
+  <si>
+    <t>US 2019/0025292 W</t>
+  </si>
+  <si>
+    <t>EP 14173129 A</t>
+  </si>
+  <si>
+    <t>US 201916769336 A</t>
+  </si>
+  <si>
+    <t>RU 2003111241 A</t>
+  </si>
+  <si>
+    <t>US 67342900 A</t>
+  </si>
+  <si>
+    <t>RU 2009140817 A</t>
+  </si>
+  <si>
+    <t>US 10692302 A</t>
+  </si>
+  <si>
+    <t>RO 2012000029 W</t>
+  </si>
+  <si>
+    <t>US 0323349 W</t>
+  </si>
+  <si>
+    <t>US 62758303 A</t>
+  </si>
+  <si>
+    <t>US 201816627068 A</t>
+  </si>
+  <si>
+    <t>EP 10002345 A</t>
+  </si>
+  <si>
+    <t>US 9778102 A</t>
+  </si>
+  <si>
+    <t>RU 2012116219 A</t>
+  </si>
+  <si>
+    <t>UA 2001085834 A</t>
+  </si>
+  <si>
+    <t>US 2018/0040448 W</t>
+  </si>
+  <si>
+    <t>EP 17168506 A</t>
+  </si>
+  <si>
+    <t>US 2015/0028741 W</t>
+  </si>
+  <si>
+    <t>US 201515307440 A</t>
+  </si>
+  <si>
+    <t>US 201816609080 A</t>
+  </si>
+  <si>
+    <t>US 26032302 A</t>
+  </si>
+  <si>
+    <t>EP 2018060779 W</t>
+  </si>
+  <si>
+    <t>EP 12784129 A</t>
+  </si>
+  <si>
+    <t>US 96940801 A</t>
+  </si>
+  <si>
+    <t>US 77292691 A</t>
+  </si>
+  <si>
+    <t>GB 9202376 W</t>
+  </si>
+  <si>
+    <t>EP 18213484 A</t>
+  </si>
+  <si>
+    <t>EP 93900327 A</t>
+  </si>
+  <si>
+    <t>US 9208549 W</t>
+  </si>
+  <si>
+    <t>US 202418740776 A</t>
+  </si>
+  <si>
+    <t>US 202117236201 A</t>
+  </si>
+  <si>
+    <t>US 201214351408 A</t>
+  </si>
+  <si>
+    <t>US 59570904 A</t>
+  </si>
+  <si>
+    <t>US 201816182646 A</t>
+  </si>
+  <si>
+    <t>US 2012/0059955 W</t>
+  </si>
+  <si>
+    <t>US 201514634166 A</t>
+  </si>
+  <si>
+    <t>IB 2004003588 W</t>
+  </si>
+  <si>
+    <t>METHOD FOR TREATING INFECTIOUS AND INFLAMMATORY DISEASES OF KIDNEY</t>
+  </si>
+  <si>
+    <t>system for diagnostics of a functional state of lower urinary tracts</t>
+  </si>
+  <si>
+    <t>AGENT FOR CHRONIC PYELONEPHROSIS TREATMENT</t>
+  </si>
+  <si>
+    <t>METHOD FOR EVALUATION OF EFFECTIVENESS OF TREATMENT OF PATIENTS WITH CHRONIC PYELONEPHRITIS WITH RECURRENT COURSE</t>
+  </si>
+  <si>
+    <t>METHOD FOR DIAGNOSING FUNCTIONAL STATE OF KIDNEYS IN CHILDREN WITH CHRONIC RENAL DISEASE</t>
+  </si>
+  <si>
+    <t>SOCIAL NETWORK ANALYSIS</t>
+  </si>
+  <si>
+    <t>Use of Ultrasound Imaging equipment in classroom as a teaching aid</t>
+  </si>
+  <si>
+    <t>METHOD FOR TREATING ACUTE TOXIC NEPHROPATHY</t>
+  </si>
+  <si>
+    <t>METHOD FOR PREDICTING CHRONIC PYELONEPHRITIS WITH RECURRENT COURSE</t>
+  </si>
+  <si>
+    <t>THE METHOD FOR STIMULATION OF NONSPECIFIC AND SPECIFIC IMMUNITY, AND ANTIOXIDANT SYSTEM IN THE PATIENTS WITH CHRONIC PYELONEPHRITIS</t>
+  </si>
+  <si>
+    <t>METHOD OF COMPENSATION FOR ISCHEMIA OF KIDNEY TISSUE</t>
+  </si>
+  <si>
+    <t>LOW BURST SUSTAINED RELEASE LIPOPHILIC AND BIOLOGIC AGENT COMPOSITIONS</t>
+  </si>
+  <si>
+    <t>METHOD FOR INCREASING SENSITIVITY OF PCR-DIAGNOSTICS OF CHLAMYDIAL UROGENITAL INFECTION IN PATIENTS WITH PRONOUNCED EXUDATIVE INFLAMMATION</t>
+  </si>
+  <si>
+    <t>METHOD FOR DIAGNOSTICS OF DEGREE OF ACTIVITY OF PYELONEPHRITIS PROCESS IN CHILDREN</t>
+  </si>
+  <si>
+    <t>Method for differential diagnostics of glomerulonephritis and pielonephritis at stage of chronic kidney insufficiency of IV grade</t>
+  </si>
+  <si>
+    <t>SOLID, ORODISPERSIBLE AND/OR DISPERSIBLE COMPOSITION, WITHOUT AN EXCIPIENT OF KNOWN EFFECT AND ITS PROCESS OF PREPARATION</t>
+  </si>
+  <si>
+    <t>Method for predicting the risk of developing renal fibrosis/sclerosis in children with vesicoureteral reflux</t>
+  </si>
+  <si>
+    <t>DIAGNOSTIC TEST FOR DEVELOPMENT OF NEPHROGENOUS HYPERTENSION AND METHOD FOR ITS PROGNOSTICATION IN CHILDREN WITH CHRONIC PYELONEPHRITIS</t>
+  </si>
+  <si>
+    <t>Impregnated powder improving bioavailability and/or the solubility and method of production</t>
+  </si>
+  <si>
+    <t>Inferred specialty system</t>
+  </si>
+  <si>
+    <t>Social network analysis</t>
+  </si>
+  <si>
+    <t>METHOD FOR PREDICTING NEPHROSCLEROSIS IN CHILDREN</t>
+  </si>
+  <si>
+    <t>DIAGNOSTIC TECHNIQUE FOR NEPHROANGIOSCLEROSIS IN CHILDREN AND ADOLESCENTS</t>
+  </si>
+  <si>
+    <t>Impregnated powder improving bioavailability and/or solubility and method of production</t>
+  </si>
+  <si>
+    <t>METHOD FOR THE EARLY DIAGNOSIS OF UROPERITONEUM</t>
+  </si>
+  <si>
+    <t>ELECTRIC URETER STIMULATION TECHNIQUE</t>
+  </si>
+  <si>
+    <t>A MONITORING AND PREDICTION SYSTEM OF DIURESIS FOR THE CALCULATION OF KIDNEY FAILURE RISK, AND THE METHOD THEREOF</t>
+  </si>
+  <si>
+    <t>METHOD FOR DETERMINING THE RISK OF CALCIINATE DEVELOPMENT IN CASE OF CYSTIC OF KIDNEY DISEASES OF CHILDREN</t>
+  </si>
+  <si>
+    <t>FUNCTIONALIZED ZWITTERIONIC AND MIXED CHARGE POLYMERS, RELATED HYDROGELS, AND METHDS FOR THEIR USE</t>
+  </si>
+  <si>
+    <t>METHOD FOR UROLITHIASIS DIAGNOSIS</t>
+  </si>
+  <si>
+    <t>Method of Reducing Malpractice Premiums for Physicians</t>
+  </si>
+  <si>
+    <t>METHOD OF ORGAN-PRESERVING TREATMENT OF UROTHELIAL CANCER OF RENAL PELVIS</t>
+  </si>
+  <si>
+    <t>METHOD OF STONE-THROUGH THERAPY IN CASE OF UROLITHIASIS AFTER EXTRACORPOREAL SHOCKWAVE LITHOTRIPSY</t>
+  </si>
+  <si>
+    <t>GENETIC ANALYSIS</t>
+  </si>
+  <si>
+    <t>Genetic analysis</t>
+  </si>
+  <si>
+    <t>METHODS OF DISEASE DETECTION AND CHARACTERIZATION USING COMPUTATIONAL ANALYSIS OF URINE RAMAN SPECTRA</t>
+  </si>
+  <si>
+    <t>METHOD FOR DIAGNOSING OBSTRUCTIVE UROPATHIES IN NEWBORNS AND INFANTS</t>
+  </si>
+  <si>
+    <t>Canine erythropoietin gene and recombinant protein</t>
+  </si>
+  <si>
+    <t>FLUOROMETRIC SENSORY ARRAYS FOR THE DETECTION OF URINARY BLADDER CANCER-RELATED VOCS</t>
+  </si>
+  <si>
+    <t>DIAGNOSTIC TECHNIQUE FOR FUNCTIONAL STATE OF KIDNEY PARENCHYMA IN CHILDREN</t>
+  </si>
+  <si>
+    <t>Fidelity of physicians' thoughts to digital data conversions</t>
+  </si>
+  <si>
+    <t>KIDNEY TARGETED DELIVERY OF DRUGS</t>
+  </si>
+  <si>
+    <t>Best method of computerized transcriptions</t>
+  </si>
+  <si>
+    <t>ZWITTERIONIC MICROGELS, THEIR ASSEMBLIES AND RELATED FORMULATIONS, AND METHODS FOR THEIR USE</t>
+  </si>
+  <si>
+    <t>INTELLIGENT BIOIMPEDANCE SENSOR FOR BIOMEDICAL APPLICATIONS</t>
+  </si>
+  <si>
+    <t>CANINE ERYTHROPOIETIN GENE AND RECOMBINANT PROTEIN</t>
+  </si>
+  <si>
+    <t>Sterile Protective Membrane with Light Guides for a Medical Probe and Associated Method of Production</t>
+  </si>
+  <si>
+    <t>Method for creating a blood bank with associated data bank</t>
+  </si>
+  <si>
+    <t>Sterile Protective membrane with light guides for a medical probe and associated method of production</t>
+  </si>
+  <si>
+    <t>METHOD FOR LAPAROSCOPIC URETERONEOCYSTOANASTOMOSIS USING A SINGLE THREAD</t>
+  </si>
+  <si>
+    <t>MEDICAL RESIDENTIAL AND LABORATORY USES OF PURIFIED AIR</t>
+  </si>
+  <si>
+    <t>Combined use of amides of mono- and dicarboxylic acids and silymarin in the treatment of renal diseases</t>
+  </si>
+  <si>
+    <t>METHOD FOR CONSERVATIVE TREATMENT OF NEPHROPTOSIS</t>
+  </si>
+  <si>
+    <t>METHOD OF DIFFERENTIAL DIAGNOSTICS OF CALYX DIVERTICULA AND SOLITARY RENAL CYSTS IN CHILDREN</t>
+  </si>
+  <si>
+    <t>Use of an immediate-release powder in pharmaceutical and nutraceutical compositions</t>
+  </si>
+  <si>
+    <t>COMPLETE DIAGNOSTIC METHOD AND IMPLEMENTATION SYSTEM BY ON- LINE INTEGRATION OF A REAL TIME INTERACTING PANEL OF MEDICAL SPECIALITIES</t>
+  </si>
+  <si>
+    <t>METHODS FOR THE USE OF NEUROTOXIN IN THE TREATMENT OF UROLOGIC DISORDERS</t>
+  </si>
+  <si>
+    <t>Methods for the use of neurotoxin in the treatment of urologic disorders</t>
+  </si>
+  <si>
+    <t>N-OXIDE AND ECTOINE MONOMERS, POLYMERS, THEIR COMPOSITIONS, AND RELATED METHODS</t>
+  </si>
+  <si>
+    <t>Disposable towelette for genito-urinary and surrounding area</t>
+  </si>
+  <si>
+    <t>Film-forming powder, compositions containing it, methods for their preparation and their uses</t>
+  </si>
+  <si>
+    <t>METHOD OF RADIONUCLIDE DIAGNOSTICS OF FUNCTIONAL STATE OF KIDNEY PARENCHYMA</t>
+  </si>
+  <si>
+    <t>METHOD FOR TREATING FIBROPLASTIC PENILE INDURATION</t>
+  </si>
+  <si>
+    <t>DIAGNOSTIC TOOL TO DETERMINE PODOCYTE FOOT PROCESS EFFACEMENT</t>
+  </si>
+  <si>
+    <t>SYSTEM AND METHODS FOR SCORING DATA TO DIFFERENTIATE BETWEEN DISORDERS</t>
+  </si>
+  <si>
+    <t>Diagnostic tool to determine podocyte foot process effacement</t>
+  </si>
+  <si>
+    <t>Use of 5-HT4 modulators for the manufacture of a medicament for the treatment of the bladder diseases</t>
+  </si>
+  <si>
+    <t>TUBULAR PROSTHESES</t>
+  </si>
+  <si>
+    <t>Palatable trimethoprim oral solution</t>
+  </si>
+  <si>
+    <t>USE OF 5-HT4 MODULATORS FOR THE MANUFACTURE OF A MEDICAMENT FOR THE TREATMENT OF THE BLADDER DISEASES</t>
+  </si>
+  <si>
+    <t>TUBULAR PROTHESES</t>
+  </si>
+  <si>
+    <t>USE OF 5-HT4 - ANTAGONISTS FOR THE MANUFACTURE OF A MEDICAMENT FOR THE TREATMENT OF URINARY INCONTINENCE</t>
+  </si>
+  <si>
+    <t>TRIMETHOPRIM ORAL LIQUID</t>
+  </si>
+  <si>
+    <t>DETECTING THE PRESENCE OF URINARY STONE DISEASE USING A PLURALITY OF URINARY METABOLITES</t>
+  </si>
+  <si>
+    <t>Tubular Prostheses</t>
+  </si>
+  <si>
+    <t>Tubular prostheses</t>
+  </si>
+  <si>
+    <t>MYO-INOSITOL HEXAPHOSPHATE FOR TOPICAL USE</t>
+  </si>
+  <si>
+    <t>Urology &amp; Nephrology</t>
+  </si>
+  <si>
+    <t>The method for treating the infectious inflammatory diseases of the kidney relates to the medicine, namely to the urology and the nephrology and may be used for etiopathogenetic treatment of the infectious inflammatory diseases of the kidney.</t>
+  </si>
+  <si>
+    <t>A system for diagnostics of a functional state of lower urinary tracts relates to medicine, namely to urology, nephrology and andrology and can be used for combined remote diagnostics of patient urination.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine, urology, nephrology. SUBSTANCE: method of treatment involves the use of prostatilen that provides effect on both immune and hemostasis systems. EFFECT: enhanced effectiveness of treatment.</t>
+  </si>
+  <si>
+    <t>Method for evaluation of effectiveness of treatment of patients with chronic pyelonephritis with recurring course relates to medicine, in particular to nephrology and urology and can be used for determination of volume and duration of therapeutic measures for each particular patient.</t>
+  </si>
+  <si>
+    <t>A method for diagnosing the functional state of the kidneys in children with the chronic renal disease relates to medicine, namely to methods for diagnosis in nephrology and urology and may be used for assessing the functional state of the kidneys in the children with the chronic diseases of the urinary system.</t>
+  </si>
+  <si>
+    <t>This invention is generally directed to one or more systems or methods relating to social network analysis. More specifically, this invention is generally directed to one or more systems or methods relating to personal communication networks and the analysis of personal-communication-network data.</t>
+  </si>
+  <si>
+    <t>The inventive process named SWITCH is a unique teaching aid for students and teachers of biology to help them better understand the basic concepts and remove the ambiguities left behind by traditional teaching methods. It utilizes a portable ultrasound machine in a class room setting to obtain real time images of internal organs of human/animal body and project them on a big screen while the audience watches. The images so produced are not only vivid and multidimensional but also carry information like organ size, shape, texture, position and physical relationship to other organs in the body. In case of heart and blood vessels the real time images demonstrate exact function of chambers and valves and flow of blood in color from arterial to venous tree. The technique aims at fortifying truthful concepts of systems in a living body from the very basic to advanced levels of biology education. It has been developed in accordance with curricular guidelines for various levels and therefore has different modules dedicated to those levels (high school, colleges, universities, technical training institutes and other professional training institutions). Modules are based on chapters of respective recommended text books and can be utilized at the beginning, during or at the end of a chapter.</t>
+  </si>
+  <si>
+    <t>The invention relates to the medicine, in particular to urology and nephrology and may be used in treating the acute toxic nephropathy with the acute renal failure. The method comprises the localized exposure of the area of renal projection to the mechanical oscillations at a frequency of 1.3±0.1 kHz, the intensity of 140±10 mW/cm2 at a wavelength of 1.85±0.25 mm for 30±2 min.</t>
+  </si>
+  <si>
+    <t>The method relates to medicine, namely to nephrology, urology and clinical biochemistry and can be used for improving the efficacy of the therapy in the patients with chronic pyelonephritis with recurrent course. The method for predicting chronic pyelonephritis with recurrent course consists in measuring the index of the oxidative stress in blood serum of the patients with pyelonephritis prior to the treatment. The index exceeding 2.5 units is suggestive of the recurrent course of pyelonephritis.</t>
+  </si>
+  <si>
+    <t>The invention relates to the medicine, namely to urology, nephrology, in particular - to the treatment of chronic pyelonephritis. Method for stimulation of nonspecific and specific immunity, and antioxidant system in the patients with chronic pyelonephritis includes the stimulation of T-lymphocytes, phagocytic activity of leukocytes. The tincture of Echinacea (Echinacea purpurea) on 25 drops 30 minutes prior to food intake is prescribed for 14-day period.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine, more specifically, urology, nephrology, roentgenology; applicable in prophylaxis and treatment of chronic renal insufficiency, chronic pyelonephritis, nephrogenic hypertension of pyelonephritic and angiogenic character. SUBSTANCE: method includes roentgenoendovascular transcatheter treatment of kidney vessels by stenosing of subsegmental renal veins with help of introduction into vein of occlusion devices. EFFECT: reduced injury and terms of treatment. 2 cl, 4 dwg</t>
+  </si>
+  <si>
+    <t>FIELD: medicine, urology, nephrology, venerology, gynecology, pulmonology, obstetrics, neonatology, ophthalmology. ^ SUBSTANCE: before performing microbiological sample patients should be introduced with antibiotics of fluoroquinolonic group at the dosage of 100-250 mg twice daily for 2 d along with nonsteroid antiphlogistic preparations at the dosage of 75-150 mg/d for 2-3 d. The present innovation favors to put correct diagnosis and conduct corresponding therapy in the most optimal terms. ^ EFFECT: higher sensitivity of PCR-technique. ^ 2 tbl</t>
+  </si>
+  <si>
+    <t>The invention relates to medicine, in particular to child nephrology and child urology and can be used for diagnostics of degree of activity of pyelonephritis process in children and prescribes determination in urine of children with pyelonephritis disease of level of activity of thermo-stable calcium ferment N-acetyl--D-glucozaminidase B of lizosomic orogin, and at its increase over control values 1,5-3,4 times one diagnoses first or minimal degree, 3,5-5,4 times – second or moderate degree and at increase 5,5 and more times – third or maximal degree of activity of pyelonephritis process.</t>
+  </si>
+  <si>
+    <t>The invention relates to medicine, in particular to urology and nephrology and can be used for laboratory diagnostics of glomerulonephritis and pielonephritis in patients with chronic kidney insufficiency of IV grade. Method for differential diagnostics of glomerulonephritis and pielonephritis at stage of chronic kidney insufficiency of IV grade includes determination in urine of activity of lisosomic ferment of beta-galactozidase and comparison of activity of N-acetyl-beta-D-glukozaminidase to activity of beta-galactozidase and at coefficient of ratio K over 4.5 one diagnoses glomerulonephritis at stage of chronic kidney insufficiency of IV grade and at K value lower that 4.5 – pielonephritis at stage of chronic kidney insufficiency of IV grade. 1</t>
+  </si>
+  <si>
+    <t>The invention relates to medicine, namely to pediatrics, and can be used in urology and nephrology for predicting the risk of developing renal fibrosis/sclerosis in children with vesicoureteral reflux.Summary of the invention consists in that urine is collected dynamically from children with vesicoureteral reflux, namely before and after treatment, then the urine is examined using an enzyme-linked immunosorbent assay (ELISA) to determine the quantitative value of fibroblast growth factor-beta (FGF-beta) and kidney injury molecules-1 (KIM-1), if the quantitative value of FGF-beta exceeds 55 pg/ml, and KIM-1 exceeds 337 pg/ml, the risk of developing renal fibrosis/sclerosis in children with vesicoureteral reflux is predicted.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine, pediatrics, nephrology, urology. ^ SUBSTANCE: invention can be used for diagnosis and development of new effective methods for treatment of nephrogenous arterial hypertension in children with chronic pyelonephritis. Method involves the complex study of medical-biological, clinical-laboratory and functional indices and detection of risk factors in development of nephrogenous hypertension. Based on specific values of detected indices the method for prognostication in development of nephrogenous hypertension in children with chronic pyelonephritis has been developed. Invention provides the development of diagnostic test and method for prognostication in development of symptomatic nephrogenous hypertension in children with chronic pyelonephritis. ^ EFFECT: improved and valuable diagnostic test. ^ 4 cl, 2 tbl, 1 ex</t>
+  </si>
+  <si>
+    <t>A system identifies a clinician's specialty by examining procedures performed by that clinician, the diagnoses made by the clinician, and the age and gender of the clinician's patients.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine, urology, nephrology, pediatrics. ^ SUBSTANCE: one should carry out ultrasound dopplerographic renal studying at the mode of chromatic duplex mapping along calculation of resistance index upon segmental and arched renal arteries, moreover, the above-mentioned resistance index should be calculated by the well-known formula twice - before and 2 h after single peroral intake of specific blocking agent of angiotensin II (subtype AT1) receptors - losarthane at the dosage of 0.8 mg/kg and at unaltered values of resistance index being within 0.73-1.00 one should diagnose nephrosclerosis. The innovation enables to detect risk groups by nephrosclerotic development in case of obstructive uropathies and other forms of renal pathology, determine the tactics correctly, organize therapy and shorten the terms of patient's staying in hospital. ^ EFFECT: higher accuracy of diagnostics. ^ 3 ex, 3 tbl</t>
+  </si>
+  <si>
+    <t>FIELD: medicine. ^ SUBSTANCE: invention is related to medicine, namely paediatrics, paediatric nephrology and urology and aims at diagnosing nephroangiosclerosis in children and adolescents. Doppler sonography of renal vessels is conducted. A maximum systolic speed and a resistance index are measured at the level of interlobal renal arteries prior to and 30 minutes after intramuscular injections of Lasiks 1 mg/kg. If the end diastolic speed reduces more than 5% and resistance index increases more than 2%, a normal reaction of the renal parenchyma arteries is to be diagnosed. The unchanged blood flow velocity rates, or the increasing end diastolic velocity and the decreasing resistance index enables diagnosing the presence of fibrosclerotic, dysplastic changes in the renal parenchyma - nephroangiosclerosis. ^ EFFECT: technique is simple; it doesn't require special preparation for examination, allows detecting nephroangiosclerosis in children and adolescents at the different stages of renal disease. ^ 2 ex</t>
+  </si>
+  <si>
+    <t>The present invention refers to a diagnostic method for the diagnosis, including early diagnosis, of uroperitoneum in patients, in particular in urological patients in a post-surgical phase following urological surgery, comprising the detection of a biomarker in a sample of abdominal drainage previously taken from the patient.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine; biophysics.SUBSTANCE: invention relates to medicine and biophysics, can be used in pediatrics, nephrology, urology. Electric oscillations are excited in the patient's body by means of electrodes, one of which is located in the area of the pubic bone, and the other is paravertebral along the external edge of the spinal straightening muscle in the area between the XII rib and the sacral segment. Feed electric oscillation occurs sequentially for every paravertebrally electrodes disposed in the direction of sacral pulse signal generated in the burst. Further, the signal is supplied with amplitude of 12 V, pulse repetition frequency in the pack is selected to be 5 kHz, the repetition frequency of the packs is selected to be 3–30 Hz, wherein the pulse packets are continuously supplied. Excitation carried out for 3–5 minutes 1 time per day for 5–20 days.EFFECT: what is presented is a method for ureter stimulation.1 cl, 4 dwg, 1 tbl, 1 ex</t>
+  </si>
+  <si>
+    <t>The invention relates to a monitoring system, and the related monitoring and predicting methods of diuresis (1) for the calculation of the risk of onset of renal failure of a patient, including a device (5) comprising a first algorithm (15) for recording, storing, comparing and processing the measurements of the urine container (2) and a second algorithm (25) for predicting the future measurements of the urine container (2) and the level of kidney failure risk associated with them. The invention also relates to, more generally, to a monitoring system, and relevant monitoring and predicting methods, of biological fluid (10) for predicting the state of health of a patient, comprising a device (50) comprising a first algorithm (150) for recording, storing, comparing and processing the measurements of the biological fluid container (20) and a second algorithm (250) for predicting the future measurements of the biological fluid container (20) and the patient's state of health associated with them. The present invention finds advantageous applications in hospital and nursing clinic, intensive care, nephrology, urology, cardiology and transplant fields.</t>
+  </si>
+  <si>
+    <t>The invention relates to a monitoring system (1), and the related monitoring and predicting methods of diuresis for the calculation of the risk of onset of renal failure of a patient, including a device (5) comprising a first algorithm (15) for recording, storing, comparing and processing the measurements of the urine container (2) and a second algorithm (25) for predicting the future measurements of the urine container (2) and the level of kidney failure risk associated with them. The invention also relates to, more generally, to a monitoring system, and relevant monitoring and predicting methods, of biological fluid (10) for predicting the state of health of a patient, comprising a device (50) comprising a first algorithm (150) for recording, storing, comparing and processing the measurements of the biological fluid container (20) and a second algorithm (250) for predicting the future measurements of the biological fluid container (20) and the patient's state of health associated with them. The present invention finds advantageous applications in hospital and nursing clinic, intensive care, nephrology, urology, cardiology and transplant fields.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention refers to medicine, namely to nephrology and urology, and can be used in order to predict complications of polycystic kidney disease that increase the severity of the disease, in particular, to predict the formation of calcifications in the cysts of the kidneys. Citrate-creatinine index is calculated according to the following formula in order to determine the risk of development of calcifications in children with polycystic kidney disease in urine, determine the daily excretion of citrates and creatinine: N=C/K, where N is the citrate-creatinine index; C – daily excretion of citrates, mmol/l; K – creatinine content in urine, mmol/l and at N less than 0.3 the risk of calcification in the kidney cysts is defined as high.EFFECT: technical result consists in the reliable prediction of the development of calcification in polycystic kidney disease by means of examining the biochemical components of urine, which allows to timely start the appropriate therapy, including the appointment of citrate-containing drugs.1 cl, 3 ex</t>
+  </si>
+  <si>
+    <t>Functionalized zwitterionic and mixed charge polymers and copolymers, methods for making the polymers and copolymers, hydrogels prepared from the functionalized zwitterionic and mixed charge polymers and copolymers, methods for making and using the hydrogels, and zwitterionic and mixed charge polymers and copolymers for administration for therapeutic agents.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention relates to medicine, namely to nephrology and urology,and can be used to diagnose urolithiasis. Method for diagnosis of urolithiasis includes preliminary preparation of a patient's serum sample, study of a prepared serum sample using IR spectroscopy, determination of the peak height of absorption bands with maxima on the IR spectrum 1,170; 1,140; 1,130; 1,070; 1,060; 1,025 cm, calculation of peak height to peak ratio at 1,170 cmto the height of the peak with a maximum of 1,140 cm, at 1,130 cmto the height of the peak with a maximum of 1,025 cm, at 1,070 cmto the height of the peak with a maximum of 1,060 cmand at a ratio of 1,170/1,140, equal to 0.28±0.05, a ratio of 1,130/1,025, equal to 0.67±0.10, and at a ratio of 1,070/1,060, equal to 1.01±0.09, diagnose urolithiasis.EFFECT: invention allows to diagnose with high accuracy urolithiasis without large material and time costs.1 cl, 3 ex</t>
+  </si>
+  <si>
+    <t>Methods of reducing medical malpractice insurance premiums for physicians or hospitals and reducing health care costs for employees covered by an employer's health plan. Employees waive their rights to litigate any potential medical malpractice claims. The reduction of risk of potential malpractice claims reduces the cost of insuring medical malpractice policies. These reduced costs for the insurance underwriters are passed as savings to employees in the form of reduced health insurance premiums and physicians in the form of reduced malpractice insurance premiums.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention refers to medicine, namely to oncology, urology, nephrology, and can be used for organ-preserving treatment of urothelial cancer of renal pelvis. That is ensured by introducing a chlorine E6 photosensitiser once in the form of an intravenous drop infusion for 30 minutes at dose of 1.0 mg/g for 3 hours before surgery. That is followed by fibrourethropyeloscopy. Volume of tumor involvement is estimated. Primary percutaneous approach to nephroscope 24 Ch is formed. Additionally, mini-nephroscope 5.5 Ch is installed. Tumors are removed with the help of a monopolar resectoscope and a laser apparatus. Session of an intraoperative photodynamic therapy is performed. For this purpose, an optical fiber is performed along the working path of the nephroscope and the cavity of the pelvis is irradiated with a laser with light exposure of radiation with wavelength of 662±3 nm in dose of 50–100 J/cm.EFFECT: method provides reducing sessions of intra-local interventions, reducing frequency and complications, reducing length of hospitalization, avoiding organ-carrying treatment – nephroureterectomy, programmed hemodialysis.1 cl, 1 ex</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention relates to medicine, namely to urology, nephrology and physiotherapy, and can be used to treat urolithiasis. Correction of the system of blood circulation regulation of the organs of the upper urinary tract is performed by percutaneous action on the lower thoracic and lumbar ganglia of the sympathetic nervous system by a rotating field of electrical impulses. Field is formed in the space between the ganglia by means of two multi-element electrodes. Each of the electrodes contains several partial galvanically isolated conductive elements performing the function of cathodes, and one element serving as an anode. Electrodes are placed in the projection of the corresponding ganglia. When the cathodes are connected in series in the space between the cathode and the anode, the position of the current vector changes and a rotating electric field of current pulses is created. Frequency, duration and amplitude of the pulses are set individually for each patient.EFFECT: method allows to improve the peristalsis of the ureter, to reduce the ischemia of the renal parenchyma, to restore renal hemodynamics after remote shock wave lithotripsy, that ensures earlier and more effective separation of fragments and small ureteral stones with earlier restoration of renal functions.1 cl, 1 ex</t>
+  </si>
+  <si>
+    <t>The present invention provides methods for generating genetic profiles or analyses, fncluded are methods for conducting comprehensive, dynamic genetic testing and/or analysis. Also provided are methods for determining genetic health scores for specific phenotypes as well as for organ systems, for certain specialties, and for overall health.</t>
+  </si>
+  <si>
+    <t>The present invention provides methods for generating genetic profiles or analyses. Included are methods for conducting comprehensive, dynamic genetic analysis. Also provided are methods for determining genetic health scores for specific phenotypes, such as diseases, disorders, traits, and conditions, as well as for organ systems, for certain medical specialties, and for overall health.</t>
+  </si>
+  <si>
+    <t>Disease detection and characterization using computational analysis of Raman spectra is used to detect disease-specific multi-molecular patterns “spectral fingerprint” associated with specific diseases, cellular physiologic derangements, or altered metabolism from systemic reactions to disease. Comparison of the Raman spectral fingerprint of urine from subjects with specific diseases and those not (healthy persons) provides the means to identify key disease-associated changes in urine molecular composition. Methods include applying baseline correction to spectra of a desired wavenumber range e.g., with the Goldindec algorithm, or with ISREA and StaBAL; vector or specific band normalization; and one or more of principal component analysis (PCA); discriminant analysis of principal components (DAPC); principal least squares (PLS) regression, machine learning with neural networks (NN); identification of wavenumber loadings; calculation of total canonical distance (TCD); total spectral distance (TSD), total principal component distance (TPD); ANOVA; pairwise comparisons; and performing leave-one-out or multi-fold cross-validation analysis of chemometric models (DAPC, PLS, NN) to report predictive capabilities in terms of accuracy, sensitivity (true-positives), and specificity (true-negatives), positive predictive value (PPV) and negative predictive value (NPV).</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention relates to the field of medicine, namely to urology, nephrology, pediatrics and ultrasound diagnostics, and can be used in the diagnosis of obstructive uropathies in infants. To do this, an ultrasound examination (scan) is performed with the calculation of the resistance index on the segmental and arc arteries of the kidneys. In addition, pulse-wave dopplerometry with duplex scanning of kidney vessels in the clinostatic position is performed 2 times with ultrasound: before the next physiological feeding and 1 hour after the next physiological feeding. The expansion of the calyx-pelvic system is visualized and determined, corticomedullary differentiation is visualized, the presence of blood flow is detected in the mode of energy Doppler mapping and the resistance index (RI) is calculated at the level of segmental, interlobular and arc renal arteries. When registering an RI of 0.77±0.04, the size of the renal pelvis is 15 mm and the thickness of the renal parenchyma is 9-10 mm, the diagnosis of obstructive uropathy is verified.EFFECT: method provides a highly informative and effective diagnosis of obstructive uropathies in this category of children, excluding isotopic research methods and diuretic loads for choosing surgical treatment tactics by developing certain criteria for evaluating the calyx-pelvic system.1 cl, 2 ex</t>
+  </si>
+  <si>
+    <t>One aspect of the present invention is an isolated nucleic acid molecule encoding canine erythropoietin. The present invention also relates to an isolated canine erythropoietin protein or polypeptide. Another aspect of the present invention is a method for providing erythropoietin therapy to a dog or a cat including administering recombinant canine erythropoietin to a dog or a cat in need of erythropoietin therapy is an amount sufficient to increase production or reticulocytes and red blood cells in the dog or cat.</t>
+  </si>
+  <si>
+    <t>A system/"NABIL" device based on an array of environmentally sensitive f luorophores, selected from Nile Red (NR), Eosin Y (EY) and Rose Bengal (RB) as sensor materials for detecting bladder cancer VOCs from urine samples. Large increment of fluorescence intensity with a spectral shift of fluorophores could be recorded by the calorimetric unit upon the interaction of the fluorescent sensor dyes with trapped VOC, ethyl benzene present in urinary bladder cancer.</t>
+  </si>
+  <si>
+    <t>One aspect of the present invention is an isolated nucleic acid molecule encoding canine erythropoietin. The present invention also relates to an isolated canine erythropoietin protein or polypeptide. Another aspect of the present invention is a method for providing erythropoietin therapy to a dog or a cat including administering recombinant canine erythropoietin to a dog or a cat in need of erythropoietin therapy in an amount sufficient to increase production of reticulocytes and red blood cells in the dog or cat.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention refers to medicine, namely to urology and nephrology, and can be used for diagnosing functional state of kidney parenchyma in children. Ultrasonic examination is carried out using colored Doppler mapping with preliminary triple dosed water load for 120, 60 and 20 minutes before the beginning of the study per os in amount of 10 ml/kg of weight, but not more than 300 ml for a single dose. If observing the first ureteral ejection (UE) in vesicoureteral junction 20–30 minutes after the last water load, the normal functional state of the kidney parenchyma is diagnosed. If observing the first and subsequent UE within 30 minutes to 60 minutes after the last water load, the functional state of the kidney parenchyma is reduced. In the absence of UE within 30–60 minutes after the last water load, a non-functioning kidney is diagnosed.EFFECT: method is highly informative, does not depend on kidney tissue tropism to radiopharmaceutical, is safe, can be applied on an ambulatory basis in children since birth, allows avoiding false-negative result in case of non-functioning kidney.1 cl, 5 ex</t>
+  </si>
+  <si>
+    <t>A system of administering words, terms and phrases for optimizing the fidelity and accuracy of health and health-care information on patients generated by physicians in the process of transferring the information from physicians' minds to digital voice data to first digital text data derived from the conversions of corresponding digital voice data to first digital text data. The system provides the editions of and additions of second digital text data into first digital text data.</t>
+  </si>
+  <si>
+    <t>The present disclosure provides, inter alia, compositions comprising drug-containing polymeric particles, wherein each drug-containing polymeric particle is attached to one or more immunoglobulin light chains or a megalin-binding fragment thereof. Methods of preparing and using these drug-containing polymeric particles are also provided.</t>
+  </si>
+  <si>
+    <t>A method of labeling individual digital data with individual physicians' medical or surgical specialties and of corresponding words in digital text data to words in corresponding digital voice data wherein digital text data are generated by computer-automated conversions of digital voice data into digital text data and of corresponding words in digital voice data or digital text data with words in digital medical and surgical dictionaries and thesauruses for improving the accuracy of information between information in digital text data and their parent digital voice data.</t>
+  </si>
+  <si>
+    <t>Zwitterionic microgels, zwitterionic microgel assemblies, their formulations and methods for their use.</t>
+  </si>
+  <si>
+    <t>The invention relates to an intelligent bioimpedance sensor for biomedical applications, which can carry out bioimpedance measurements in a plurality of configurable frequencies, process data in order to obtain the modulus and the phase of the bioimpedance (or real and imaginary part of the bioimpedance) in each of the frequencies, and wirelessly transmit the results of the processing, configured by means of a device that is in contact with the biological means to be measured by means of a series of electrodes in such a way that the device injects electrical current, via said electrodes, into the biological means, in the different frequencies, and measures the tension generated by the circulation of said current based on the joint operation of various subsystems.</t>
+  </si>
+  <si>
+    <t>One aspect of the present invention is an isolated nucleic acid molecule encoding canine erythropoietin. The present invention also relates to an isolated canine erythropoietin protein or polypeptide. Another aspect of the present invention is a method for providing erythropoietin therapy to a dog or a cat including administering recombinant canine erythropoietin to a dog or a cat in need of erythropoietin therapy in an amount sufficient to increase production or reticulocytes and red blood cells in the dog or cat.</t>
+  </si>
+  <si>
+    <t>In the field of dual-mode medical probes, a simple device perfectly meets the double need for dual-modality and sterilization, and provides a sterile, disposable, or sterilizable protective membrane, also called a “glove” or “sock”, equipped with optical fibres. This protective membrane can be slipped onto an ultrasound probe. It therefore ensures both the dual-mode functionality and perfect sterilization of the probe, this being the desired effect. The protective membrane is easy to produce and easy to use.</t>
+  </si>
+  <si>
+    <t>The present invention relates to a method for creating a blood bank in which blood samples are preserved and the values determined from the blood samples can be linked via suitable algorithms to a data bank in which clinical data and specialized medical knowledge are stored.</t>
+  </si>
+  <si>
+    <t>In the field of dual-mode medical probes, a simple device perfectly meets the double need for dual-modality and sterilization, and provides a sterile, disposable, or sterilizable protective membrane, also called a “glove” or “sock”, equipped with optical fibers. This protective membrane can be slipped onto an ultrasound probe. It therefore ensures both the dual-mode functionality and perfect sterilization of the probe, this being the desired effect. The protective membrane is easy to produce and easy to use.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention relates to medicine, namely to urology, surgery, nephrology, transplantology. The ureter and bladder are mobilized, the ureter is ligated and transected, and the bladder detruser is incised. At the same time, the formation of ureteroneocystoanastomosis is carried out using a thread with a loop and a needle (V-lock type). To do this, two holding stitches are performed without puncturing the mucosa proximal to the spatulation zone. Then, the mucosa and muscle layer are punctured from the outside to the inside into the lateral angle of the bladder and ureter. After that, the posterior lip of the anastomosis is formed with a muscular-serous continuous suture from the lateral angle to the medial one, where a duplicate stitch is formed to prevent the suture from unraveling. An internal ureteral stent is placed. The anterior lip of the anastomosis is formed with a continuous muscular-serous suture from the medial to the lateral angle, where a duplicate stitch is also performed.EFFECT: method allows to form a reliable hermetic anastomosis, reduce the operation time, reduce the traumatization of patients, which leads to a decrease in the frequency of intra- and postoperative complications, improves the final result of the operation, accelerates rehabilitation after surgery, reduces the length of the patient's stay in the hospital and reduces the economic costs of stage of the operation.1 cl, 1 ex, 7 dwg</t>
+  </si>
+  <si>
+    <t>The air purification technology and methods of the disclosure will reduce the levels of airborne biological, chemical, and particulate contamination and thus improve outcomes in, for example, all areas of basic, applied, commercial, industrial, biological, and chemical research and manufacturing, as well as hospital settings, and long-term care facilities, as set forth herein.</t>
+  </si>
+  <si>
+    <t>FIELD: medicine, urology, nephrology. ^ SUBSTANCE: the present innovation deals with prescribing the massage, physical exercises, the mode to restrict lifting of heavy things, medicinal therapy and application of special bandage. Massage should be conducted by stages beginning from vertebral and lumbar areas followed by abdominal massage, then comes manual renal reposition to finish the course with a complex of special physical exercises with the help of a masseur at a course of 10 procedures, each procedure lasts for 60 min, also, after the 5th and the 10th seances one should perform renal US-survey to visualize organ reposition. Massage of vertebral, lumber and abdominal areas includes fold's stroking, stretching and rolling. Renal manual reposition should be carried out by "lifting" and "shaking" lumbar area. After massage a patient should do a complex of special exercises with the help of a masseur. Then, after exercises, a patient should put on a bandage onto lumber area in initial position at recommendation to remove the bandage in 1 h. When the course is over a patient should be prescribed to fulfill recommended complex of physical exercises at home independently during 1 yr. The innovation enables to obtain more stable curative result. ^ EFFECT: higher efficiency of therapy. ^ 2 cl, 24 dwg</t>
+  </si>
+  <si>
+    <t>FIELD: medicine. ^ SUBSTANCE: invention relates to medicine, namely to nephrology and urology and is intended for differential diagnostics of calyx diverticula and solitary renal cysts in children. After carrying out water loading in amount 10 mg/kg of child body weight and intramuscular introduction of lasix in dose 0.6 mg/kg of child body weight, ultrasonic examination (USE) is performed 20 and 30 minutes after lasix introduction. In case, if after 20 minutes, during ultrasonic examination pelvis and cystic formation, which is not connected with kidney collector system, are visualised, and 30 minutes after lasix introduction during ultrasonic examination size of cystic formation does not increase in dynamics - solitary cyst is diagnosed. In case, if after 20 minutes after lasix introduction, during ultrasonic examination pelvis, cystic formation and dilatation of renal calyx neck are visualised, and 30 minutes after - increase of cystic formation dimensions and renal calyx neck diametre - calyx diverticulum is diagnosed. ^ EFFECT: method ensures possibility of carrying out differential diagnostics of solitary renal cysts and calyx diverticula, as a result of visualisation during ultrasonic scanning of calyx neck dilatation under conditions of water loading and forced diuresis. ^ 7 dwg, 4 ex</t>
+  </si>
+  <si>
+    <t>Methods and compositions for treating urological disorders are provided. In the subject methods, an effective amount of a neurotoxin is intravesically delivered into the bladder lumen of a patient in need thereof. Also provided are compositions, e.g., pharmaceutical preparations and kits, for practicing the subject methods.</t>
+  </si>
+  <si>
+    <t>N-oxide and monomers, N-oxide polymers and copolymers, methods for making the N-oxide monomers, polymers, and copolymers, compositions and materials that include N-oxide polymers and copolymers, and methods for using the N-oxide monomers, N-oxide polymers, and N-oxide copolymers.</t>
+  </si>
+  <si>
+    <t>A disposable napkin for genito-urinary and surrounding areas is described, comprising: a first layer (A) made of soft, semi-waterproof viscose, the semi-waterproof strata allowing the passage of water polluted by micro-organisms towards the central part (CP) and preventing its return back to the surface; a second layer or central part (CP), made up of highly-absorbent TNT tissue to guarantee the capturing of every single drop of water to ensure a dry surface where used; and a third layer (B) equal to the first layer (A) and made of the same material, wherein the second layer (CP) is sandwiched between the first layer (A) and the second layer (B).</t>
+  </si>
+  <si>
+    <t>FIELD: medicine.SUBSTANCE: invention relates to medicine, radionuclide diagnostics in urology and nephrology with estimation of kidney parenchyma state in case of congenital and acquired diseases of kidneys and urinary tract. Registration of scintigrams is performed 15, 30 and 120 min after intravenous introduction of radiopharmaceutical preparation (RPP) to patient. Image of kidneys is divided with horizontal and vertical lines into equal zones. In each of zones of scintigrams, obtained 15, 30 and 120 min after RPP introduction, number of impulses originating from zone is counted automatically with further determination of total quantity of impulses from all zones of kidney. Values of indices of zone (ZA) and total zone accumulation (?ZA) of RPP by parenchyma on 15, 30 and 120 min performed is calculation of indices of RPP accumulation intensity by each zone (IZA) and entire kidney (I?ZA) for separate time periods of examination: 0-15, 15-30, 30-120 min. Intensity of impairment of RPP capture by tubules of dysfunctional zones is estimated by degree of difference of zone accumulation (ZA) indices - by deviation from norm values for healthy kidney. Ratio of intensity of early - by 15 min and delayed - from 30 to 120 min of total zone accumulation of RPP I?ZA15/ I?ZA90 is used to judge about functional consistency and reserve possibilities of renal tubules on the whole.EFFECT: method ensures increase of diagnostics accuracy.1 dwg, 2 ex</t>
+  </si>
+  <si>
+    <t>The method for treating the fibroplastic penile induration comprises electrophoresis with hyaluronidase, therapy with vitamin E, and the following complex of the drugs: stugeron - 25 mg, vobenzime - 5dragee thrice a day, trental - 200 mg twice a day (all the drugs are taken for a month). At the same time the following procedures are employed: phonophoresis with sodium diclophenac gel, vibroacoustics, and local exposure to the negative pressure (0.3 atm., twice a day). The duration of each procedure is 10 minutes. The 10-days course for each procedure is provided for. The procedures are separated by 2-hour interval.</t>
+  </si>
+  <si>
+    <t>The present invention relates to a method for diagnosing or pre-diagnosing a disease associated with podocyte foot process effacement in a subject or for determining the risk of a subject to develop a disease associated with podocyte foot process effacement, said method comprising the steps of a) determining the length of the slit diaphragm (I SD ) formed by podocyte foot processes in a specific area A in a renal tissue sample of said subject by super resolution light microscopy; b) comparing the length of the slit diaphragm (I SD ) formed by podocyte foot processes in a specific area A as determined in step (a) with the length of the slit diaphragm (I SD ) formed by podocyte foot processes in a comparable specific area A' in a renal tissue sample of a subject who at the time of the sampling showed no clinical symptoms of a disease associated with podocyte foot process effacement, wherein a deviation indicates a disease associated with podocyte foot process effacement.</t>
+  </si>
+  <si>
+    <t>A clinical scoring system and methods that effectively and efficiently utilizes a number of different data sources to determine a diagnosis of patient conditions. The score is compared to a spectrum of scores in order to identify between disorders, such as Inflammatory bowel disease (IBD) and irritable bowel syndrome (IBSd) or gastroesophageal reflux disease (GERD) and functional dyspepsia.</t>
+  </si>
+  <si>
+    <t>The present invention relates to a method for diagnosing or pre-diagnosing a disease associated with podocyte foot process effacement in a subject or for determining the risk of a subject to develop a disease associated with podocyte foot process effacement, said method comprising the steps of a) determining the length of the slit diaphragm (ISD) formed by podocyte foot processes in a specific area A in a renal tissue sample of said subject by super resolution light microscopy; b) comparing the length of the slit diaphragm (ISD) formed by podocyte foot processes in a specific area A as determined in step (a) with the length of the slit diaphragm (ISD) formed by podocyte foot processes in a comparable specific area A in a renal tissue sample of a subject who at the time of the sampling showed no clinical symptoms of a disease associated with podocyte foot process effacement, wherein a deviation indicates a disease associated with podocyte foot process effacement.</t>
+  </si>
+  <si>
+    <t>A compound which acts as an antagonist at 5-HT4 receptors is of potential use in the treatment of conditions associated with bladder hypersensitivity, such as urinary incontinence, which is often associated with irritable bowel syndrome (IBS) and a compound which acts as an agonist at 5-HT4 receptors is of potential use in the treatment of conditions associated with a poorly functioning bladder, such as urinary bladder hypoactivity following prostectomy.</t>
+  </si>
+  <si>
+    <t>This invention is directed to an aqueous pharmaceutical composition with 1.25 mg to about 10 mg trimethoprim per mL (wt/vol) of solution and a compound of suitable acid strength to permit the dissolving of trimethoprim at the appropriate concentration, with the composition having a pH of less than 6.0. This composition is particularly useful for pediatric oral use.</t>
+  </si>
+  <si>
+    <t>The present invention relates to systems, kits, and methods for identifying subjects with increased levels (e.g., in a urine sample) of at least two urine metabolites selected from: butanal; 2-Hydroxy-1,3-dimethoxy-8,9-methylenedioxycoumestan; 6-Methylmercaptopurine; Dimethyl-L-arginine; N-butanoyl-lhomoserine lactone; Hexanoylglycine; Methyl propenyl ketone; Ferulate; 2-Oxoarginine; and 2-Hydroxyestradiol-3-methyl ether, as well as methods of determining if a subject has or is at risk of urinary stone disease based on such urine metabolites. In certain embodiments, the urinary tract of a subject with elevated levels of at least two of the urine metabolites is imaged (e.g., to generate an image showing the size, location, or number of urinary stones present).</t>
+  </si>
+  <si>
+    <t>Tubular prostheses are provided for use in airways, upper digestive, and urinary tracts. Each of these uses has its own specific sets of biological specifications, based on what it must contain and exclude and the physical and chemical pressures and stresses to which it is subjected. The prostheses may be made from allogeneic cells. Thus they can be manufactured and stored prior to an individual's personal need arising.</t>
+  </si>
+  <si>
+    <t>The invention relates to a composition that includes myo-inositol hexaphosphate applied by topical administration for utilisation in the treatment or prevention of a disease associated with the development of heterogeneous nucleants in a soft tissue. Said composition can be used for manufacturing a drug for the treatment of a disease associated with the development of heterogeneous nucleants in a soft tissue</t>
+  </si>
+  <si>
+    <t>The present invention describes a system of automatic interaction between three groups of participants: a multitude of health care provider units, pharmacies or pharmaceutical or medical device manufacturers, a central organization system and a multitude of potential health care users or payers such as potential patients or groups of patients, employers or insurance companies. The purpose of the automatic interaction executed by the central organization system is to determine the best or lowest acceptable negotiated price for healthcare services or medications/devices by interested parties such as individual patients or groups of patients, employers or health insurance companies and resulting into a contract that will apply over a comprehensive all-inclusive list of health services or medications or devices, and that will result into health services rendered or medications or devices being sold from the all inclusive comprehensive list of services, medications or devices at any time during the time period indicated in contract.</t>
+  </si>
+  <si>
+    <t>The invention relates to a composition that includes myo-inositol hexaphosphate in a form adapted to topical administration for utilisation in the treatment or prevention of a disease associated with the development of heterogeneous nucleants in a soft tissue. Said composition can be used for manufacturing a drug for the treatment of a disease associated with the development of heterogeneous nucleants in a soft tissue.</t>
+  </si>
+  <si>
+    <t>GRASES FREIXEDAS FELICIA;;PERELLO BESTARD JOAN;;ISERN AMENGUAL BERNAT;;PRIETO ALMIRALL RAFAEL;;COSTA BAUZA ANTONIA</t>
+  </si>
+  <si>
+    <t>SIEGERIST FLORIAN;;ENDLICH KARLHANS;;ENDLICH NICOLE</t>
+  </si>
+  <si>
+    <t>ANGHELOIU GEORGE O;;ANGHELOIU NICOLETA A;;SUBRAMANY NARAYANA;;ANGHELOIU VIOREL;;HAIDUC OVIDIU</t>
+  </si>
+  <si>
+    <t>NIKLASON LAURA;;HUANG ANGELA;;DAHL SHANNON</t>
+  </si>
+  <si>
+    <t>NIKLASON LAURA;;HUANG ANGELA;;ZHAO LIPING;;DAHL SHANNON</t>
+  </si>
+  <si>
+    <t>GRASES FREIXEDAS FELICIA</t>
+  </si>
+  <si>
+    <t>MILLER AARON W;;AGUDELO JOSE</t>
+  </si>
+  <si>
+    <t>MENDES ROBERT W;;PATHAK NITIN;;CLEMENTE EMMETT</t>
+  </si>
+  <si>
+    <t>SANGER GARETH JOHN;;WARDLE KAY ALISON</t>
+  </si>
+  <si>
+    <t>NIKLASON LAURA;;HUANG ANGELA;;DAHL SHANNON;;ZHAO LIPING</t>
+  </si>
+  <si>
+    <t>ENDLICH KARLHANS;;ENDLICH NICOLE;;SIEGERIST FLORIAN</t>
+  </si>
+  <si>
+    <t>ENDLICH KARLHANS;;ENDLICH NICOLE;;SLEGERIST FLORIAN</t>
+  </si>
+  <si>
+    <t>CAVE DAVID;;MARYA NEIL;;MACOMBER CHRISTOPHER</t>
+  </si>
+  <si>
+    <t>LI BOWEN;;JIANG SHAOYI;;JAIN PRIYESH;;MA JINRONG</t>
+  </si>
+  <si>
+    <t>HORPYNCHENKO IHOR IVANOVYCH;;HURZHENKO YURII MYKOLAIOVYCH</t>
+  </si>
+  <si>
+    <t>MATJUSHINA KATERINA MARKOVNA;;ROSTOVSKAJA VERA VASIL EVNA;;FOMIN DMITRIJ KIRILLOVICH;;KAZANSKAJA IRINA VALER EVNA</t>
+  </si>
+  <si>
+    <t>LAGANO ROCCO</t>
+  </si>
+  <si>
+    <t>BESSE JEROME;;BESSE LAURENCE;;CORNU PHILIPPE;;TARAVELLA BRIGITTE</t>
+  </si>
+  <si>
+    <t>JIANG SHAOYI;;JAIN PRIYESH;;MA JINRONG</t>
+  </si>
+  <si>
+    <t>DOSHI RAJIV</t>
+  </si>
+  <si>
+    <t>BÎZGAN ADRIAN;;ANDREI VALENTIN MANU MARIN</t>
+  </si>
+  <si>
+    <t>BESSE JEROME;;BESSE LAURENCE</t>
+  </si>
+  <si>
+    <t>VRUBLEVSKAJA ELENA NIKOLAEVNA;;GUREVICH ANZHELIKA IOSIFOVNA;;KOVARSKIJ SEMEN L VOVICH;;VRUBLEVSKIJ SERGEJ GRANITOVICH;;FEOKTISTOVA ELENA VLADIMIROVNA;;PODDUBNYJ GEORGIJ SERGEEVICH</t>
+  </si>
+  <si>
+    <t>MACLEOD JAMES N</t>
+  </si>
+  <si>
+    <t>CHIKHAREV A V;;GUDKOV A V</t>
+  </si>
+  <si>
+    <t>WORRILOW KATHRYN C</t>
+  </si>
+  <si>
+    <t>DELLA VALLE FRANCESCO;;DELLA VALLE MARIA FEDERICA;;MARCOLONGO GABRIELE;;CUZZOCREA SALVATORE</t>
+  </si>
+  <si>
+    <t>WORRILOW KATHRYN</t>
+  </si>
+  <si>
+    <t>SOKOLOV ALEKSANDR ALEKSANDROVICH;;MARTOV ALEKSEJ GEORGIEVICH;;SOKOLOV SERGEJ ALEKSANDROVICH</t>
+  </si>
+  <si>
+    <t>BOUTET JÉR HACEK OVER O ME;;DEBOURDEAU MATHIEU</t>
+  </si>
+  <si>
+    <t>GROSSE RICHARD;;RODGER HANS-JOACHIM;;GERHARD WOLFGANG;;GROSSE ROBERT</t>
+  </si>
+  <si>
+    <t>BOUTET JEROME;;DEBOURDEAU MATHIEU</t>
+  </si>
+  <si>
+    <t>ROA ROMERO LAURA MARIA;;REINA TOSINA LUIS JAVIER;;NARANJO HERNANDEZ DAVID;;ESTUDILLO VALDERRAMA MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JIANG SHAOYI;;SINCLAIR ANDREW;;O'KELLY MARY ELIZABETH;;BAI TAO;;JAIN PRIYESH</t>
+  </si>
+  <si>
+    <t>ABDI REZA</t>
+  </si>
+  <si>
+    <t>BENJA-ATHON ANUTHEP;;BENJA-ATHON SIRIKIT</t>
+  </si>
+  <si>
+    <t>CHERNORUTSKAYA EKATERINA IGOREVNA</t>
+  </si>
+  <si>
+    <t>BHATTACHARYYA NEHA;;SINGH SOUMENDRA SINGH;;MUKHERJEE DIPANJAN;;NABI GULAM;;MALLICK ASIM KUMAR;;PAL SAMIR KUMAR</t>
+  </si>
+  <si>
+    <t>BAIROV VLADIMIR GIREEVICH;;SUKHOTSKAYA ANNA ANDREEVNA;;GANIEV SHOKHRAMAZON SULTONOVICH;;OVADYUK NADEZHDA VASILEVNA</t>
+  </si>
+  <si>
+    <t>ROBERTSON JOHN L;;SENGER RYAN</t>
+  </si>
+  <si>
+    <t>COLBY BRANDON;;SLATER BETHANY;;COLBY MELVYN;;COLBY BRYON</t>
+  </si>
+  <si>
+    <t>COLBY BRANDON;;NORMAN ANDREW;;SLATER BETHANY;;COLBY MELVYN;;COLBY BRYON</t>
+  </si>
+  <si>
+    <t>BERESTETSKIJ ILYA EVGENEVICH;;MAKARYAN ALBERT ALBERTOVICH;;BORZUNOV IGOR VIKTOROVICH;;VAKHLOV SERGEJ GENNADEVICH;;KUBLANOV VLADIMIR SEMENOVICH</t>
+  </si>
+  <si>
+    <t>KAPRIN ANDREJ DMITRIEVICH;;APOLIKHIN OLEG IVANOVICH;;ALEKSEEV BORIS YAKOVLEVICH;;ROSHCHIN DMITRIJ ALEKSANDROVICH;;MERINOV DMITRIJ STANISLAVOVICH;;FILONENKO ELENA VYACHESLAVOVNA;;PEREPECHIN DMITRIJ VLADIMIROVICH;;GURBANOV SHAMIL SHUKUROVICH;;KACHMAZOV ALEKSANDR ALEKSANDROVICH</t>
+  </si>
+  <si>
+    <t>PECAN ROBERT GRGORY;;PECAN GEOFFREY ROBERT</t>
+  </si>
+  <si>
+    <t>GORDETSOV ALEKSANDR SERGEEVICH;;KRASNIKOVA OLGA VLADIMIROVNA;;BOYARINOVA LARISA VALENTINOVNA;;STRELTSOVA OLGA SERGEEVNA;;POCHTIN DMITRIJ PETROVICH</t>
+  </si>
+  <si>
+    <t>JIANG SHAOYI;;BAI TAO;;SUBRAMANIAN HARIHARA;;SINCLAIR ANDREW WILLIAM;;ELLA-MENYE JENE-RENE;;JAIN PRIYESH</t>
+  </si>
+  <si>
+    <t>MOROZOV SERGEJ LEONIDOVICH;;DLIN VLADIMIR VIKTOROVICH;;VOZDVIZHENSKAYA EKATERINA SERGEEVNA;;YUREVA ELEONORA ALEKSANDROVNA;;KUSHNAREVA MARIYA VASILEVNA</t>
+  </si>
+  <si>
+    <t>ANCONA ANDREA;;CAUDA VALENTINA ALICE;;MANTI ERIKA</t>
+  </si>
+  <si>
+    <t>RYTIK ANDREJ PETROVICH;;VERBITSKIJ SEMEN MIKHAJLOVICH;;KUTIKOVA OKSANA YUREVNA</t>
+  </si>
+  <si>
+    <t>FORFORI FRANCESCO;;BROGI ETRUSCA;;BIGNAMI ELENA</t>
+  </si>
+  <si>
+    <t>BESSE JEROME;;BESSE LAURENCE;;ALPHONSE MYRIAM</t>
+  </si>
+  <si>
+    <t>AVERCHENKO MARGARITA VIKTOROVNA;;KOVTUN OL GA PETROVNA;;KOMAROVA SVETLANA JUR EVNA;;PANKRATOVA IRINA BORISOVNA;;OSNOVIN PAVEL LEONIDOVICH</t>
+  </si>
+  <si>
+    <t>KHVOROSTOV IGOR NIKOLAEVICH;;SMIRNOV IVAN EVGEN EVICH;;ZORKIN SERGEJ NIKOLAEVICH;;DVORJAKOVSKIJ IGOR VJACHESLAVO;;SKUTINA LARISA EVGEN EVNA;;BELOVA NATAL JA REMOVNA</t>
+  </si>
+  <si>
+    <t>MCGUIRE HEATHER A;;MARKUS MICHAEL J;;KIONGA-KAMAU PETER M;;SMITH BRIAN N</t>
+  </si>
+  <si>
+    <t>ROSEN DANIEL J;;MARX THOMAS</t>
+  </si>
+  <si>
+    <t>BESSE JEROME;;BESSE LAURENCE;;POURNIN JULIEN</t>
+  </si>
+  <si>
+    <t>AGAPOV E G;;LUCHANINOVA V N;;NI A N;;POPOVA V V;;SYCHEVA EH V</t>
+  </si>
+  <si>
+    <t>BERNIC JANA;;CEBAN EMIL;;CIUNTU ANGELA;;ANDRONACHE LILIA;;ROLLER VICTOR;;REVENCO ADRIAN</t>
+  </si>
+  <si>
+    <t>Мигаль Людмила Якимівна;;Мигаль Людмила Якимовна;;Нікуліна Галина Григорівна;;Никулина Галина Григорьевна;;Баран Євген Якович;;Баран Евгений Яковлевич;;Кіндій Тетяна Вікторівна;;Киндий Татьяна Викторовна;;Баран Євген Євгенович;;Баран Евгений Евгеньевич</t>
+  </si>
+  <si>
+    <t>MYHAL LIUDMYLA YAKYMIVNA;;BAHDASAROVA INHRETTA VARTANIVNA;;DASCHENKO OKSANA OLEKSANDRIVNA;;KOROL LESIA VIKTORIVNA;;LAVRENCHUK OLHA VASYLIVNA;;FOMINA SVITLANA PETRIVNA</t>
+  </si>
+  <si>
+    <t>KOSHKIN S V;;ZONOV O A;;ZONOVA JU A</t>
+  </si>
+  <si>
+    <t>MCCLAIN JAMES B;;TAYLOR CHARLES DOUGLAS;;CARLYLE WENDA C</t>
+  </si>
+  <si>
+    <t>GALKIN E V</t>
+  </si>
+  <si>
+    <t>KALUHIN VADYM ONYSYMOVYCH;;HARAZDIUK IVAN VASYLIIOVYCH;;ZUB LILIYA OLEKSIIVNA;;MALIUH LARYSA SAMOILIVNA;;IATSKIV MARYNA VOLODYMYRIVNA</t>
+  </si>
+  <si>
+    <t>KOLESNYK MYKOLA OLEKSIIOVYCH;;KOROL LESIA VIKTORIVNA;;MYHAL LIUDMYLA YAKYMIVNA;;STEPANOVA NATALIA MYKHAILIVNA;;ROMANENKO OKSANA ANTONIVNA</t>
+  </si>
+  <si>
+    <t>Леонов Василь Васильович;;Леонов Василий Васильевич;;Козін Юрій Іванович;;Козин Юрий Иванович</t>
+  </si>
+  <si>
+    <t>HAIDER MUHAMMAD RIZWAN</t>
+  </si>
+  <si>
+    <t>HEATHER A MCGUIRE;;MICHAEL J MARKUS;;PETER M KIONGA-KAMAU;;BRIAN N SMITH</t>
+  </si>
+  <si>
+    <t>MAKIEIEVA NATALIIA IVANIVNA;;SENATOROVA HANNA SERHIIVNA;;DRYL INNA SERHIIVNA;;HONCHAR MARHARYTA OLEKSANDRIVNA</t>
+  </si>
+  <si>
+    <t>STEPANOVA NATALIIA MYKHAILIVNA;;MYHAL LIUDMYLA YAKYMIVNA;;KOROL LIESIA VIKTORIVNA</t>
+  </si>
+  <si>
+    <t>AL-SHUKRI S KH;;GORBACHEV A G;;KUZ MIN I V</t>
+  </si>
+  <si>
+    <t>ZUBARENKO OLEKSANDR VSEVOLODOVYCH;;STOEVA TETIANA LEONIDIVNA;;HODLEVSKA TAMARA LEONIDIVNA</t>
+  </si>
+  <si>
+    <t>HARAZDIUK OLEKSANDR IVANOVYCH;;KALUHIN VADYM ONYSYMOVYCH;;SHEVCHENKO BORYS IVANOVYCH;;HARAZDIUK IVAN VASYLIOVYCH</t>
+  </si>
+  <si>
+    <t>Barot et al. Prodrug Strategies. Ocular Drug Delivery Med. Chem. 8(4):753-768 (2012).;;Co-Pending U.S. Appl. No. 18/369,737, inventor Horn; Gerald, filed on Sep. 18, 2023.;;Krise et al. A novel prodrug approach for tertiary amines. 2. Physicochemical and in vitro enzymatic evaluation of selected N-phosphonooxymethyl prodrugs. J Pham Sci 88(9):922-927 (1999).;;Mäntylä et al. Design, synthesis and in vitro evaluation of novel water-soluble prodrugs of buparvaquone. Eur J Pharm Sci 23(2):151-158 (2004).;;Pramanik et al. A new route to cevimeline. Tetrahedron Letters 54(24):3043-3045 (2013).;;PubChem CID-22416839, Dec. 5, 2007.;;U.S. Appl. No. 17/988,366 Office Action dated Jan. 8, 2024.;;U.S. Appl. No. 18/239,072 Office Action dated Nov. 21, 2023.;;PCT/US2024/024819 International Search Report and Written Opinion dated Jul. 15, 2024.;;Akorn Incorporated MSDS: Tropicacyl (R); Rev. 11-11 (date unknown).;;Berge et al. Pharmaceutical Salts. Journal of Pharmaceutical Sciences 66(1):1-19 (Jan. 1977).;;Bijsluiter: Glaucocare. Available at https://consumed.nl/bijsluiters/glaucocare. Machine Translation Provided.;;CAS printout for Mashkovskii, The Relation Between the Chemical Structure and Pharmacological Activity of Some Esters of 3-Hydroxyquinuclidine (Quinuclidine-3-ol), Proc. Intern. Pharmacol., 7:359-366 (1961).;;Chung et al., The effect of dioptric blur on reading performance. Vision Res47(12):1584-94 (2007).;;Cowan et al., Clinical evaluation of a new mydriatic-mydrilate. Br J Ophthalmol 46(12):730-6 (1962).;;Davidson., General medicine and visual side effects. Br Med J 1(6166):821 (1979).;;Drance et al., Dose response of human intraocular pressure to aceclidine. Arch Ophthalmol 88(4):394-6 (1972).;;Edwards., Behaviour of the fellow eye in acute angle-closure glaucoma. Br J Ophthalmol 66(9):576-9 (1982).;;Edwards et al., Effect of brimonidine tartrate 0.15% on night-vision difficulty and contrast testing after refrActive surgery, J Cataract Refract Surg. 34(9):1538-41 (2008).;;Ehlert et al. The interaction of the enantiomers of aceclidine with subtypes of the muscarinic receptor. J Pharmacol Exp Ther 279(3):1335-1344 (1996).;;Fechner et al., Accomodative effects of aceclidine in the treatment of glaucoma. Amer J Ophth. 79 (1):104-106 (1975).;;Francois et al. Ultrasonographic study of the effect of different miotics on the eye components. Ophthalmologica 175(6):328-338 (1977).;;Fricke et al. Global Prevalence of Presbyopia and Vision Impairment from Uncorrected Presbyopia: Systematic Review, Meta-analysis, and Modelling. Ophthalmology 125(10):1492-1499 (2018).;;Gardiner., ABC of Ophthalmology: accidents and first aid. Br Med J 2(6148):1347-50 (1978).;;Gardiner., ABC of Ophthalmology: Methods of examination. Br Med J 2(6152):1622-6 (1978).;;Glaucadrine, poudre et solvant pour collyre en solution, boite de 1 acon de lyophilisat + acon le solvant de 10 ml GI. Available at Http://www.doctissimo.fr/medicament-GLAUCADRINE.htm Machine Translation Provided.;;Glaunorm toma all'Indice farmaci. Available at http://www.anibaldi.eu/farmaci/schedetecniche/GLAUNORM.html. (last updated Dec. 15, 2012) Machine Translation Provided.;;Grünberger et al., The pupillary response test as a method to differentiate various types of dementia. Neuropsychiatr 23(1):52-57 (2009).;;Hoyng et al., The combination of guanethidine 3% and adrenaline 0.5% in 1 eyedrop (GA) in glaucoma treatment. Br J Ophthalmol 63(1):56-62 (1979).;;Ishikawa et al. Selectivity of muscarinic agonists including (+/−)-aceclidine and antimuscarinics on the human intraocular muscles. J Ocul Pharmacol Ther 14(4):363-373 (1998).;;Josefa Valcarcel, Glaucostat(R) 2% colirio. Machine Translation Provided.;;Kaufman et al. Presbyopia and Glaucoma: Two Diseases, One Pathophysiology? The 2017 Friedenwald Lecture. Invest Ophthalmol Vis Sci 60(5):1801-1812 (2019).;;Kibbe. Handbook of Pharmaceutical Excipients. 3rd Edition, American Pharmaceutical Association and Pharmaceutical Press (pp. 416-419) (2000).;;Latanoprost Label (2006).;;Lubrizol Pharmaceutical Bulletin 21 (Lubrizol Advanced Materials, Inc.) May 31, 2011.;;Mayama et al. Myopia and advanced-stage open-angle glaucoma. Ophthalmology 109(11):2072-2077 (2002).;;Mayo Clinic: Tropicamide (Opthalmic Route), 2015, http://www.mayoclinic.org/drugs-supplements/tropicamide-ophthalmic-route/description/drg-20066481.;;Mohan et al., Optimal dosage of cyclopentolate 1% for cycloplegic refraction in hypermetropes with brown irides. Indian J Ophthalmol 59(6):514-6 (2011).;;Muller and R.P. Dessing (Eds.) 4th Edition, European Drug Index, European Society of Clinical Pharmacy, Jeutscher Apotheker Verlag Suttgart (p. 550) (1997).;;Nayak et al., A comparison of cycloplegic and manifest refractions on the NR-1000F (an objective Auto Refractometer). Br J Ophthalmol 71(1):73-5 (1987).;;Park., The comparison of mydriatic effect between two drugs of different mechanism. Korean J Ophthalmol 23(1):40-2 (2009).;;PCT/US2014/052256 International Search Report and Written Opinion dated Dec. 18, 2014.;;PCT/US2016/036687 International Search Report and Written Opinion dated Sep. 9, 2016.;;PCT/US2016/036692 International Search Report and Written Opinion dated Sep. 22, 2016.;;PCT/US2016/036694 International Search Report and Written Opinion dated Oct. 26, 2016.;;PCT/US2017/021244 International Search Report and Written Opinion dated May 22, 2017.;;PCT/US2019/055116 International Search Report and Written Opinion dated Dec. 19, 2019.;;PCT/US2019/063923 International Invitation to Pay Additional Fees dated Feb. 3, 2020.;;PCT/US2019/063923 International Search Report and Written Opinion dated Apr. 23, 2020.;;PCT/US2021/029536 International Search Report and Written Opinion dated Aug. 9, 2021.;;PCT/US2022/026435 International Invitation to Pay Additional Fees dated Jul. 5, 2022.;;PCT/US2022/026435 International Search Report and Written Opinion dated Sep. 28, 2022.;;PCT/US2022/050028 International Search Report and Written Opinion dated Mar. 2, 2023.;;Primožič et al. Influence of the acyl moiety on the hydrolysis of quinuclidinium esters catalyzed by butyrylcholinesterase. Croatica Chemica Acta 84(2):245-249 (2011).;;Prospectus/Technical Sheet for Glaucostat Josefa Valcarecel Glaucostat® 2% colirio (2000).;;PubChem 233021624 deposited on Feb. 12, 2015 (Feb. 12, 2015).;;PubChem 427198483 deposited Aug. 13, 2020 (Aug. 13, 2020).;;PubChem-CID-22416839, Create Date: Dec. 5, 2007.;;Romano., Double-blind cross-over comparison of aceclidine and pilocarpine in open-angle glaucoma. Br J Ophthalmol 54(8):510-21 (1970).;;Smith et al., Subsensitivity to cholinoceptor stimulation of the human iris sphincter in situ following acute and chronic administration of cholinomimetic miotic drugs. Br J Pharmacol 69(3):513-8 (1980).;;Stella. Prodrugs: Some Thoughts and Current Issues. J Pharm Sci 99(12):4755-4765 (2010).;;Tataru et al., Antiglaucoma pharmacotherapy. J Med Life 5(3):247-51 (2012).;;Trinavarat et al., Effective pupil dilatation with a mixture of 0.75% tropicamide and 2.5% phenylephrine: A randomized controlled trial. Indian J Ophthalmol 57(5):351-4 (2009).;;U.S. Appl. No. 14/223,639 Office Action dated Jan. 5, 2015.;;U.S. Appl. No. 14/223,639 Office Action dated Sep. 30, 2014.;;U.S. Appl. No. 14/742,903 Office Action dated Dec. 2, 2015.;;U.S. Appl. No. 14/742,903 Office Action dated Jul. 17, 2015.;;U.S. Appl. No. 14/742,921 Office Action dated Jul. 15, 2015.;;U.S. Appl. No. 14/860,770 Office Action dated Dec. 13, 2016.;;U.S. Appl. No. 14/860,777 Office Action dated Mar. 9, 2017.;;U.S. Appl. No. 15/073,089 Office Action dated May 8, 2017.;;U.S. Appl. No. 15/073,089 Office Action dated Nov. 30, 2016.;;U.S. Appl. No. 15/073,139 Office Action dated Dec. 1, 2016.;;U.S. Appl. No. 15/235,431 Office Action dated Mar. 9, 2018.;;U.S. Appl. No. 15/864,703 Office Action dated Apr. 8, 2019.;;U.S. Appl. No. 15/864,703 Office Action dated Feb. 11, 2019.;;U.S. Appl. No. 15/864,703 Office Action dated Mar. 26, 2018.;;U.S. Appl. No. 15/956,931 Office Action dated Oct. 2, 2018.;;U.S. Appl. No. 15/956,936 Office Action dated Feb. 11, 2019.;;U.S. Appl. No. 15/956,936 Office Action dated Sep. 28, 2018.;;U.S. Appl. No. 16/106,730 Office Action dated Jun. 11, 2021.;;U.S. Appl. No. 16/106,730 Office Action dated Jun. 2, 2020.;;U.S. Appl. No. 16/106,730 Office Action dated Oct. 19, 2020.;;U.S. Appl. No. 16/156,276 Office Action dated Jun. 26, 2020.;;U.S. Appl. No. 16/156,276 Office Action dated Oct. 22, 2020.;;U.S. Appl. No. 16/700,088 Office Action dated May 28, 2021.;;U.S. Appl. No. 16/700,088 Office Action dated Nov. 2, 2021.;;U.S. Appl. No. 16/747,070 Office Action dated Jun. 25, 2021.;;U.S. Appl. No. 16/747,070 Office Action dated Oct. 30, 2020.;;U.S. Appl. No. 16/796,364 Office Action dated Apr. 30, 2021.;;U.S. Appl. No. 16/796,364 Office Action dated Dec. 30, 2020.;;U.S. Appl. No. 16/796,364 Office Action dated Jun. 11, 2021.;;U.S. Appl. No. 16/881,570 Office Action dated Oct. 7, 2020.;;U.S. Appl. No. 17/069,155 Office Action dated Aug. 19, 2021.;;U.S. Appl. No. 17/242,398 Office Action dated Apr. 27, 2023.;;U.S. Appl. No. 17/242,398 Office Action dated Oct. 14, 2022.;;U.S. Appl. No. 17/502,066 Office Action dated Jun. 22, 2023.;;U.S. Appl. No. 17/502,066 Office Action dated Mar. 31, 2022.;;U.S. Appl. No. 17/502,066 Office Action dated Nov. 14, 2022.;;U.S. Appl. No. 17/552,622 Office Action dated Feb. 9, 2023.;;U.S. Appl. No. 17/552,654 Office Action dated Apr. 20, 2022.;;U.S. Appl. No. 17/552,654 Office Action dated Dec. 2, 2022.;;U.S. Appl. No. 17/988,366 Office Action dated Jul. 19, 2023.;;Varma et al. Concentration of Latanoprost Ophthalmic Solution after 4 to 6 Weeks' Use in an Eye Clinic Setting. Invest Ophthalmol Vis Sci. 47(1):222-225 (2006).;;Ward et al., 1,2,5-Thiadiazole analogues of aceclidine as potent ml muscarinic agonists. J Med Chem 41(3):379-392 (1988).;;Wood et al., Pupil dilatation does affect some aspects of daytime driving performance. Br J Ophthalmol (11):1387-90 (2003).;;Zhang et al. ReActive impurities in large and small molecule pharmaceutical excipients—A review. TrAC Trends in Analytical Chemistry 101:34-42 (2018).;;Aceclidine (Hydrochloride) Item No. 1790. Product Information. Cayman Chemical Company (1 pg) (Dec. 2, 2022).;;Charman, W. Neil. Pinholes and presbyopia: solution or sideshow? Ophthalmic Physiol Opt 39(1):1-10 (2019).;;Co-Pending U.S. Appl. No. 18/763,722, inventors Horn; Gerald et al., filed on Jul. 3, 2024.;;Co-Pending U.S. Appl. No. 18/765,066, inventors Horn; Gerald et al., filed on Jul. 5, 2024.;;Co-Pending U.S. Appl. No. 18/765,156, inventors Horn; Gerald et al., filed on Jul. 5, 2024.;;Co-Pending U.S. Appl. No. 18/766,429, inventors Horn; Gerald et al., filed on Jul. 8, 2024.;;Drug information Q&amp;A “Q29. What is the expiry date of drugs and how to store them properly?”, Japan Pharmaceutical Manufacturers Association [online], Mar. 2014, [retrieved on Mar. 25, 2024], Retrieved from the Internet: URL: https://www.jpma.or.jp/about_medicine/guide/med_qa/q29.html (English translation provided).;;Jiao, Jim. Polyoxyethylated nonionic surfactants and their applications in topical ocular drug delivery. Advanced Drug Delivery Reviewed 60:1663-1673 (2008).;;Randazzo et al., Pharmacological management of night vision disturbances after refrActive surgery Results of a randomized clinical trial. J Cataract Refract Surg 31(9):1764-1772 (2005).;;Santvliet, et al. Determinants of Eye Drop Size. Survey of Ophthamology 49(2):197-213 (2004).;;U.S. Appl. No. 17/502,066 Office Action dated Mar. 27, 2024.;;U.S. Appl. No. 17/730,376 Office Action dated Jul. 17, 2024.;;U.S. Appl. No. 17/988,366 Office Action dated Apr. 29, 2024.;;U.S. Appl. No. 18/239,045 Office Action dated Jan. 26, 2024.;;U.S. Appl. No. 18/239,072 Office Action dated Mar. 27, 2024.;;U.S. Appl. No. 18/241,733 Office Action dated Jan. 30, 2024.;;U.S. Appl. No. 18/369,737 Office Action dated Jun. 6, 2024.;;U.S. Appl. No. 18/465,918 Office Action dated Feb. 1, 2024.;;Xu, Renfeng et al. Effect of Target Luminance on Optimum Pupil Diameter for Presbyopic Eyes. Optom Vis Sci 93(11):1409-1419 (2016).</t>
+  </si>
+  <si>
+    <t>A drug delivery composition including a lipophilic agent or a biologic agent and a polymer wherein the lipophilic agent exhibits sustained release and wherein there is less than 35% agent release within the first hour of elution. A drug delivery composition including a lipophilic agent or a biologic agent and a polymer wherein the elution profile is substantially linear, and wherein there is less than 35% agent release within the first hour of elution. The lipophilic agent may be crystalline and the biologic agent may be in Active form.</t>
+  </si>
+  <si>
+    <t>The present invention relates to a solid, orodispersible and/or dispersible composition comprising (a) from 0.1 to 59% by weight of at least one Active substance with particle size no exceeding 50 μm; (b) from 40 to 99% by weight of at least one diluent without known effect, non water-soluble; (c) from 0.1 to 15% by weight of at least one disintegrating agent; and (d) from 0.05 to 10% by weight at least of one sweetening agent with particle size not exceeding 50 μm, percentages by weight being expressed compared to the total weight of the aforementioned composition. The present invention also relates to the use of said composition as a drug, a food supplement or in cosmetics and a method of preparation of an orodispersible and/or dispersible compound implementing said composition.</t>
+  </si>
+  <si>
+    <t>The present invention relates to a solid, orodispersible and/or dispersible composition comprising (a) from 0.1 to 59% by weight of at least one Active substance with particle size not exceeding 50 mum; (b) from 40 to 99% by weight of at least one diluent without known effect, non water-soluble; (c) from 0.1 to 15% by weight of at least one disintegrating agent; and (d) from 0.05 to 10% by weight at least of one sweetening agent with particle size not exceeding 50 mum, percentages by weight being expressed compared to the total weight of the aforementioned composition. The present invention also relates to the use of said composition as a drug, a food supplement or in cosmetics and a method of preparation of an orodispersible and/or dispersible compound implementing said composition.</t>
+  </si>
+  <si>
+    <t>This invention relates to an impregnated powder for increasing the bioavailabilty and/or the solubility of at least one Active principle comprising a solid, inert support in a particle form impregnated by a liquid medium comprising a hydrophobic phase and optionally a hydrophilic phase, at least one surfactant and at least one Active principle dissolved in at least one of said phases, wherein said Active principle(s) is(are) also present in at least one of said phases in the form of a suspension. Such an impregnated powder is used as a base for various preparations in the pharmaceutical, parapharmaceutical and cosmetic field, in the food complement field and in the food processing industry.</t>
+  </si>
+  <si>
+    <t>The present invention relates to the use of a powder comprising at least one Active substance, at least one surfactant, at least one wetting agent and at least one diluent, for preparing a pharmaceutical or nutraceutical composition, this composition allowing rapid and immediate release of the Active substance.</t>
+  </si>
+  <si>
+    <t>The invention refers to an innovative diagnostics protocol by using a cooperative methodology between multidisciplinary medical teams that participate simultaneously at an evaluation and an analysis of the case, said team which exchanges medical opinions and works together proActively and in real-time in order to establish the diagnostics and a complete treatment scheme. The interest area of the present invention is the rapid and complete diagnostics of a patient using a multidisciplinary team of doctors that simultaneously work and evaluate the patient in real time by using remote continuous monitoring equipment of the vital functions at the patient's home, after which the relevant data are transmitted and analyzed continuously in a decision center. The necessary technical platform for implementing the complete diagnostics method is composed of a dispatch system (1) which can manage a number of simultaneous calls, where patients call and get in touch with the coordinating medical doctor, said doctor who retrieves patient information and decides which medical domains will be involved in the panel following the method for choosing the medical specialties, then he or she nominates doctors that will take part in the panel by selecting them from a specialists database (2), said specialists who communicate between them and with the patient using a telemedicine system (3) which is composed of an audio-video bidirectional communication patient terminal (4) which is brought by the medical doctor that examines the patient at his or hers location, audio-video bidirectional specialist communication systems (5) which specialists use and a software application that manages the telemedicine system (6), said application which allows simultaneous bidirectional audio-video communication between medical specialists, the coordinating doctor, the doctor that performs the tests and the examination, said application which runs on a specialized server (7).</t>
+  </si>
+  <si>
+    <t>The present invention relates to a film-forming powder comprising at least one Active substance, at least one bioadhesive agent, and optionally surfactants, wetting agents, plasticizers, binders, retardants, penetration promoters and bioerodible diluents.</t>
+  </si>
+  <si>
+    <t>INTERActive ALGORITHM FOR DETERMINING NEGOTIATED HEALTHCARE PRICE RATES</t>
+  </si>
+  <si>
+    <t>Patented</t>
+  </si>
+  <si>
+    <t>"Medical Ultrasonography - Wikipedia, the free encyclopedia. February 27, 2008. Retrieved from the Internet: URL.</t>
+  </si>
+  <si>
+    <t>"A Model of Network Capitalism: Basic Ideas and Post-Soviet Evidence", Journal of Economic Issues, Mar. 2004, vol. 38, No. 1, pp. 85-111.;;Bardon, Debbie, "Online social Networking for Business; An Interview with Konstantin Guericke Marketing VP, LinkedIn Interview", Online, Nov. 1, 2004, No. 6, vol. 28, p. 25.;;Dickie, Jim, Is Social Networking an Overhyped Fad or a Useful Tool? When Put to the Test, This Sales and Marketing Application Delivers: Reality Check, CRM Magazine, Feb. 1, 2005, No. 2, Vol. 9, p. 20.;;Dvorak, John C., "The New Networking Crock; This is Plain, Old-Fashioned, Hopeless, Silicon Valley Utopianism at Work. Grab Hold of Your Wallets and Hold on for Dear Lifel", PC Magazine.com, Feb. 11, 2004.;;Fitzgerald, Michael, "Internet Working", Technology Review, Apr. 1, 2004, vol. 107, No. 3, p. 44.;;Frauenfelder, Mark, "Sir Tim Berners-Lee He Created the Web. Now He's Working on Internet 2.0", Technology Review, Oct. 2004, pp. 40-45.;;Gathier, Chris, "West Coast 'Social Networking' Web Sites Attract Users, Investors", Boston Globe, Dec. 7, 2003.;;Greenbaum, Joshua, "Cirlce of Friends: Social Networking Software Can Help Enterprises Take Advantage of Existing Relationships, Both Internally and Externally", Intelligent Enterprise, Apr. 3, 2004, p. 36.;;Harney, John, "Social Networks in Sales: Social Network Software Tells Salespeople Who in Their Organization Knows Whom Within a Company They're Trying to Sell to and Then They Can Use the Intermediary to Broker a Sale", KM World, Jun. 1, 2004, No. 6, vol. 13, p. 16.;;Herman, Jim, "The New Science of Networks", Business Communications Review, Jun. 1, 2003, No. 6, vol. 33, p. 22.;;Hicks, Matt, "Spoke Revs Hosted Enterprise Social Networking Application: The Startup Plans to Offer Spoke Workgroups in the Spring for Smaller Sales Teams That Want to Tap into Social Networking Without Deploying Software", eWeek.com, Mar. 4, 2004.;;Hicks, Matt, "Social Networking Stretches its Reach; Two Smaller Companies Move to Integrate the Concept of Mapping Social Connections with Mobile-Phone Text Messaging and With Web Conferencing", eWeek.com, Apr. 8, 2004.;;Lee, Ellen, "New 'Social Networking' Sites Help Land Jobs in San Francisco Bay Area", Contra Costa Times, Sep. 17, 2004.;;Padgett, Lauree, "Networking, Migrating and Aggravating: In Other Words, Discusses Migrating Library Systems, Malware Tools, Social Networking", Information Today, Mar. 1, 2004, No. 3, vol. 21, Page 40.;;Pankhurst, Steve, "Social Networks Run on Trust, As Do We At Friends Reunited", Revolution, Feb. 9, 2004, p. 13.;;Schofield, Jack, "Software to Help You Network", Computer Weekly, Mar. 16, 2004, p. 32.;;Solheim, Shelley, "Social-Networking Vendors Set Their Sights on the Enterprise", eWeek.com, Mar. 19, 2004.;;Solheim, Shelley, "Let's Keep in Touch: Social Network Tools Take Air at Enterprise Sales", eWeek, News &amp; Analysis, Mar. 29, 2004, p. 31.;;Solomon, Marc, "Searching Becomes Conversing: Social Networking Application for Sales, Recruiting, etc.", Searcher, Mar. 1, 2004, No. 3, vol. 12, p. 16.;;Smith, Philip, "Marketing Promise of Social Sites", Revolution, Apr. 21, 2004, p. 17.;;Topper, Elisa F., "Working Knowledge: Putting Networks to Work: Professional Development", American Libraries, Dec. 1, 2003, No. 11, vol. 34, p. 88.;;Whaley, Charles, "Six Degrees of Separation Takes on an Electronic Spin: Social Networking Via the Web is All the Rage, and Venture Capitalists of Throwing Handfuls of Money at Startups", Computing Canada, Mar. 26, 2004, No. 4, vol. 30, p. 13.;;International Search Report for WO 2006/036165 (Application No. PCT/US04/38064); Mar. 9, 2006.;;International Search Report for WO 2006/036187 (Application No. PCT/US05/06617); May 8, 2007.;;International Search Report for WO2006/041425 (Application No. PCT/US04/30259); May 30, 2006.;;International Search Report for WO2006/055555 (Application No. PCT/US05/41349); Jun. 1, 2006.;;International Search Report for WO2006036186 (Application No. PCT/US2005/005847); Apr. 21, 2006.;;International Search Report for WO2007005463 (Application No. PCT/US06/25166); Dec. 14, 2007.;;International Search Report for WO2006/036216 (Application No. PCT/US05/15952); Aug. 25, 2006.;;International Search Report for WO2007016252 (Application No. PCT/US06/29210); Jul. 13, 2007 Applicant S.M.A.R.T. Link Medical, Inc.;;Written Opinion for WO 2006/036187 (Application No. PCT/US05/06617); May 8, 2007.;;Written Opinion for WO2006/036165 (Application No. PCT/US04/38064); Mar. 9, 2006.;;Written Opinion for WO2006/036216 (Application No. PCT/US05/15952); Aug. 25, 2006.;;Written Opinion for WO2006/041425 (Application No. PCT/US04/30259); May 30, 2006.;;Written Opinion for WO2006/055555 (Application No. PCT/US05/41349; Jun. 1, 2006.;;Written Opinion for WO2007005463 (Application No. PCT/US06/25166); Dec. 14, 2007.;;Written Opinion for WO2007016252 (Application No. PCT/US06/29210); Jul. 13, 2007.;;Google search of "totally random keywords", May 14, 2009.;;Markus, Michael J., "Collection of Linked Databases"; Final Office Action issued in U.S. Appl. No. 11/686,421.;;Markus, Michael J., "Collection of Linked Databases"; Office Action issued in U.S. Appl. No. 11/686,421.;;Markus, Michael J., "Collection of Linked Databases"; Office Action issued in U.S. Appl. No. 11/686,416.;;Markus, Michael J., "Collections of Linked Databases"; Final Office Action issued in U.S. Appl. No. 11/686,416.;;Markus, Michael J., "Collections of Linked Databases"; Non-Final Office Action issued in U.S. Appl. No. 11/686,409.;;Markus, Michael J., "Collections of Linked Databases"; Final Office Action issued in U.S. Appl. No. 11/686,409.;;Markus, Michael J., "Collections of Linked Databases"; Office Action issued in U.S. Appl. No. 11/686,429.;;Markus, Michael J., "Collections of Linked Databases",; Final Office Action issued in U.S. Appl. No. 11/686,429.;;Markus, Michael J., "Collections of Linked Databases and Systems and Methods for Communicating About Updates Thereto"; Non-Final Office Action issued in U.S. Appl. No. 11/989,039.;;Markus, Michael J., "Social Network Analysis"; Final Office Action issued in U.S. Appl. No. 11/686,401.</t>
+  </si>
+  <si>
+    <t>LI Y X ET AL: "Spontaneous uroperitoneum and elevated Ca-125", EUROPEAN JOURNAL OF INTERNAL MEDICINE, ELSEVIER, AMSTERDAM, NL, vol. 19, no. 7, 1 November 2008 (2008-11-01), pages e47 - e48, XP025669576, ISSN: 0953-6205, [retrieved on 20080401], DOI: 10.1016/J.EJIM.2008.02.001</t>
+  </si>
+  <si>
+    <t>ШАРКОВ С. М. и др. "Внутрипузырная электростимуляция и магнитотерапия при хроническом пиелонефрите и цистите у детей с нарушениями уродинамики", "Урология", 2011 г., N 6, с 92 - 97.;;KROLL P. et all "Electrostimulation in treatment of neurogenic and non-neurogenicvoiding dysfunction", Wiad Lek. 1998;51 Suppl 3:92-7.;;Ishigooka M. et all Electricalpelvic floor stimulation in the management of urinary incontinence due to neuropathicoveractive bladder, Front Med Biol Eng. 1993;5(1):1-10.</t>
+  </si>
+  <si>
+    <t>Y. Ogawa et al. URINARY SATURATION AND RISK FACTORS FOR CALCIUM OXALATE STONE DISEASE BASED ON SPOT AND 24-HOUR URINE SPECIMENS / Frontiers in Bioscience 8, 2003, pages 167-176 [Найдено он-лайн в Интернете 31.01.2018 http://www.bioscience.org/2003/v8/a/1139/fulltext.htm].;;M. G. Penido et al. Urinary excretion of calcium, uric acid and citrate in healthy children and adolescents / Jornal de Pediatria, 2002, vol. 78, N2, pages 153-160 [Найдено он-лайн в Интернете 31.01.2018 http://www.jped.com.br/conteudo/02-78-02-153/ing.pdf].</t>
+  </si>
+  <si>
+    <t>See references of EP 3191016A4</t>
+  </si>
+  <si>
+    <t>KRAVDAL G. et al. Infrared spectroscopy is the gold standard for kidney stone analysis // Tidsskr Nor Legeforen, 2015, V.135, pp.313-314.;;POPESCU G.S. et al. The Use of Infrared Spectroscopy in the Investigation of Urolithiasis // Revista Romana de Medicina de Laborator, 2010, V.18, pp.67-77.;;GOLDFARB M.D. et al. Metabolic Evaluation of First-time and Recurrent Stone Formers // Urol Clin North Am., 2013, V.40, pp.13-20.</t>
+  </si>
+  <si>
+    <t>АКОПЯН Г.Н. и др. "Перкутанное удаление уротелиального рака верхних мочевых путей" // "Медицинский вестник Башкортостана", том 12, N3(69), 2017, стр.66-70.;;"Хлорин Е6" // помещено на сайт в Интернет:</t>
+  </si>
+  <si>
+    <t>ФЕДОРОВ А.А. и др. Комплексная физиобальнеотерапия с использованием минеральной воды "Обуховская-10" и диадинамических токов у больных нефролитиазом в период восстановительного лечения. Курортная медицина, 2015, N4, с.68-72.</t>
+  </si>
+  <si>
+    <t>Beaudet et al. (Am. J. Hum. Genet. 44:319-326, 1989);;Elston (Ann. Rev. Biophys. Bioeng., 1978, 7:253-86)</t>
+  </si>
+  <si>
+    <t>Fisher, A. K. (2018). Raman Chemometrics and Application to Enzyme Kinetics and Urinalysis [Doctoral dissertation, Virginia Tech]. Semantic Scholar. 142 p. &lt;URL: www.semanticscholar.org/paper/Raman-Chemometrics-and-Application-to-Enzyme-and-Fisher/0d9773853f5ece82993ea928e97ef212ae023941&gt; (Year: 2018);;Del Mistro et al., (2015). Analytical and Bioanalytical Chemistry, 407, 3271-3275. (Year: 2015);;Bispo et al., (2013). Journal of biomedical optics, 18(8), p.087004-087004. (Year: 2013);;Xu and Du, (2019, July 27-August 01). ISREA:A Novel Approach for Raman Spectrum Baseline Correction and Its Application on Real Data [abstract]. JSM 2019, Denver, CO. [Retrieved online 02 June 2023] &lt;URL: https://ww2.amstat.org/meetings/jsm/2019/onlineprogram/AbstractDetails.cfm?abstractid=304883&gt; (Year: 2019);;Fisher et al., (2018). The Rametrix™ LITE Toolbox v1.0 for MATLAB®. Journal of Raman Spectroscopy, 49(5), 885-896. (Year: 2018);;Liu et al., ((2015). Goldindec: a novel algorithm for Raman spectrum baseline correction. Applied spectroscopy, 69(7), 834-842);;Xu et al., (2021). ISREA: an efficient peak-preserving baseline correction algorithm for Raman spectra. Applied Spectroscopy, 75(1), 34-45;;Schena, F.P., 2011. Management of patients with chronic kidney disease. Internal and emergency medicine, 6, pp.77-83. (Year: 2011);;Bonifacio, A., Cervo, S. and Sergo, V., 2015. Label-free surface-enhanced Raman spectroscopy of biofluids: fundamental aspects and diagnostic applications. Analytical and bioanalytical chemistry, 407, pp.8265-8277. (Year: 2015);;Webster, A.C., Nagler, E.V., Morton, R.L. and Masson, P., 2017. Chronic kidney disease. The lancet, 389(10075), pp.1238-1252. (Year: 2017);;Van Rhijn, B.W., Van der Poel, H.G. and van Der Kwast, T.H., 2005. Urine markers for bladder cancer surveillance: a systematic review. European urology, 47(6), pp.736-748. (Year: 2005)</t>
+  </si>
+  <si>
+    <t>ЗОРКИН С.Н. и др. Диагностика и лечение обструктивных уропатий у детей. Детская хирургия. N6 (2012), стр.23-26.;;ГУРЕВИЧ А.И. Лучевая диагностика обструктивных уропатий у детей//Учебное пособие. Москва, 2013, стр.11-16.;;ОБУХОВ Н.С. и др. Пренатальная диагностика и постнатальная верификация обструктивных уропатий у детей первого года жизни. Вестник уральской медицинской академической науки, No 2, 2016, стр. 24-29.;;STEFOS T. et all. Routine obstetrical ultrasound at 18-22 weeks: our experience on 7236 fetuses // J. Matern. Fetal Med. 1999. V.8. No 2. P. 64-69.</t>
+  </si>
+  <si>
+    <t>Wells, Additivity of Mutational Effects in Proteins. Biochemistry. vol. 29, No. 37 pp. 8509-8517 (Sep. 1990).;;Wen et al., "Erythropoietin Structure-Function Relationships: High Degree of Sequence Homology Among Mammals," Blood82(5):1507-1516 (1993).;;Macleod et al., "Expression and Bioactivity of Recombinant Canine Erythropoietin, "Am. J. Vet. Res.59(9):1144-1148 (1998).;;Cowgill et al., "Use of Recombinant Human Erythropoietin for Management of Anemia in Dogs and Cats with Renal Failure," J. Am. Vet. Med. Assoc.212(4):521-528 (1998).;;Spivak, "Recombinant Human Erythropoietin and the Anemia of Cancer," Blood 84(4):997-1004 (1994).;;Randolph et al., "Comparison of the Biological Activity and Safety of Recombinant Canine Erythropoietin to Recombinant Human Erythropoietin in Normal Beagle Dogs," American College of Veterinary Internal Medicine, Official Abstract Form for Oral and Poster Presentations, 16thAnnual Veterinary Medical Forum (May 1998) (abstract).;;Randolph et al., "Comparison of Biological Activity and Safety of Recombinant Canine Erythropoietin with that of Recombinant Human Erythropoietin in Clinically Normal Dogs, " Am. J. Vet. Res.60(5):636-642 (1999).</t>
+  </si>
+  <si>
+    <t>ZHU SIMIAN, CORSETTI STELLA, WANG QIFAN, LI CHUNHUI, HUANG ZHIHONG, NABI GHULAM: "Optical sensory arrays for the detection of urinary bladder cancer‐related volatile organic compounds", JOURNAL OF BIOPHOTONICS, vol. 12, no. 10, 1 October 2019 (2019-10-01), DE , pages 1 - 10, XP093150575, ISSN: 1864-063X, DOI: 10.1002/jbio.201800165</t>
+  </si>
+  <si>
+    <t>Шмиткова Е.В. Оценка состояния уретеровезикального сегмента при обструктивных уропатиях у детей раннего возраста с помощью ультразвуковой доплерографии: автореф. дис. к.м.н. Москва. 2005: 22.;;Логиновских В. Особенности реакции почки человека на введение свободной и гель-связанной формы препаратов-аналогов антидиуретического гормона: автореф. дис. к.м.н. Москва. 2007: 25.;;Дыбунов А.Г. и др. Оценка мочеточнико-пузырного выброса у здоровых детей методом допплерографии // Ультразвуковая диагностика. 200; No1: 73-7.;;de Bessa J Jr. et al. Diagnostic accuracy of Onen's Alternative Grading System combined with Doppler evaluation of ureteral jets as an alternative in the diagnosis of obstructive hydronephrosis in children // PeerJ. 2018 May 18; 6: e4791.;;Jandaghi A.B. et al. Assessment of ureterovesical jet dynamics in obstructed ureter by urinary stone with color Doppler and duplex Doppler examinations // Urolithiasis. 2013 Apr; 41(2): 159-63.</t>
+  </si>
+  <si>
+    <t>MacLeod et al., "Expression and Bioactivity of Recombinant Canine Erythropoietin," Am J. Vet. Res. 59(9):1144-1148 (1998).;;Cowgill et el., "Use of Recombinant Human Erythropoietin for Management of Anemia in Dogs and Cats with Renal Failure," J. Am. Vet. Med. Assoc. 212(4):521-528 (1998).;;Spivak, "Recombinant Human Erythropoietin and the Anemia of Cancer," Blood 84(4):997-1004 (1994).;;Randolph et al., "Comparison of the Biological Activity and Safety of Recombinant Canine Erythropoietin to Recombinant Human Erythropoietin in Normal Beagle Dogs," American College of Veterinary Internal Medicine, Official Abstract Form for Oral and Poster Presentation, 16&lt;SUP&gt;th &lt;/SUP&gt;Annual Veterinary Medical Forum (May 1998) (abstract).;;Randolph et al., "Comaparison of the Biological Activity and Safety of Recombinant Canine Erythropoietin with that of Recombinant Human Erythropoietin in Clinically Normal Dogs," Am. J. Vet. Res. 60(5):636-642 (1999).;;Wen et al., "Erythropoietin Structure-Function Relationships: High Degree of Sequence Homology Among Mammals," Blood 82:1507-1516 (1993).</t>
+  </si>
+  <si>
+    <t>ZHOU ET AL.: "Kidney-targeted drug delivery systems.", ACTA PHARMACEUTICA SINICA B, vol. 4, no. 1, February 2014 (2014-02-01), pages 37 - 42, XP055506266, DOI: 10.1016/j.apsb.2013.12.005;;WANG ET AL.: "Peptide and antibody ligands for renal targeting: nanomedicine strategies for kidney disease", BIOMATER SCI, vol. 5, no. 8, 25 July 2017 (2017-07-25), pages 1450 - 1459, XP055507100, DOI: 10.1039/C7BM00271H;;KLASSEN ET AL.: "Light chains are a ligand for megalin.", J APPL PHYSIOL, vol. 98, no. 1, January 2005 (2005-01-01), pages 257 - 263, XP055931267</t>
+  </si>
+  <si>
+    <t>JIANG ET AL., BIOMATERIALS, vol. 35, 2014, pages 3926;;HEILSHORN ET AL., TISSUE ENGINEERING PART A, vol. 18, 2012, pages 806;;See also references of EP 3487537A4</t>
+  </si>
+  <si>
+    <t>MACLEOD J. N., ET AL.: "EXPRESSION AND BIOACTIVITY OF RECOMBINANT CANINE ERYTHROPOIETIN.", AMERICAN JOURNAL OF VETERINARY RESEARCH., AMERICAN VETERINARY MEDICINE ASSOCIATION, US, vol. 59., no. 09., 1 September 1998 (1998-09-01), US, pages 1144 - 1148., XP002921757, ISSN: 0002-9645;;WEN D., ET AL.: "ERYTHROPOIETIN STRUCTURE-FUNCTION RELATIONSHIP: HIGH DEGREE OF SEQUENCE HOMOLOGY AMONG MAMMALS.", BLOOD, AMERICAN SOCIETY OF HEMATOLOGY, US, vol. 82., no. 05., 1 September 1993 (1993-09-01), US, pages 1507 - 1516., XP002921758, ISSN: 0006-4971;;COWGILL L. D., ET AL.: "USE OF RECOMBINANT HUMAN ERYTHROPOIETIN FOR MANAGEMENT OF ANEMIA IN DOGS AND CATS WITH RENAL FAILURE.", JOURNAL OF THE AMERICAN VETERINARY MEDICAL ASSOCIATION, AMERICAN VETERINARY MEDICAL ASSOCIATION, US, vol. 212., no. 04., 15 February 1998 (1998-02-15), US, pages 521 - 528., XP002921760, ISSN: 0003-1488;;SPIVAK J. L.: "RECOMBINANT HUMAN ERYTHROPOIETIN AND THE ANEMIA OF CANCER.", BLOOD, AMERICAN SOCIETY OF HEMATOLOGY, US, vol. 84., no. 04., 15 August 1994 (1994-08-15), US, pages 997 - 1004., XP002921761, ISSN: 0006-4971;;See references of EP 1071795A4</t>
+  </si>
+  <si>
+    <t>Zhen Jiang, et al., "Trans-rectal Ultrasound-Coupled Near-Infrared Optical Tomography of the Prostate Part II: Experimental Demonstration", Optics Express, Oct. 27, 2008, pp. 17505-17520, vol. 16, NR. 22, Optical Society of America, US, XP002646498.;;J. Masood et al.: "Condom perforation during transrectal ultrasound guided (TRUS) prostate biopsies: a potential infection risk," International Urology and Nephrology, vol. 39, 2007, pp. 1121-1124.;;J. Boutet et al.: "Bimodal ultrasound and fluorescence approach for prostate cancer diagnosis," Journal of Biomedical Optics, vol. 14, 2009, pp. 064001-1 to 064001-7.;;Z. Jiang et al.: "In vivo trans-rectal ultrasound-coupled optical tomography of a transmissible venereal tumor model in the canine pelvic canal," Journal of Biomedical Optics, vol. 14, May 2009.;;W.W. Miller et al.: "Performance of an In-Vivo, Continuous Blood-Gas Monitor with Disposable Probe," Clinical Chemistry, vol. 33, No. 9, 1987.;;C.C.Schulman: "Transrectal Prostatic Biopsy," International Urology and Nephrology, vol. 2, 1970, pp. 157-161.</t>
+  </si>
+  <si>
+    <t>ПОЛЯКОВ Н.В. И ДР. Оперативное лечение стриктур нижней трети мочеточника после лучевой терапии органов малого таза. Онкоурология. 2016, N3, Т.12, С.68-73.;;KWANG HYUN KIM et al. A modified technique for ureteral reimplantation: intravesical detrusorrhaphy. J Pediatr Surg. 2013, N 48(8), P. 1813-1818.;;VICTOR P ALBERTS et al. Ureterovesical anastomotic techniques for kidney transplantation: a systematic review and meta-analysis. 2014, 27(6), P. 593-605.</t>
+  </si>
+  <si>
+    <t>"Molecular Cloning: A Laboratory Manual", 1989, COLD SPRING HARBOR LABORATORY PRESS;;AUSUBEL ET AL.: "Methods in Enzymology: Guide to Molecular Cloning Techniques", 1987, GREENE PUBLISHING ASSOCIATES;;SCOPES: "Protein Purification: Principles and Practice", 1994, SPRINGER-VERLOG;;MURAKAMI ET AL.: "The Molecular Basis of Cancer", 1995, WB SAUNDERS, article "Cell cycle regulation, oncogens, and antineoplastic drugs";;WILMAN: "Prodrugs in Cancer Chemotherapy", BIOCHEMICAL SOCIETY TRANSACTIONS, vol. 14, 1986, pages 375 - 382;;STELLA ET AL.: "Directed Drug Delivery", 1985, HUMANA PRESS, article "Prodrugs: A Chemical Approach to Targeted Drug Delivery", pages: 247 - 267;;SHARPE, P.AM.G. SCHMIDT: "Control and mitigation of healthcare-acquired infections: designing clinical trials to evaluate new materials and technologies", HERD: HEALTH ENVIRONMENTS RESEARCH &amp; DESIGN JOURNAL, vol. 5, no. 1, 2011, pages 94 - 115;;PRICE, D.L. ET AL.: "Mold colonization during use of preservative-treated and untreated airfilters, including HEPA filters from hospitals and commercial locations over an 8-year period (1996-2003", JOURNAL OF INDUSTRIAL MICROBIOLOGY AND BIOTECHNOLOGY, vol. 32, no. 7, 2005, pages 319 - 321, XP019357740, DOI: 10.1007/s10295-005-0226-1;;BANERJEE, D. ET AL.: "Green'' oxidation catalysis for rapid deactivation of bacterial spores", ANGEWANDTE CHEMIE INTERNATIONAL EDITION, vol. 45, no. 24, 2006, pages 3974 - 3977;;MARONI, M.B. SEIFERTT. LINDVALL: "Indoor air quality: a comprehensive reference book", vol. 3, 1995, ELSEVIER;;LI, Y. ET AL.: "Role of ventilation in airborne transmission of infectious agents in the built environment-a multidisciplinary systematic review", INDOOR AIR, vol. 17, no. 1, 2007, pages 2 - 18, XP071765381, DOI: 10.1111/j.1600-0668.2006.00445.x;;MAHIEU, L. ET AL.: "A prospective study on factors influencing aspergillus spore load in the air during renovation works in a neonatal intensive care unit", JOURNAL OF HOSPITAL INFECTION, vol. 45, no. 3, 2000, pages 191 - 197;;O'CONNELL, NH. HUMPHREYS: "Intensive care unit design and environmental factors in the acquisition of infection", JOURNAL OF HOSPITAL INFECTION, vol. 45, no. 4, 2000, pages 255 - 262;;MACDONALD, A.: "Protective air enclosures in health buildings", 1981, PAF WHITE THE MACMILLAN PRESS LTD., pages: 182;;ARAUJO, R.J.P. CABRALA.G. RODRIGUES: "Air filtration systems and restrictive access conditions improve indoor air quality in clinical units: Penicillium as a general indicator of hospital indoor fungal levels", AMERICAN JOURNAL OF INFECTION CONTROL, vol. 36, no. 2, 2008, pages 129 - 134, XP022499829, DOI: 10.1016/j.ajic.2007.02.001;;BOONE, S.AC.P. GERBA: "Significance of fomites in the spread of respiratory and enteric viral disease", APPLIED AND ENVIRONMENTAL MICROBIOLOGY, vol. 73, no. 6, 2007, pages 1687 - 1696;;LOPEZ, G.U. ET AL.: "Transfer efficiency of bacteria and viruses from porous and nonporous fomites to fingers under different relative humidity", APPLIED AND ENVIRONMENTAL MICROBIOLOGY, 2013;;GREENE, V.R. BONDG. MICHAELSEN, AIR PURIFICATION IN HOSPITALS. CLEANING AND PURIFICATION OF AIR IN BUILDINGS, 1960, pages 16;;See also references of EP 3775706A4</t>
+  </si>
+  <si>
+    <t>HAKAN SENTURK ET AL: "Silymarin attenuates the renal ischemia/reperfusion injury-induced morphological changes in the rat kidney", WORLD JOURNAL OF UROLOGY, SPRINGER, BERLIN, DE, vol. 26, no. 4, 12 April 2008 (2008-04-12) , pages 401-407, XP019627185, ISSN: 1433-8726;;FARUK TURGUT ET AL: "Antioxidant and protective effects of silymarin on ischemia and reperfusion injury in the kidney tissues of rats", INTERNATIONAL UROLOGY AND NEPHROLOGY, KLUWER ACADEMIC PUBLISHERS, DO, vol. 40, no. 2, 27 March 2008 (2008-03-27) , pages 453-460, XP019616368, ISSN: 1573-2584;;Foroud Shahbazi ET AL: "Potential renoprotective effects of silymarin against nephrotoxic drugs: a review of literature", Journal of pharmacy &amp; pharmaceutical sciences : a publication of the Canadian Society for Pharmaceutical Sciences, Société canadienne des sciences pharmaceutiques, 1 January 2012 (2012-01-01), pages 112-123, XP055100768, Canada Retrieved from the Internet: URL:http://www.ncbi.nlm.nih.gov/pubmed/223 65093 [retrieved on 2014-02-06]</t>
+  </si>
+  <si>
+    <t>Wen et al. Erythropoietin structure-function relationships: high degree of sequence homology among mammals. Blood vol. 82/5 pp. 1507-1516 (1993).*;;MacLeod et al., "Expression and Bioactivity of Recombinant Canine Erythropoietin," Am. J. Vet. Res. 59(9):1144-1148 (1998).;;Cowgill et al., "Use of Recombinant Human Erythropoietin for Management of Anemia in Dogs and Cats with Renal Failure," J. Am. Vet. Med. Assoc. 212(4):521-528 (1998).;;Spivak, "Recombinant Human Erythropoietin and the Anemia of Canc er," Blood 84(4):997-1004 (1994).;;Randolph et al., "Comparison of the Biolog ical Activity and Safety of Recombinant Canine Erythropoietin to Recombinant Human Erythropoietin in Normal Beagle Dogs," American College of Veterinary Internal Medicine, Official Abstract Form for Oral and Poster Presentations, 16&lt;th &gt;Annual Veterinary Medical Forum (May 1998) (abstract).;;Randolph et al., "Comparison of Biological Activity and Safety of Recombinant Canine Erythropoietin with that of Recombinant Human Erythropoietin in Clinically Normal Dogs," Am. J. Vet. Res. 60(5):636-642 (1999).</t>
+  </si>
+  <si>
+    <t>ChemSpider, N,N-dimethylaminopropyl acrylamide, 1 page;;Kim et al. Nature, 441/18, 2006, 362-365 (Year: 2006);;Kenney Polymer Engineering and Science, 8/3, 1968, 216-226 (Year: 1968);;Ma, Study of a Novel Zwitterionic Material and Its Biological Applications. Diss. 2018, 43 pages</t>
+  </si>
+  <si>
+    <t>Яцык С.П. и др. Сцинтиграфическое определение объема функционирующей паренхимы почек у детей с хроническим обструктивным пиелонефритом. - Вопросы современной педиатрии, 2006, No. 5, с.685-686, найдено [21.12.2012] из Интернет http://elibrary.ru.;;Outomuro Perez J.M. et al. [Radiologic and gammagraphic findings in a case of pyonephrosis. Anatomopathologic correlation] // Arch Esp Urol. 2002 Mar; 55(2): 199-204, реферат, найдено [21.12.2012] из Интернет www.pubmed.com.</t>
+  </si>
+  <si>
+    <t>SALLY MARSHALL: "The Podocyte: a Potential Therapeutic Target in Diabetic Nephropathy?", CURRENT PHARMACEUTICAL DESIGN, vol. 13, no. 26, 1 September 2007 (2007-09-01), pages 2713 - 2720, XP055199663, ISSN: 1381-6128, DOI: 10.2174/138161207781662957;;O. SMITHIES: "Why the kidney glomerulus does not clog: A gel permeation/diffusion hypothesis of renal function", PROCEEDINGS NATIONAL ACADEMY OF SCIENCES PNAS, vol. 100, no. 7, 1 April 2003 (2003-04-01), US, pages 4108 - 4113, XP055392518, ISSN: 0027-8424, DOI: 10.1073/pnas.0730776100;;J. PATRAKKA: "The Number of Podocyte Slit Diaphragms Is Decreased in Minimal Change Nephrotic Syndrome", PEDIATRIC RESEARCH, vol. 52, no. 3, 21 August 2002 (2002-08-21), US, pages 349 - 355, XP055392665, ISSN: 0031-3998, DOI: 10.1203/01.PDR.0000025285.72240.11;;FOGO AB; LUSCO MA; NAJAFIAN B; ALPERS CE: "AJKD Atlas of Renal Pathology: Minimal Change Disease", AMERICAN JOURNAL OF KIDNEY DISEASES THE OFFICIAL JOURNAL OF THE NATIONAL KIDNEY FOUNDATION, vol. 66, no. 2, 2015, pages 376 - 7;;HUANG B; BABCOCK H; ZHUANG X: "Breaking the diffraction barrier: Super-resolution imaging of cells", CELL, vol. 143, no. 7, 2010, pages 1047 - 58, XP028362268, DOI: doi:10.1016/j.cell.2010.12.002;;SULEIMAN H; ZHANG L; ROTH R; HEUSER JE; MINER JH; SHAW AS; DANI A: "Nanoscale protein architecture of the kidney glomerular basement membrane", ELIFE, vol. 2, 2013, pages E01149;;UNNERSJO-JESS D; SCOTT L; BLOM H; BRISMAR H: "Super-resolution stimulated emission depletion imaging of slit diaphragm proteins in optically cleared kidney tissue", KIDNEY INT, vol. 89, no. 1, 2016, pages 243 - 7;;GUSTAFSSON MG: "Surpassing the lateral resolution limit by a factor of two using structured illumination microscopy", J MICROSC, vol. 198, 2000, pages 82 - 7, XP008083176, DOI: doi:10.1046/j.1365-2818.2000.00710.x;;GUSTAFSSON MGL; SHAO L; CARLTON PM; WANG CJR; GOLUBOVSKAYA IN; CANDE WZ; AGARD DA; SEDAT JW: "Three-dimensional resolution doubling in wide-field fluorescence microscopy by structured illumination", BIOPHYSICALJOURNAL, vol. 94, no. 12, 2008, pages 4957 - 70, XP055047246, DOI: doi:10.1529/biophysj.107.120345;;DEEGENS JKJ; DIJKMAN HBPM; BORM GF; STEENBERGEN EJ; VAN DEN BERG JG; WEENING JJ; WETZELS JFM: "Podocyte foot process effacement as a diagnostic tool in focal segmental glomerulosclerosis", KIDNEY INT, vol. 74, no. 12, 2008, pages 1568 - 76, XP055392344, DOI: doi:10.1038/ki.2008.413;;VAN DEN BERG JG; VAN DEN BERGH WEERMAN MA; ASSMANN KJM; WEENING JJ; FLORQUIN S: "Podocyte foot process effacement is not correlated with the level of proteinuria in human glomerulopathies", KIDNEYLNT, vol. 66, no. 5, 2004, pages 1901 - 6;;PATRAKKA J; RUOTSALAINEN V; KETOLA I; HOLMBERG C; HEIKINHEIMO M; TRYGGVASON K; JALANKO H: "Expression of nephrin in pediatric kidney diseases", JOURNAL OF THE AMERICAN SOCIETY OF NEPHROLOGY JASN, vol. 12, no. 2, 2001, pages 289 - 96;;FURNESS PN; HALL LL; SHAW JA; PRINGLE JH: "Glomerular expression of nephrin is decreased in acquired human nephrotic syndrome", NEPHROLOGY, DIALYSIS, TRANSPLANTATION OFFICIAL PUBLICATION OF THE EUROPEAN DIALYSIS AND TRANSPLANT ASSOCIATION - EUROPEAN RENAL ASSOCIATION, vol. 14, no. 5, 1999, pages 1234 - 7;;AGRAWAL V; PRASAD N; JAIN M; PANDEY R: "Reduced podocin expression in minimal change disease and focal segmental glomerulosclerosis is related to the level of proteinuria", CLINICAL AND EXPERIMENTAL NEPHROLOGY, vol. 17, no. 6, 2013, pages 811 - 8;;SUVANTO M; JAHNUKAINEN T; KESTILA M; JALANKO H: "Podocyte proteins in congenital and minimal change nephrotic syndrome", CLINICAL AND EXPERIMENTAL NEPHROLOGY, vol. 19, no. 3, 2015, pages 481 - 8;;"Visualization of podocyte substructure with structured illumination microscopy (SIM): A new approach to nephrotic disease", BIOMED OPT EXPRESS, vol. 7, no. 2, 2016, pages 302 - 11;;BOHMAN SO; JAREMKO G; BOHLIN AB; BERG U: "Foot process fusion and glomerular filtration rate in minimal change nephrotic syndrome", KIDNEY LNT, vol. 25, no. 4, 1984, pages 696 - 700;;HLADUNEWICH MA; LEMLEY KV; BLOUCH KL; MYERS BD: "Determinants of GFR depression in early membranous nephropathy", AMERICAN JOURNAL OF PHYSIOLOGY. RENAL PHYSIOLOGY, vol. 284, no. 5, 2003, pages F1014 - 22;;CHINDELIN J; ARGANDA-CARRERAS I; FRISE E; KAYNIG V; LONGAIR M; PIETZSCH T; PREIBISCH S; RUEDEN C; SAALFELD S; SCHMID B: "Fiji: An open-source platform for biological- image analysis", NATURE METHODS, vol. 9, no. 7, 2012, pages 676 - 82, XP055343835, DOI: doi:10.1038/nmeth.2019;;STEGER C: "An unbiased detector of curvilinear structures", IEEE TRANS. PATTERNANAL. MACHINE INTEL!, vol. 20, no. 2, 1998, pages 113 - 25, XP000619964, DOI: doi:10.1109/34.659930</t>
+  </si>
+  <si>
+    <t>Unnersjo-Jess Kidney International 2016 89:243-247 (Year: 2016)</t>
+  </si>
+  <si>
+    <t>Pullman (Optical Society of America (OSA) 2016 vol. 7, No. 2, total 10 pages). (Year: 2016).;;Unnersjo-Jess Kidney International 2016 89:243-247 (Year: 2016).;;International Search Report; European Patent Office; International Application No. PCT/EP2018/060779; dated Jun. 6, 2018; 4 pages.;;Written Opinion of the International Searching Authority; European Patent Office; International Application No. PCT/EP2018/060779; dated Jun. 6, 2018; 9 pages.;;Vinita Agrawal et al.; Reduced Podocin Expression in Minimal Change Disease and Focal Segmental Glomerulosclerosis is Related to the Level of Proteinuria; Clin Exp Nephrol; 2013; 8 pages; vol. 17.;;Sven-Olof Bohman et al.; Foot Process Fusion and Glomerular Filtration Rate in Minimal Change Nephrotic Syndrome; Kidney International; 1984; 5 pages; vol. 25.;;Jeroen K.J. Deegens et al.; Podocyte Foot Process Effacement as a Diagnostic Tool in Focal Segmental Glomerulosclerosis; Kidney International; 2008; 9 pages; vol. 74.;;Agnes B. Fogo et al.; AJKD Atlas of Renal Pathology: Minimal Change Disease; Am J Kidney Dis.; 2015; 2 pages; vol. 66, No. 2.;;Peter N. Furness et al.; Glomerular Expression of Nephrin is Decreased in Acquired Human Nephrotic Syndrome; Nephrology Dialysis Transplantation; 1999; 4 pages; vol. 14.;;M.G.L. Gustafsson et al.; Surpassing the Lateral Resolution Limit by a Factor of Two Using Structured Illumination Microscopy; Journal of Microscopy; May 2000; 6 pages; vol. 198, Pt. 2.;;Mats G.L. Gustafsson et al.; Three-Dimensional Resolution Doubling in Wide-Field Fluorescence Microscopy by Structured Illumination; Biophysical Journal; Jun. 2008; 14 pages; vol. 94.;;M.A. Hladunewich et al.; Determinants of GFR Depression in Early Membranous Nephropathy; Am J Physiol Renal Physiol; Jan. 14, 2003; 9 pages; vol. 284.;;Bo Huang et al.; Breaking the Diffraction Barrier: Super-Resolution Imaging of Cells; Cell; Dec. 23, 2010; 12 pages; vol. 143.;;Sally M. Marshall; The Podocyte: A Potential Therapeutic Target in Diabetic Nephropathy?; Current Pharmaceutical Design; 2007; 8 pages; vol. 13.;;Jaakko Patrakka et al.; Expression of Nephrin in Pediatric Kidney Diseases; J Am Soc Nephrol; 2001; 8 pages vol. 12.;;Jaakko Patrakka et al.; The Number of Podocyte Slit Diaphragms is Decreased in Minimal Change Nephrotic Syndrome; Pediatric Research; 2002; 7 pages; vol. 52, No. 3.;;James M. Pullman et al.; Visualization of Podocyte Substructure with Structured Illumination Microscopy (SIM): A New Approach to Nephrotic Disease; Biomedical Optics Express 302; Feb. 2016; 10 pages; vol. 7, No. 2.;;Johannes Schindelin et al.; Fiji: An Open-Source Platform for Biological-Image Analysis; Nature Methods; Jul. 2012; 7 pages; vol. 9, No. 7.;;Oliver Smithies; Why the Kidney Glomerulus Does Not Clog: A Gel Permeation/Diffusion Hypothesis of Renal Function; PNAS; Apr. 1, 2003; 6 pages; vol. 100, No. 7.;;Carsten Steger; An Unbiased Detector of Curvilinear Structures; IEEE Transactions on Pattern Analysis and Machine Intelligence; Feb. 1998; 13 pages; vol. 20, No. 2.;;Hani Suleiman et al.; Nanoscale Protein Architecture of the Kidney Glomerular Basement Membrane; eLife Research Article; 2013; 18 pages; vol. 2.;;Maija Suvanto et al.; Podocyte Proteins in Congenital and Minimal Change Nephrotic Syndrome; Clin Exp Nephrol; 2015; 8 pages; vol. 19.;;David Unnersjo-Jess et al.; Super-Resolution Stimulated Emission Depletion Imaging of Slit Diaphragm Proteins in Optically Cleared Kidney Tissue; Kidney International; 2016; 5 pages; vol. 89.;;Jose G. Van Den Berg et al.; Podocyte Foot Process Effacement is not Correlated with the Level of Proteinuria in Human Glomerulopathies; Kidney International; 2004; 6 pages; vol. 66.;;“Acta Physiologica,” Official Journal of the Federation of European Physiological Societies, vol. 219, Mar. 2017.;;Korean Office Action, Korean Intellectual Property Office, Korean Application No. 10-2019-7034313, dated Jun. 15, 2022, 4 pages.;;Hladunewich, M.A. et al., “Determinants of GFR depression in early membranous Nephropathy” Am J Physiol Renal Physiol, vol. 284, Jan. 14, 2003.;;Lahdenkari, Anne-Tiina et al., “Podocytes Are Firmly Attached to Glomerular Basement Membrane in Kidneys with Heavy Proteinuria” Journal of the American Society of Nephrology—J Am Soc Nephrol, vol. 15, Mar. 2004.;;Jeffersson, J.A. et al., “Proteinuria in diabetic kidney disease: A mechanistic Viewpoint” International Society of Nephrology—Kidney International, Apr. 16, 2008.;;Toyoda, Masao et al., “Podocyte Detachment and Reduced Glomerular Capillary Endothelial Fenestration in Human Type 1 Diabetic Nephropathy” Diabetes, vol. 56, Aug. 2007.;;Veron, Delma et al., “Overexpression of VEGF-A in podocytes of adult mice causes glomerular disease” Kidney International, vol. 77, Mar. 10, 2010.;;Cybulsky, Andrey et al., “Experimental membranous nephropathy redux” Am J Physiol Renal Physiol, vol. 289, 2005 Podocyte cytoskeltal changes induced by antibody compl. p. 664-666.;;Wilson, Tony, “Resolution and optical sectioning in the confocal microscope” Journal of Microscopy, vol. 244, 2011.;;Ilgen, Peter et al., “STED Super-Resolution Microscopy of Clinical Paraffin-Embedded Human Rectal Cancer Tissue” Plos One, vol. 9, No. 7, Jul. 15, 2014.;;Declaration of Prof. Dr. Nicole Endlich dated May 20, 2022.;;Email dated Jan. 24, 2017.;;Email dated Mar. 7, 2017.;;European Summons to attend oral proceedings pursuant to Rule 115(1) EPC, European Patent Office, European Application No. 17168506.8, Jul. 22, 2022, 16 pages.;;Siegerist et al., Super-resolution microscopy of the podocyte slit diaphragm, Post Session B, 2017; pp. 117-118, John Wiley &amp; Sons Ltd.;;Japanese Office Action, Japanese Patent Office, dated Mar. 1, 2022, Japanese Patent Application No. 2019-557788, 6 pages.;;Israeli Office Action, Israel Patent Office, Israeli Application No. 270131, dated Dec. 14, 2022, 4 pages.;;Japanese Office Action, Japan Patent Office, Japanese Application No. 2019-557788, dated Nov. 22, 2022, 7 pages.;;Korean Decision to Grant, Korean Intellectual Property Office, Korean Application No. 10-2019-7034313, dated Dec. 27, 2022, 2 pages.</t>
+  </si>
+  <si>
+    <t>Etienne, M.; Verlinden, M.; Brassinne, M.; "Treatment with Cisapride of the Gastrointestinal and Urological Sequelae of Spinal Cord Transection: Case Report", Paraplegia, 26 (1998), pp 162-164.*;;A.P.C.W. Ford and M.S.Kava, Chapter 8: "5-HT4 receptors in lower urinary tract tissues", pp. 171-193, in: "5-HT4 receptors in the Brain and the Periphery", ed. R.M. Englen, Springer-Verlag and RG Landes &amp; Co, 1998.;;M.V. Waikar, APDW Ford et al., Br. J. Pharmacol., 1994, 111(1), 213-218.;;R.M. Eglen et al., Br. J. Pharmacol., vol. 107, Dec. 1992 Proceedings Supplement, 439P.;;J. Bermudez et al., J. Med. Chem., 1990, 33, 1924-1929.;;K.H. Buchheit and R. Gamse, Naunyn-Schmiedeberg's Arch. Pharmacol., 1991, 343 (Suppl.), R101.;;K.H. Buchheit, R. Gamse et al., Eur. J. Pharmacol., 1991, 200, 373-374.;;ML Cohen et al., J. Pharmacol. Exptl. Therap., 1989, 248, 197-201.;;M. Corsi et al., Br. J. Pharmacol., 1991, 104, 709.;;D.A. Craig et al., J. Pharmacol. Exp. Therapeutics, 1990, 252(3), 1378-1386.;;G.H. De Groot, et al., Paraplegia, vol. 26, No. 3, 1988, pp. 159-161.;;A. Dumuis et al., Eur. J. Pharmacol., 1988, 146, 187-188.;;A. Dumuis et al., Naunyn-Schmiedeberg's Arch. Pharmacol., 1989, 340, 403-410.;;A. Dumuis et al., Naunyn-Schmiedeberg's Arch. Pharmacol., 1992, 345, 264-269.;;C.J. Elswood et al., Eur. J. Pharmacol., 1991, 196, 149-155.;;M. Etienne, et al., Paraplegia, vol. 26, No. 3, 1988, pp. 162-164.;;A.P.C.W. Ford et al., "5HT4 receptor agonism inhibits neuronally-mediated responses in monkey urinary bladder", 2nd International Symposium on Serotonin, Houston, Sep. 1992, p. 53.;;R. Gamse, Cancer Treatment Reviews, 1990, 17, 301-305.;;P. Hanson, et al., Acta Belg. Med. Phys., vol. 12, No. 3, 1989, pp. 81-88.;;J.R. Hindmarsh et al., Br. J. Pharmacol., 1977, 61, 115P.;;A.J. Kaumann, Naunyn-Schmiedeberg's Arch. Pharmacol., 1990, 342, 619-622.;;A.J. Kaumann et al., Br. J. Pharmacol., 1990, 100, 879-885.;;M. Lazzaroni, et al., Digestion 37: 110-113 (1987).;;E. Messori, et al., Br. J. Pharmacol. 115, 677-683 (1995).;;DR Nelson et al. Biochem. Pharmacol., 1989, 38(10), 1693-1695.;;William D. Steers, et al. Drug Dev. Res. vol. 27, No. 4, 1992, pp. 361-375.;;GJ Sanger and DR Nelson, Eur. J. Pharmacol., 1989, 159, 113-124.;;M. Tonini, et al. Br. J. Pharmacol., 1994, 113, 1-2.;;M. Turconi, et al., Drugs of the Future, vol. 16, No. 11, 1991, pp. 1011-1026.;;JW Upward et al., Eur. J. Cancer, 1990, 26 (Suppl.), S12-S15.;;S. Vaidyanathan, J. Urology, 1981, vol. 125 42-43.;;H van den Brink et al, Eur. J. Pharmacol., 1990, 181(1-2), 119-125; (Chem Abs 1990, vol 113, p57, abstract 126402c).;;Scand. J. Urology and Nephrology, 1979, 13, 79-82.</t>
+  </si>
+  <si>
+    <t>SALLY MARSHALL: "The Podocyte: a Potential Therapeutic Target in Diabetic Nephropathy?", CURRENT PHARMACEUTICAL DESIGN, vol. 13, no. 26, 1 September 2007 (2007-09-01), pages 2713 - 2720, XP055199663, ISSN: 1381-6128, DOI: 10.2174/138161207781662957;;O. SMITHIES: "Why the kidney glomerulus does not clog: A gel permeation/diffusion hypothesis of renal function", PROCEEDINGS NATIONAL ACADEMY OF SCIENCES PNAS, vol. 100, no. 7, 1 April 2003 (2003-04-01), US, pages 4108 - 4113, XP055392518, ISSN: 0027-8424, DOI: 10.1073/pnas.0730776100;;J. PATRAKKA: "The Number of Podocyte Slit Diaphragms Is Decreased in Minimal Change Nephrotic Syndrome", PEDIATRIC RESEARCH, vol. 52, no. 3, 21 August 2002 (2002-08-21), US, pages 349 - 355, XP055392665, ISSN: 0031-3998, DOI: 10.1203/01.PDR.0000025285.72240.11;;FOGO AB; LUSCO MA; NAJAFIAN B; ALPERS CE: "AJKD Atlas of Renal Pathology: Minimal Change Disease", AMERICAN JOURNAL OF KIDNEY DISEASES THE OFFICIAL JOURNAL OF THE NATIONAL KIDNEY FOUNDATION, vol. 66, no. 2, 2015, pages 376 - 7;;HUANG B; BABCOCK H; ZHUANG X: "Breaking the diffraction barrier: Super-resolution imaging of cells", CELL, vol. 143, no. 7, 2010, pages 1047 - 58, XP028362268, DOI: doi:10.1016/j.cell.2010.12.002;;SULEIMAN H; ZHANG L; ROTH R; HEUSER JE; MINER JH; SHAW AS; DANI A: "Nanoscale protein architecture of the kidney glomerular basement membrane", ELIFE, vol. 2, 2013, pages e01149;;UNNERSJO-JESS D; SCOTT L; BLOM H; BRISMAR H: "Super-resolution stimulated emission depletion imaging of slit diaphragm proteins in optically cleared kidney tissue", KIDNEY INT, vol. 89, no. 1, 2016, pages 243 - 7;;GUSTAFSSON MG: "Surpassing the lateral resolution limit by a factor of two using structured illumination microscopy", J MICROSC, vol. 198, 2000, pages 82 - 7, XP008083176, DOI: doi:10.1046/j.1365-2818.2000.00710.x;;GUSTAFSSON MGL; SHAO L; CARLTON PM; WANG CJR; GOLUBOVSKAYA IN; CANDE WZ; AGARD DA; SEDAT JW: "Three-dimensional resolution doubling in wide-field fluorescence microscopy by structured illumination", BIOPHYSICALJOURNAL, vol. 94, no. 12, 2008, pages 4957 - 70, XP055047246, DOI: doi:10.1529/biophysj.107.120345;;DEEGENS JKJ; DIJKMAN HBPM; BORM GF; STEENBERGEN EJ; VAN DEN BERG JG; WEENING JJ; WETZELS JFM: "Podocyte foot process effacement as a diagnostic tool in focal segmental glomerulosclerosis", KIDNEY INT, vol. 74, no. 12, 2008, pages 1568 - 76, XP055392344, DOI: doi:10.1038/ki.2008.413;;VAN DEN BERG JG; VAN DEN BERGH WEERMAN MA; ASSMANN KJM; WEENING JJ; FLORQUIN S: "Podocyte foot process effacement is not correlated with the level of proteinuria in human glomerulopathies", KIDNEYLNT, vol. 66, no. 5, 2004, pages 1901 - 6;;PATRAKKA J; RUOTSALAINEN V; KETOLA I; HOLMBERG C; HEIKINHEIMO M; TRYGGVASON K; JALANKO H: "xpression of nephrin in pediatric kidney diseases", JOURNAL OF THE AMERICAN SOCIETY OF NEPHROLOGY JASN, vol. 12, no. 2, 2001, pages 289 - 96;;FURNESS PN; HALL LL; SHAW JA; PRINGLE JH: "Glomerular expression of nephrin is decreased in acquired human nephrotic syndrome", NEPHROLOGY, DIALYSIS, TRANSPLANTATION OFFICIAL PUBLICATION OF THE EUROPEAN DIALYSIS AND TRANSPLANT ASSOCIATION - EUROPEAN RENAL ASSOCIATION, vol. 14, no. 5, 1999, pages 1234 - 7;;AGRAWAL V; PRASAD N; JAIN M; PANDEY R: "Reduced podocin expression in minimal change disease and focal segmental glomerulosclerosis is related to the level of proteinuria", CLINICAL AND EXPERIMENTAL NEPHROLOGY, vol. 17, no. 6, 2013, pages 811 - 8;;SUVANTO M; JAHNUKAINEN T; KESTILA M; JALANKO H: "Podocyte proteins in congenital and minimal change nephrotic syndrome", CLINICAL AND EXPERIMENTAL NEPHROLOGY, vol. 19, no. 3, 2015, pages 481 - 8;;PULLMAN JM; NYLK J; CAMPBELL EC; GUNN-MOORE FJ; PRYSTOWSKY MB; DHOLAKIA K: "Visualization of podocyte substructure with structured illumination microscopy (SIM): A new approach to nephrotic disease", BIOMED OPT EXPRESS, vol. 7, no. 2, 2016, pages 302 - 11;;BOHMAN SO; JAREMKO G; BOHLIN AB; BERG U: "Foot process fusion and glomerular filtration rate in minimal change nephrotic syndrome", KIDNEY LNT, vol. 25, no. 4, 1984, pages 696 - 700;;HLADUNEWICH MA; LEMLEY KV; BLOUCH KL; MYERS BD: "Determinants of GFR depression in early membranous nephropathy", AMERICAN JOURNAL OF PHYSIOLOGY. RENAL PHYSIOLOGY, vol. 284, no. 5, 2003, pages F1014 - 22;;SCHINDELIN J; ARGANDA-CARRERAS I; FRISE E; KAYNIG V; LONGAIR M; PIETZSCH T; PREIBISCH S; RUEDEN C; SAALFELD S; SCHMID B: "Fiji: An open-source platform for biological- image analysis", NATURE METHODS, vol. 9, no. 7, 2012, pages 676 - 82, XP055343835, DOI: doi:10.1038/nmeth.2019;;STEGER C: "An unbiased detector of curvilinear structures", IEEE TRANS. PATTERN ANAL. MACHINE INTEL!, vol. 20, no. 2, 1998, pages 113 - 25, XP000619964, DOI: doi:10.1109/34.659930</t>
+  </si>
+  <si>
+    <t>BASU J ET AL: "Platform technologies for tubular organ regeneration", TRENDS IN BIOTECHNOLOGY, ELSEVIER PUBLICATIONS, CAMBRIDGE, GB, vol. 28, no. 10, 1 October 2010 (2010-10-01), pages 526-533, XP027300102, ISSN: 0167-7799 [retrieved on 2010-08-25];;PARK ET AL: "Small Intestinal Submucosa Covered Expandable Z Stents for Treatment of Tracheal Injury: An Experimental Pilot Study in Swine", JOURNAL OF VASCULAR AND INTERVENTIONAL RADIOLOGY, VA, AMSTERDAM, NL, vol. 11, no. 10, 1 November 2000 (2000-11-01), pages 1325-1330, XP022405174, ISSN: 1051-0443, DOI: 10.1016/S1051-0443(07)61310-4;;KOJI KOJIMA ET AL.: "AUTOLOGOUS TISSUE-ENGINEERED TRACHEA WITH SHEEP NASAL CHONDROCYTES", THE JOURNAL OF THORACIC AND CARDIOVASCULAR SURGERY, vol. 123, 2002, pages 1177-1184, XP002694598,;;KITAGAMI ET AL.: "EXPERIMENTAL STUDY OF TRACHEAL PATCH RECONSTRUCTION WITH A COVERED EXPANDABLE METALLIC STENT", ANN THORACIC SURG., vol. 66, 1998, pages 1777-1781, XP002694599,;;MAURIZIO MARZARO ET AL.: "IN VITRO AND IN VIVO PROPOSAL OF AN ARTIFICIAL ESOPHAGUS", JOURNAL OF BIOMEDICAL MATERIALS RESEARCH PART A, vol. 77A, no. 4, 2006, pages 795-801, XP002694600, DOI: 10.1002/JBM.A.30666;;ZANI A ET AL: "Tissue engineering: an option for esophageal replacement?", SEMINARS IN PEDIATRIC SURGERY, SAUNDERS, PHILADELPHIA, PA, US, vol. 18, no. 1, 1 February 2009 (2009-02-01), pages 57-62, XP025815250, ISSN: 1055-8586, DOI: 10.1053/J.SEMPEDSURG.2008.10.011 [retrieved on 2008-12-19];;WANG C ET AL: "A small diameter elastic blood vessel wall prepared under pulsatile conditions from polyglycolic acid mesh and smooth muscle cells differentiated from adipose-derived stem cells", BIOMATERIALS, ELSEVIER SCIENCE PUBLISHERS BV., BARKING, GB, vol. 31, no. 4, 1 February 2010 (2010-02-01), pages 621-630, XP026762071, ISSN: 0142-9612, DOI: 10.1016/J.BIOMATERIALS.2009.09.086 [retrieved on 2009-10-12];;HEATHER L PRICHARD ET AL: "An Early Study on the Mechanisms that Allow Tissue-Engineered Vascular Grafts to Resist Intimal Hyperplasia", JOURNAL OF CARDIOVASCULAR TRANSLATIONAL RESEARCH, SPRINGER US, BOSTON, vol. 4, no. 5, 12 July 2011 (2011-07-12), pages 674-682, XP019953888, ISSN: 1937-5395, DOI: 10.1007/S12265-011-9306-Y;;POH M ET AL: "Blood vessels engineered from human cells", THE LANCET, LANCET LIMITED. LONDON, GB, vol. 365, no. 9477, 18 June 2005 (2005-06-18), pages 2122-2124, XP027765106, ISSN: 0140-6736 [retrieved on 2005-06-18];;NIKLASON L E ET AL: "Functional arteries grown in vitro", SCIENCE, AMERICAN ASSOCIATION FOR THE ADVANCEMENT OF SCIENCE, WASHINGTON, DC; US, vol. 284, no. 5413, 16 April 1999 (1999-04-16), pages 489-493, XP002198665, ISSN: 0036-8075, DOI: 10.1126/SCIENCE.284.5413.489</t>
+  </si>
+  <si>
+    <t>Trimethoprim in Pediatric Urinary Tract Infection Child Nephrol. Urol. 1988 1989; 9: 77 81 Rajkumar et al.;;Manius in: Flory, ed. Analytical Profiles of Drug Substances, vol. 7 (Academic Press, 1978), pp. 445 475.</t>
+  </si>
+  <si>
+    <t>PARAPLEGIA vol. 26, no. 3, 1988, pages 162 - 164; M.ETIENNE ET AL.: 'Treatment with cisapride of the gastrointestinal and urological sequelae of spinal cord transection: case report';;PARAPLEGIA vol. 26, no. 3, 1988, pages 159 - 161; G.H. DE GROOT ET AL.: 'Effects of cisapride on constipation due to neurological lesion';;ACTA BELG. MED. PHYS. vol. 12, no. 3, 1989, pages 81 - 88; P.HANSON ET AL.: 'Effet du cisapride sur les vessies neurologiques';;DRUG. DEV. RES. vol. 27, no. 4, 1992, pages 361 - 375; WILLIAM D. STEERS ET AL.: 'Effects of serotonic agonists on micturation and sexual function in the rat';;DRUGS FUTURE vol. 16, no. 11, 1991, pages 1011 - 1026; M. TURCONI ET AL: 'Azabicycloalkyl benzimidazolones: Interaction with serotonergic 5-HT3 and 5-HT4 receptors and potential therapeutic implications'</t>
+  </si>
+  <si>
+    <t>BASU J ET AL: "Platform technologies for tubular organ regeneration", TRENDS IN BIOTECHNOLOGY, ELSEVIER PUBLICATIONS, CAMBRIDGE, GB, vol. 28, no. 10, 1 October 2010 (2010-10-01), pages 526-533, XP027300102, ISSN: 0167-7799 [retrieved on 2010-08-25];;PARK ET AL: "Small Intestinal Submucosa Covered Expandable Z Stents for Treatment of Tracheal Injury: An Experimental Pilot Study in Swine", JOURNAL OF VASCULAR AND INTERVENTIONAL RADIOLOGY, VA, AMSTERDAM, NL, vol. 11, no. 10, 1 November 2000 (2000-11-01), pages 1325-1330, XP022405174, ISSN: 1051-0443, DOI: 10.1016/S1051-0443(07)61310-4;;KOJI KOJIMA ET AL.: "AUTOLOGOUS TISSUE-ENGINEERED TRACHEA WITH SHEEP NASAL CHONDROCYTES", THE JOURNAL OF THORACIC AND CARDIOVASCULAR SURGERY, vol. 123, 2002, pages 1177-1184, XP002694598,;;KITAGAMI ET AL.: "EXPERIMENTAL STUDY OF TRACHEAL PATCH RECONSTRUCTION WITH A COVERED EXPANDABLE METALLIC STENT", ANN THORACIC SURG., vol. 66, 1998, pages 1777-1781, XP002694599,;;MAURIZIO MARZARO ET AL.: "IN VITRO AND IN VIVO PROPOSAL OF AN ARTIFICIAL ESOPHAGUS", JOURNAL OF BIOMEDICAL MATERIALS RESEARCH PART A, vol. 77A, no. 4, 2006, pages 795-801, XP002694600, DOI: 10.1002/JBM.A.30666;;ZANI A ET AL: "Tissue engineering: an option for esophageal replacement?", SEMINARS IN PEDIATRIC SURGERY, SAUNDERS, PHILADELPHIA, PA, US, vol. 18, no. 1, 1 February 2009 (2009-02-01), pages 57-62, XP025815250, ISSN: 1055-8586, DOI: 10.1053/J.SEMPEDSURG.2008.10.011 [retrieved on 2008-12-19];;WANG C ET AL: "A small diameter elastic blood vessel wall prepared under pulsatile conditions from polyglycolic acid mesh and smooth muscle cells differentiated from adipose-derived stem cells", BIOMATERIALS, ELSEVIER SCIENCE PUBLISHERS BV., BARKING, GB, vol. 31, no. 4, 1 February 2010 (2010-02-01), pages 621-630, XP026762071, ISSN: 0142-9612, DOI: 10.1016/J.BIOMATERIALS.2009.09.086 [retrieved on 2009-10-12]</t>
+  </si>
+  <si>
+    <t>See references of EP 0662828A4</t>
+  </si>
+  <si>
+    <t>Tan et al., Esophageal Tissue Engineering: An In Depth Review on Scaffold Design, Wiley Online Library, Biotechnology and Bioengineering, pgs.1-15 (Year: 2011)</t>
+  </si>
+  <si>
+    <t>Basu J et al: “Platform technologies for tubular organ regeneration”, Trends in Biotechnology, Elsevier Publications, Cambridge, GB, vol. 28, No. 10, Oct. 1, 2010 (Oct. 1, 2010), pp. 526-533.;;Park et al: “Small Intestinal Submucosa Covered Expandable Z Stents for Treatment of Tracheal Injury: An Experimental Pilot Study in Swine”, Journal of Vascular and Interventional Radiology, VA, Amsterdam, NL, vol. 11, No. 10, Nov. 1, 2000 (Nov. 1, 2000), pp. 1325-1330.;;Koji Kojima et al.: “Autologous Tissue-Engineered Trachea With Sheep Nasal Chondrocytes”, The Journal of Thoracic and Cardiovascular Surgery, vol. 123, 2002, pp. 1177-1184.;;Kitagami et al.: “Experimental Study of Tracheal Patch Reconstruction With a Covered Expandable Metallic Stent”, Ann Thoracic Surg., vol. 66, 1998, pp. 1777-1781.;;Maurizio Marzaro et al.: “In Vitro and in Vivo Proposal of an Artificial Esophagus”, Journal of Biomedical Materials Research Part A, vol. 77A, No. 4, 2006, pp. 795-801.;;Zani A et al: “Tissue engineering: an option for esophageal replacement?”, Seminars in Pediatric Surgery, Saunders, Philadelphia, PA, US, vol. 18, No. 1, Feb. 1, 2009 (Feb. 1, 2009), pp. 57-62.;;Wang C et al: “A small diameter elastic blood vessel wall prepared under pulsatile conditions from polyglycolic acid mesh and smooth muscle cells differentiated from adipose-derived stem cells”, Biomaterials. Elsevier Science Publishers, BV., Barking. GB., vol. 31, No. 4, Feb. 1, 2010 (Feb. 1, 2010), pp. 621-630.;;Heather L Prichard et al: “An Early Study on the Mechanisms that Allow Tissue-Engineered Vascular Grafts to Resist Intimal Hyperplasia”, Journal of Cardiovascular Translational Research, Springer US, Boston, vol. 4, No. 5, Jul. 12, 2011 (Jul. 12, 2011), pp. 674-682.;;Poh M et al: “Blood vessels engineered from human cells”, The Lancet, Lancet Limited. London, GB, vol. 365, No. 9477, Jun. 18, 2005 (Jun. 18, 2005), pp. 2122-2124.;;Niklason L E et al: “Functional arteries grown in vitro”, Science, American Association for the Advancement of Science. Washington, DC; US, vol. 284, No. 5413, Apr. 16, 1999 (Apr. 16, 1999), pp. 489-493.;;International Search Report and Written Opinion dated Apr. 12, 2013, for PCT/US2012/059955.;;Zhao et al., “Engineered Tissue-Stent Biocomposites as Tracheal Replacements,” Tissue Engineering: Part A, vol. 22, Nos. 17 and 18, 2016, pp. 1086-1097.</t>
+  </si>
+  <si>
+    <t>http://www.perfectleg.com. updated 2011</t>
+  </si>
+  <si>
+    <t>Zhao et al., “Engineered Tissue-Stent Biocomposites as Tracheal Replacements,” Tissue ENgineering: Part A, vol. 22, Nos. 17 and 18, 2016, pp. 1086-1097.;;Basu J et al: “Platform technologies for tubular organ regeneration”, Trends in Biotechnology, Elsevier Publications, Cambridge, GB, vol. 28, No. 10, Oct. 1, 2010 (Oct. 11, 2010), pp. 526-533.;;Park et al: “Small Intestinal Submucosa Covered Expandable Z Stents for Treatment of Tracheal Injury: An Experimental Pilot Study in Swine”, Journal of Vascular and Interventional Radiology, VA, Amsterdam, NL, vol. 11, No. 10, Nov. 1, 2000 (Nov. 1, 2000), pp. 1325-1330.;;Koji Kojima et al.: “Autologous Tissue-Engineered Trachea With Sheep Nasal Chondrocytes”, The Journal of Thoracic and Cardiovascular Surgery, vol. 123, 2002, pp. 1177-1184.;;Kitagami et al.: “Experimental Study of Tracheal Patch Reconstruction With a Covered Expandable Metallic Stent”, Ann Thoracic Surg., vol. 66, 1998, pp. 1777-1781.;;Viaurizio Marzaro et al.: “In Vitro and In Vivo Proposal of an Artificial Esophagus”, Journal of Biomedical Materials Research Part A, vol. 77A, No. 4, 2006, pp. 795-801.;;Zani A et al: “Tissue engineering: an option for esophageal replacement?”, Seminars in Pediatric Surgery, Saunders, Philadelphia, PA, US, vol. 18, No. 1, Feb. 1, 2009 (Feb. 1, 2009), pp. 57-62.;;Wang C et al: “A small diameter elastic blood vessel wall prepared under pulsatile conditions from polyglycolic acid mesh and smooth muscle cells differentiated from adipose-derived stem cells”, Biomaterials. Elsevier Science Publishers, BV., Barking. GB., vol. 31, No. 4, Feb. 1, 2010 (Feb. 1, 2010), pp. 621-630.;;Heather L Prichard et al: “An Early Study on the Mechanisms that Allow Tissue-Engineered Vascular Grafts to Resist Intimal Hyperplasia”, Journal of Cardiovascular Translational Research, Springer US, Boston, vol. 4, No. 5, Jul. 12, 2011 (Jul. 12, 2011), pp. 674-682.;;Poh M et al: “Blood vessels engineered from human cells”, The Lancet, Lancet Limited. London, GB, vol. 365, No. 9477, Jun. 18, 2005 (Jun. 18, 2005), pp. 2122-2124.;;Niklason L E et al: “Functional arteries grown in vitro”, Science, American Association for the Advancement of Science. Washington, DC; US, vol. 284, No. 5413, Apr. 16, 1999 (Apr. 16, 1999), pp. 489-493.;;International Search Report and Written Opinion dated Apr. 12, 2013, for PCT/US2012/059955.</t>
+  </si>
+  <si>
+    <t>HEATHCARE COST AND UTILIZATION PROJECT, N.I.S., 2007;;KONETY, B.R.; JOYCE, G.F.; WISE, M.: "Bladder and upper tract urothelial cancer", JOURNAL OF UROLOGY, vol. 177, 2007, pages 1636 - 1645, XP022040685, DOI: doi:10.1016/j.juro.2007.01.055;;GUDJONSSON, S.; DAVIDSSON, T.; MANSSON, W.: "Incontinent urinary diversion", BJU INTERNATIONAL, vol. 102, 2008, pages 1320 - 1325;;KONETY, B.R.; ALLAREDDY, V.: "Influence of post-cystectomy complications on cost and subsequent outcome", JOURNAL OF UROLOGY, vol. 177, 2007, pages 280 - 287, XP005800481, DOI: doi:10.1016/j.juro.2006.08.074;;DAHL, D.M.; MCDOUGAN, W.S.: "Use of intestinal segments and urinary diversion", 2009, article "Campbell-Walsh Urology";;DAHL ET AL., SCIENCE TRANSLATIONAL MEDICINE, vol. 3, no. 68, 2011, pages 2;;"Heathcare Cost and Utilization Project", 2007, N.I.S.;;GUDJONSSON, S.; DAVIDSSON, T.; MANSSON, W.: "Incontinent. urinary diversion", BJU INTERNATIONAL, vol. 102, 2008, pages 1320 - 1325;;KONETY, B.R.; ALLAREDDY, V.: "lnfluence of post-cystectomy complications on cost and subsequent outcome", JOURNAL OF UROLOGY, vol. 177, 2007, pages 280 - 287, XP005800481, DOI: doi:10.1016/j.juro.2006.08.074;;NIKLASON, L.E.; GAO, J.; ABBOTT, W.M.; HIRSCHI, K.; HOUSER, S.; MARINI, R.; LANGCR, R.: "Functional arteries grown in vitro", SCIENCE, vol. 284, 1999, pages 489 - 493, XP002200891, DOI: doi:10.1126/science.284.5413.489;;POH, M.; BOYER, M. ET AL.: "Blood vessels engineered from human cells", THE LANCET, vol. 365, 2005, pages 2122 - 2124, XP025277702, DOI: doi:10.1016/S0140-6736(05)66735-9;;NIKLASON, L.E.; YEH, A.T.; CALLE, E.A.; BAI, Y.; VALENTIN, A.; HUMPHREY, J.D.: "Enabling tools for engineering collagenous tissues integrating bioreactors, intravital imaging, and biomechanical modeling", PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES, vol. 107, 2010, pages 3335 - 3339;;DAHL, S.L.M.; KOH, J.; PRABLAKAR, V.; NIKLASON, L.E.: "Decellularized native and engineered arterial scafolds for transplantation", CELL TRANSPLANTATION, vol. 12, 2003, pages 659 - 666, XP009062153;;DAHL, S.L.M.; KYPSON, A.P.; SAWSON, J.H.; BLUM, J.L.; STRADER, J.T.; LI, Y.; MANSON, R.J.; TENTE, W.E.; DIBERNARDO, L.; HENSLEY, M: "Readily available tissue-engineered vascular grafts", SCIENCE TRANSLATIONAL MEDICINE, March 2010 (2010-03-01);;FARNHAM, S.B.; COOKSON, M.S.: "Surgical complications of urinary diversion", WORLD JOURNAL OF UROLOGY, vol. 22, 2004, pages 157 - 167;;STEIN, J.P.: "Improving outcomes with radical cystectomy for high-grade invasive bladder cancer", WORLD JOURNAL OF UROLOGY, vol. 24, 2006, pages 509 - 516, XP019459685, DOI: doi:10.1007/s00345-006-0111-1;;KOUBA, E.; SANDS, M.; LENTZ, A.; WALLEN, E.; PRUTHI, R.S.: "Incidence and risk factors of stomal complications in patients undergoing cystectomy with ileal conduit urinary diversion for bladder cancer", JOURNAL OT UROLOGY, vol. 178, 2007, pages 950 - 954, XP022193343, DOI: doi:10.1016/j.juro.2007.05.028;;SHABSIGH, A.; KORETS, R.; VORA, K.C.; BROOKS, C.M.; CRONIN, A.M.; SAVAGE, C.; RAJ, G.; BOCHNER, B.H.; DALBAGNI, G.; HERR, H.W.: "Defining early morbidity of radical cystectomy for patients with bladder cancer using a standardized reporting methodology", EUROPEAN UROLOGY, vol. 55, 2009, pages 164 - 174;;NAZARKO, L.: "Urinary tract infection: diagnosis, treatment and prevention", BRITISH JOURNAL OF NURSING, vol. 18, 2009, pages 1170 - 1174;;LONGLEY, J.R.; RAVERA, J.; RIDDELL, O.; JETER, K.: "Carbon urinary conduits. Animal experiments", INVESTIGATIVE UROLOGY, vol. 15, 1977, pages 59 - 64;;MANSSON, W.; HARZMANN, R.: "Clinical experience with an alloplastic stoma prosthesis (Biocarbon) for urinary conduits and cutaneous ureterostomy", SCANDANAVIAN JOURNAL OF UROLOGY AND NEPHROLOGY, vol. 22, 1988, pages 223 - 226;;BASU, J.; GUTHRIE, K.; ILAGAN, R.; SANGHA, N.; GENHEIMER, C.; QUINLAN, S.; PAYNE, R.; RAPOPORT, S.; KNIGHT, T.; WAGNER, B.J.: "Functional de novo Neo-Urinary Conduit from Porcein peripheral blood and adipose-derived smooth muscle cells", 7TH ANNUAL ISSCR MEETING, 2009;;RAYA-RIVERA, A.; ESQUILLIANO, D.R.; YOO, J.J.; LOPEZ-BAYGHEN, E.; SOKER, S.; ATALA, A.: "Tissue-engineered autologous urethras for patients who need reconstruction: an observational study", LANCET, 7 March 2011 (2011-03-07);;EL-KASSABY, A.W.; RETIK, A.B.; YOO, J.J.; ATALA, A.: "Urethral stricture repair with an off-the-shelf collagen matrix", JOURNAL OF UROLOGY, vol. 169, 2003, pages 170 - 173, XP005536341, DOI: doi:10.1016/S0022-5347(05)64060-8;;BODIN, A.; BHARADWAJ, S.; WU, S.; GATENHOLM, P.; ATALA, A.; ZHANG, Y.: "Tissue-engineered conduti using urine-derived stem cells seeded bacterial cellulose polymer in urinary reconstuction and diversion", BIOMATERIALS, vol. 31, 2010, pages 88139 - 8901;;HIPP, J.; ANDERSSON, K.E.; KWON, T.G.; KWAK, E.K.; YOO, J.; ATALA, A.: "Microarray analysis of exstrophic human bladder smooth muscle", BJU INTERNATIONAL, vol. 101, 2008, pages 100 - 105;;KIM, B.S.; ATALA, A.; YOO, J.J.: "A collagen matrix derived from bladder can be used to engineer smooth muscle tissue", WORLD JOURNAL OF UROLOGY, vol. 26, 2008, pages 307 - 314, XP019627202;;TIAN, H.; BHARADWAJ, S.; LIU, Y.; MA, P.X.; ATALA, A.; ZHANG, Y.: "Differentiation of human bone marrow mesenchymal stem cells into bladder cells: potential for urological tissue engineering", TISSUE ENGINEERING PART A, vol. 16, 2010, pages 1769 - 1779;;DAHL, S.L.M.; KYPSON, A.P.; SAWSON, J.H.; BLUM, J.L.; STRADER, J.T.; LI, Y.; MANSON, R.J.; TENTE, W.E.; DIBERNARDO, L.; IIENSLEY,: "Readily available tissue-engineered vascular grafts", SCIENCE TRANSLATIONAL MEDICINE, 2011;;BACKHAUS, B.O.; KAEFER, M.; HABERSTROH, K.M.; HILE, K.; NAGATOMI, J.; RINK, R.C.; CAIN,, M.P.; CASALE, A.; BIZIOS, R.: "Alterations int he molecular determinants of bladder compliance at hydrostatic pressures less than 40 cm water", JOURNAL OF UROLOGY, vol. 168, 2002, pages 2600 - 2604;;HILES, M.C.; BADYLAK, S.F. ET AL.: "Porosity of porcine small-intestinal submucosa for use as a vascular graft", JOURNAL OF BIOMEDICAL MATERIALS RESEARCH, vol. 27, 1993, pages 139 - 144;;NIKLASON, L.E.; ABBOTT, W.A.; GAO, J.; KLAGGES, B.; HIRSCHI, K.K.; ULUBAYRAM, K.; CONROY, N.; JONES, R.; VASANAWALA, A.; SANZGIRI,: "Morphologic and mechanical characteristics of bovine engineered arteries", JOURNAL OF VASCULAR SURGERY, vol. 33, 2001, pages 628 - 638, XP002571215, DOI: doi:10.1067/mva.2001.111747;;WOESSNER, J.F.: "The determination (of hydroxyproline in tissue and protein samples containing small proportions of this amino acid", ARCHIVES OF BIOCHEMISTRY AND BIOPHYSICS, vol. 93, 1961, pages 440 - 447;;TAGUCHI, T.; IKOMA, T.; TANAKA, J.: "An improved method to prepare hyaluronic acid and type II collagne composite matrices", JOURNAL OF BIOMEDICAL MATERIALS RESEARCH, vol. 61, 2002, pages 330 - 336;;STEGMAN, S.J.; CHU, S.; BENSCH, K.; ARMSTRONG, R.: "A light and electron microscopic evaluation of Zyderm collagen and Zyplast implants in aging human facial skin. A pilot study", ARCHIVES DERMATOLOGY, vol. 123, 1987, pages 1644 - 1649;;SPINDEL, E.; PAULEY, M.; JIA, Y.; GRAVETT, C.; THOMPSON, S.; BOYLE, N.; OJEDA, S.; NORGREN, R.: "Leveraging human genomic information to identify nonhuman primate sequences for expression array development", BMC GENOMICS, vol. 6, 2005, pages 160, XP021002255, DOI: doi:10.1186/1471-2164-6-160</t>
+  </si>
+  <si>
+    <t>SALLY MARSHALL: "The Podocyte: a Potential Therapeutic Target in Diabetic Nephropathy?", CURRENT PHARMACEUTICAL DESIGN, vol. 13, no. 26, 1 September 2007 (2007-09-01), pages 2713-2720, XP055199663, ISSN: 1381-6128, DOI: 10.2174/138161207781662957;;O. SMITHIES: "Why the kidney glomerulus does not clog: A gel permeation/diffusion hypothesis of renal function", PROCEEDINGS NATIONAL ACADEMY OF SCIENCES PNAS, vol. 100, no. 7, 1 April 2003 (2003-04-01) , pages 4108-4113, XP055392518, US ISSN: 0027-8424, DOI: 10.1073/pnas.0730776100;;J. PATRAKKA: "The Number of Podocyte Slit Diaphragms Is Decreased in Minimal Change Nephrotic Syndrome", PEDIATRIC RESEARCH, vol. 52, no. 3, 21 August 2002 (2002-08-21), pages 349-355, XP055392665, US ISSN: 0031-3998, DOI: 10.1203/01.PDR.0000025285.72240.11</t>
+  </si>
+  <si>
+    <t>VAN DEN BERG, C. J. ET AL: "Inositol phosphates and phytic acid as inhibitors of biological calcification in the rat", CLINICAL SCIENCE , 43(3), 377-83 CODEN: CSCIAE; ISSN: 0143-5221, 1972, XP008042000;;GRASES, F. ET AL: "Phytate prevents tissue calcifications in female rats", BIOFACTORS , 11(3), 171-177 CODEN: BIFAEU; ISSN: 0951-6433, 2000, XP008041991;;GRASES, F. ET AL: "Effects of phytic acid on renal stone formation in rats", SCANDINAVIAN JOURNAL OF UROLOGY AND NEPHROLOGY , 32(4), 261-265 CODEN: SJUNAS; ISSN: 0036-5599, 1998, XP008041988;;KASTING G B ET AL: "SKIN PENETRATION ENHANCEMENT METHODS FOR HYDROPHILIC COMPOUNDS", PHARMACEUTICAL RESEARCH, NEW YORK, NY, US, vol. 14, no. 11, SUPPL, November 1997 (1997-11-01), pages S452, XP001105174, ISSN: 0724-8741;;GRASES, F. ET AL: "Dietary myo-inositol hexaphosphate prevents dystrophic calcifications in soft tissues: a pilot study in Wistar rats", LIFE SCIENCES , 75(1), 11-19 CODEN: LIFSAK; ISSN: 0024-3205, 2004, XP008041984</t>
+  </si>
+  <si>
+    <t>Aug 14, 2006</t>
+  </si>
+  <si>
+    <t>Feb 11, 2010</t>
+  </si>
+  <si>
+    <t>May 17, 1995</t>
+  </si>
+  <si>
+    <t>Jan 23, 2008</t>
+  </si>
+  <si>
+    <t>Nov 19, 2007</t>
+  </si>
+  <si>
+    <t>Sep 15, 2004</t>
+  </si>
+  <si>
+    <t>May 30, 2008</t>
+  </si>
+  <si>
+    <t>Apr 11, 1994</t>
+  </si>
+  <si>
+    <t>Apr 26, 2013</t>
+  </si>
+  <si>
+    <t>May 07, 2001</t>
+  </si>
+  <si>
+    <t>Apr 25, 1996</t>
+  </si>
+  <si>
+    <t>May 16, 2013</t>
+  </si>
+  <si>
+    <t>Nov 06, 2003</t>
+  </si>
+  <si>
+    <t>Mar 30, 2007</t>
+  </si>
+  <si>
+    <t>Mar 15, 2007</t>
+  </si>
+  <si>
+    <t>Jul 28, 2000</t>
+  </si>
+  <si>
+    <t>Jun 27, 2011</t>
+  </si>
+  <si>
+    <t>Feb 23, 2023</t>
+  </si>
+  <si>
+    <t>Dec 03, 2002</t>
+  </si>
+  <si>
+    <t>Aug 29, 2008</t>
+  </si>
+  <si>
+    <t>Mar 05, 2004</t>
+  </si>
+  <si>
+    <t>Feb 27, 2002</t>
+  </si>
+  <si>
+    <t>Jul 02, 2004</t>
+  </si>
+  <si>
+    <t>Jun 15, 2010</t>
+  </si>
+  <si>
+    <t>Jul 17, 2020</t>
+  </si>
+  <si>
+    <t>Nov 15, 2019</t>
+  </si>
+  <si>
+    <t>Nov 21, 2019</t>
+  </si>
+  <si>
+    <t>May 31, 2017</t>
+  </si>
+  <si>
+    <t>Jul 06, 2017</t>
+  </si>
+  <si>
+    <t>Nov 20, 2008</t>
+  </si>
+  <si>
+    <t>Dec 05, 2018</t>
+  </si>
+  <si>
+    <t>Dec 27, 2016</t>
+  </si>
+  <si>
+    <t>Sep 23, 2010</t>
+  </si>
+  <si>
+    <t>Mar 18, 2009</t>
+  </si>
+  <si>
+    <t>Jan 11, 2021</t>
+  </si>
+  <si>
+    <t>Dec 28, 2020</t>
+  </si>
+  <si>
+    <t>Apr 21, 1999</t>
+  </si>
+  <si>
+    <t>Sep 16, 2022</t>
+  </si>
+  <si>
+    <t>Mar 16, 2006</t>
+  </si>
+  <si>
+    <t>Oct 24, 2018</t>
+  </si>
+  <si>
+    <t>Jan 09, 2004</t>
+  </si>
+  <si>
+    <t>Jan 09, 2006</t>
+  </si>
+  <si>
+    <t>Oct 21, 2005</t>
+  </si>
+  <si>
+    <t>Jul 20, 2017</t>
+  </si>
+  <si>
+    <t>Nov 04, 2014</t>
+  </si>
+  <si>
+    <t>Oct 25, 2011</t>
+  </si>
+  <si>
+    <t>Oct 24, 2002</t>
+  </si>
+  <si>
+    <t>Oct 19, 2021</t>
+  </si>
+  <si>
+    <t>Jun 19, 2014</t>
+  </si>
+  <si>
+    <t>Apr 18, 2003</t>
+  </si>
+  <si>
+    <t>Dec 11, 2000</t>
+  </si>
+  <si>
+    <t>Nov 06, 2009</t>
+  </si>
+  <si>
+    <t>Mar 25, 2002</t>
+  </si>
+  <si>
+    <t>Dec 06, 2012</t>
+  </si>
+  <si>
+    <t>Jul 25, 2003</t>
+  </si>
+  <si>
+    <t>Jun 29, 2018</t>
+  </si>
+  <si>
+    <t>Mar 08, 2010</t>
+  </si>
+  <si>
+    <t>Mar 14, 2002</t>
+  </si>
+  <si>
+    <t>Apr 24, 2012</t>
+  </si>
+  <si>
+    <t>Aug 20, 2001</t>
+  </si>
+  <si>
+    <t>Apr 27, 2017</t>
+  </si>
+  <si>
+    <t>May 01, 2015</t>
+  </si>
+  <si>
+    <t>Apr 26, 2018</t>
+  </si>
+  <si>
+    <t>Sep 27, 2002</t>
+  </si>
+  <si>
+    <t>Oct 12, 2012</t>
+  </si>
+  <si>
+    <t>Oct 02, 2001</t>
+  </si>
+  <si>
+    <t>Oct 08, 1991</t>
+  </si>
+  <si>
+    <t>Dec 21, 1992</t>
+  </si>
+  <si>
+    <t>Oct 08, 1992</t>
+  </si>
+  <si>
+    <t>Jun 12, 2024</t>
+  </si>
+  <si>
+    <t>Apr 21, 2021</t>
+  </si>
+  <si>
+    <t>Nov 07, 2018</t>
+  </si>
+  <si>
+    <t>Feb 27, 2015</t>
+  </si>
+  <si>
+    <t>Jan 15, 2007</t>
+  </si>
+  <si>
+    <t>Oct 25, 2010</t>
+  </si>
+  <si>
+    <t>Feb 10, 1997</t>
+  </si>
+  <si>
+    <t>May 26, 2008</t>
+  </si>
+  <si>
+    <t>Feb 11, 2008</t>
+  </si>
+  <si>
+    <t>Apr 20, 2006</t>
+  </si>
+  <si>
+    <t>Dec 03, 2009</t>
+  </si>
+  <si>
+    <t>Jun 30, 1995</t>
+  </si>
+  <si>
+    <t>May 12, 2014</t>
+  </si>
+  <si>
+    <t>Nov 15, 2001</t>
+  </si>
+  <si>
+    <t>Sep 10, 1999</t>
+  </si>
+  <si>
+    <t>Mar 26, 2015</t>
+  </si>
+  <si>
+    <t>Nov 21, 2013</t>
+  </si>
+  <si>
+    <t>Aug 10, 2005</t>
+  </si>
+  <si>
+    <t>Mar 11, 2008</t>
+  </si>
+  <si>
+    <t>Nov 22, 2007</t>
+  </si>
+  <si>
+    <t>May 15, 2001</t>
+  </si>
+  <si>
+    <t>Oct 13, 2011</t>
+  </si>
+  <si>
+    <t>Aug 31, 2024</t>
+  </si>
+  <si>
+    <t>Jan 31, 2024</t>
+  </si>
+  <si>
+    <t>Aug 10, 2004</t>
+  </si>
+  <si>
+    <t>Apr 30, 2009</t>
+  </si>
+  <si>
+    <t>Aug 17, 2006</t>
+  </si>
+  <si>
+    <t>Feb 20, 2003</t>
+  </si>
+  <si>
+    <t>Apr 02, 2013</t>
+  </si>
+  <si>
+    <t>Feb 27, 2006</t>
+  </si>
+  <si>
+    <t>Jan 20, 2012</t>
+  </si>
+  <si>
+    <t>Aug 04, 2009</t>
+  </si>
+  <si>
+    <t>Jan 21, 2021</t>
+  </si>
+  <si>
+    <t>Sep 10, 2021</t>
+  </si>
+  <si>
+    <t>Mar 29, 2018</t>
+  </si>
+  <si>
+    <t>May 21, 2009</t>
+  </si>
+  <si>
+    <t>Jun 14, 2019</t>
+  </si>
+  <si>
+    <t>Mar 31, 2011</t>
+  </si>
+  <si>
+    <t>Jul 15, 2021</t>
+  </si>
+  <si>
+    <t>Nov 03, 2021</t>
+  </si>
+  <si>
+    <t>Sep 08, 2009</t>
+  </si>
+  <si>
+    <t>Mar 21, 2024</t>
+  </si>
+  <si>
+    <t>Aug 03, 2006</t>
+  </si>
+  <si>
+    <t>Oct 04, 2019</t>
+  </si>
+  <si>
+    <t>Jun 27, 2006</t>
+  </si>
+  <si>
+    <t>Nov 16, 2023</t>
+  </si>
+  <si>
+    <t>Jul 15, 2004</t>
+  </si>
+  <si>
+    <t>Jan 25, 2018</t>
+  </si>
+  <si>
+    <t>Sep 14, 2016</t>
+  </si>
+  <si>
+    <t>Oct 28, 1999</t>
+  </si>
+  <si>
+    <t>May 03, 2012</t>
+  </si>
+  <si>
+    <t>Aug 21, 2003</t>
+  </si>
+  <si>
+    <t>Sep 02, 2014</t>
+  </si>
+  <si>
+    <t>Mar 24, 2022</t>
+  </si>
+  <si>
+    <t>Oct 10, 2019</t>
+  </si>
+  <si>
+    <t>Mar 10, 2005</t>
+  </si>
+  <si>
+    <t>Feb 24, 2004</t>
+  </si>
+  <si>
+    <t>Feb 20, 2011</t>
+  </si>
+  <si>
+    <t>Jul 03, 2003</t>
+  </si>
+  <si>
+    <t>Feb 05, 2004</t>
+  </si>
+  <si>
+    <t>Apr 08, 2004</t>
+  </si>
+  <si>
+    <t>Apr 23, 2020</t>
+  </si>
+  <si>
+    <t>Sep 15, 2010</t>
+  </si>
+  <si>
+    <t>May 22, 2003</t>
+  </si>
+  <si>
+    <t>Jul 20, 2013</t>
+  </si>
+  <si>
+    <t>Jan 03, 2019</t>
+  </si>
+  <si>
+    <t>Oct 31, 2018</t>
+  </si>
+  <si>
+    <t>Nov 05, 2015</t>
+  </si>
+  <si>
+    <t>Feb 13, 2020</t>
+  </si>
+  <si>
+    <t>Sep 05, 2023</t>
+  </si>
+  <si>
+    <t>Mar 06, 2003</t>
+  </si>
+  <si>
+    <t>Jun 15, 2004</t>
+  </si>
+  <si>
+    <t>Nov 01, 2018</t>
+  </si>
+  <si>
+    <t>Jan 16, 2019</t>
+  </si>
+  <si>
+    <t>Sep 12, 2002</t>
+  </si>
+  <si>
+    <t>Dec 16, 1997</t>
+  </si>
+  <si>
+    <t>Jul 08, 1993</t>
+  </si>
+  <si>
+    <t>Dec 14, 2022</t>
+  </si>
+  <si>
+    <t>Sep 09, 1998</t>
+  </si>
+  <si>
+    <t>Apr 15, 1993</t>
+  </si>
+  <si>
+    <t>Mar 06, 2025</t>
+  </si>
+  <si>
+    <t>Aug 05, 2021</t>
+  </si>
+  <si>
+    <t>Mar 22, 2007</t>
+  </si>
+  <si>
+    <t>Apr 18, 2013</t>
+  </si>
+  <si>
+    <t>Sep 03, 2015</t>
+  </si>
+  <si>
+    <t>May 19, 2005</t>
   </si>
 </sst>
 </file>
@@ -9635,7 +11177,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9645,7 +11187,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -10002,7 +11543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8878ED64-6124-4A8A-8267-25992F4A017A}">
-  <dimension ref="A1:O501"/>
+  <dimension ref="A1:O601"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.77734375" customWidth="1"/>
@@ -15424,7 +16965,7 @@
         <v>787</v>
       </c>
       <c r="M119" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="N119" t="s">
         <v>24</v>
@@ -17958,7 +19499,7 @@
         <v>787</v>
       </c>
       <c r="M186" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="N186" t="s">
         <v>24</v>
@@ -22694,7 +24235,7 @@
       <c r="J312" s="6" t="s">
         <v>2607</v>
       </c>
-      <c r="K312" s="7" t="s">
+      <c r="K312" t="s">
         <v>1222</v>
       </c>
       <c r="L312" t="s">
@@ -22770,7 +24311,7 @@
       <c r="J314" s="6" t="s">
         <v>2608</v>
       </c>
-      <c r="K314" s="7" t="s">
+      <c r="K314" t="s">
         <v>1222</v>
       </c>
       <c r="L314" t="s">
@@ -22808,7 +24349,7 @@
       <c r="J315" s="6" t="s">
         <v>2609</v>
       </c>
-      <c r="K315" s="7" t="s">
+      <c r="K315" t="s">
         <v>1222</v>
       </c>
       <c r="L315" t="s">
@@ -22846,7 +24387,7 @@
       <c r="J316" s="6" t="s">
         <v>1833</v>
       </c>
-      <c r="K316" s="7" t="s">
+      <c r="K316" t="s">
         <v>1222</v>
       </c>
       <c r="L316" t="s">
@@ -22922,7 +24463,7 @@
       <c r="J318" s="6" t="s">
         <v>2611</v>
       </c>
-      <c r="K318" s="7" t="s">
+      <c r="K318" t="s">
         <v>1222</v>
       </c>
       <c r="L318" t="s">
@@ -22960,7 +24501,7 @@
       <c r="J319" s="6" t="s">
         <v>1800</v>
       </c>
-      <c r="K319" s="7" t="s">
+      <c r="K319" t="s">
         <v>1222</v>
       </c>
       <c r="L319" t="s">
@@ -22998,7 +24539,7 @@
       <c r="J320" s="6" t="s">
         <v>2612</v>
       </c>
-      <c r="K320" s="7" t="s">
+      <c r="K320" t="s">
         <v>1222</v>
       </c>
       <c r="L320" t="s">
@@ -23036,7 +24577,7 @@
       <c r="J321" s="6" t="s">
         <v>2613</v>
       </c>
-      <c r="K321" s="7" t="s">
+      <c r="K321" t="s">
         <v>1222</v>
       </c>
       <c r="L321" t="s">
@@ -23074,7 +24615,7 @@
       <c r="J322" s="6" t="s">
         <v>1832</v>
       </c>
-      <c r="K322" s="7" t="s">
+      <c r="K322" t="s">
         <v>1222</v>
       </c>
       <c r="L322" t="s">
@@ -23112,7 +24653,7 @@
       <c r="J323" s="6" t="s">
         <v>2614</v>
       </c>
-      <c r="K323" s="7" t="s">
+      <c r="K323" t="s">
         <v>1222</v>
       </c>
       <c r="L323" t="s">
@@ -23150,7 +24691,7 @@
       <c r="J324" s="6" t="s">
         <v>2615</v>
       </c>
-      <c r="K324" s="7" t="s">
+      <c r="K324" t="s">
         <v>1222</v>
       </c>
       <c r="L324" t="s">
@@ -23188,7 +24729,7 @@
       <c r="J325" s="6" t="s">
         <v>2616</v>
       </c>
-      <c r="K325" s="7" t="s">
+      <c r="K325" t="s">
         <v>1222</v>
       </c>
       <c r="L325" t="s">
@@ -23226,7 +24767,7 @@
       <c r="J326" s="6" t="s">
         <v>2617</v>
       </c>
-      <c r="K326" s="7" t="s">
+      <c r="K326" t="s">
         <v>1222</v>
       </c>
       <c r="L326" t="s">
@@ -23264,7 +24805,7 @@
       <c r="J327" s="6" t="s">
         <v>2618</v>
       </c>
-      <c r="K327" s="7" t="s">
+      <c r="K327" t="s">
         <v>1222</v>
       </c>
       <c r="L327" t="s">
@@ -23340,7 +24881,7 @@
       <c r="J329" s="6" t="s">
         <v>2620</v>
       </c>
-      <c r="K329" s="7" t="s">
+      <c r="K329" t="s">
         <v>1222</v>
       </c>
       <c r="L329" t="s">
@@ -23378,7 +24919,7 @@
       <c r="J330" s="6" t="s">
         <v>2621</v>
       </c>
-      <c r="K330" s="7" t="s">
+      <c r="K330" t="s">
         <v>1222</v>
       </c>
       <c r="L330" t="s">
@@ -23416,7 +24957,7 @@
       <c r="J331" s="6" t="s">
         <v>2622</v>
       </c>
-      <c r="K331" s="7" t="s">
+      <c r="K331" t="s">
         <v>1222</v>
       </c>
       <c r="L331" t="s">
@@ -23454,7 +24995,7 @@
       <c r="J332" s="6" t="s">
         <v>2578</v>
       </c>
-      <c r="K332" s="7" t="s">
+      <c r="K332" t="s">
         <v>1222</v>
       </c>
       <c r="L332" t="s">
@@ -23492,7 +25033,7 @@
       <c r="J333" s="6" t="s">
         <v>2623</v>
       </c>
-      <c r="K333" s="7" t="s">
+      <c r="K333" t="s">
         <v>1222</v>
       </c>
       <c r="L333" t="s">
@@ -23530,7 +25071,7 @@
       <c r="J334" s="6" t="s">
         <v>2616</v>
       </c>
-      <c r="K334" s="7" t="s">
+      <c r="K334" t="s">
         <v>1222</v>
       </c>
       <c r="L334" t="s">
@@ -23568,7 +25109,7 @@
       <c r="J335" s="6" t="s">
         <v>2624</v>
       </c>
-      <c r="K335" s="7" t="s">
+      <c r="K335" t="s">
         <v>1222</v>
       </c>
       <c r="L335" t="s">
@@ -23606,7 +25147,7 @@
       <c r="J336" s="6" t="s">
         <v>1819</v>
       </c>
-      <c r="K336" s="7" t="s">
+      <c r="K336" t="s">
         <v>1222</v>
       </c>
       <c r="L336" t="s">
@@ -23644,7 +25185,7 @@
       <c r="J337" s="6" t="s">
         <v>2625</v>
       </c>
-      <c r="K337" s="7" t="s">
+      <c r="K337" t="s">
         <v>1222</v>
       </c>
       <c r="L337" t="s">
@@ -23682,7 +25223,7 @@
       <c r="J338" s="6" t="s">
         <v>2626</v>
       </c>
-      <c r="K338" s="7" t="s">
+      <c r="K338" t="s">
         <v>1222</v>
       </c>
       <c r="L338" t="s">
@@ -23758,7 +25299,7 @@
       <c r="J340" s="6" t="s">
         <v>2607</v>
       </c>
-      <c r="K340" s="7" t="s">
+      <c r="K340" t="s">
         <v>1222</v>
       </c>
       <c r="L340" t="s">
@@ -23793,7 +25334,7 @@
       <c r="J341" s="6" t="s">
         <v>2628</v>
       </c>
-      <c r="K341" s="7" t="s">
+      <c r="K341" t="s">
         <v>2229</v>
       </c>
       <c r="L341" t="s">
@@ -23831,7 +25372,7 @@
       <c r="J342" s="6" t="s">
         <v>2629</v>
       </c>
-      <c r="K342" s="7" t="s">
+      <c r="K342" t="s">
         <v>1222</v>
       </c>
       <c r="L342" t="s">
@@ -23869,7 +25410,7 @@
       <c r="J343" s="6" t="s">
         <v>2630</v>
       </c>
-      <c r="K343" s="7" t="s">
+      <c r="K343" t="s">
         <v>1222</v>
       </c>
       <c r="L343" t="s">
@@ -23945,7 +25486,7 @@
       <c r="J345" s="6" t="s">
         <v>2632</v>
       </c>
-      <c r="K345" s="7" t="s">
+      <c r="K345" t="s">
         <v>1222</v>
       </c>
       <c r="L345" t="s">
@@ -23983,7 +25524,7 @@
       <c r="J346" s="6" t="s">
         <v>2633</v>
       </c>
-      <c r="K346" s="7" t="s">
+      <c r="K346" t="s">
         <v>1222</v>
       </c>
       <c r="L346" t="s">
@@ -24059,7 +25600,7 @@
       <c r="J348" s="6" t="s">
         <v>2635</v>
       </c>
-      <c r="K348" s="7" t="s">
+      <c r="K348" t="s">
         <v>1222</v>
       </c>
       <c r="L348" t="s">
@@ -24135,7 +25676,7 @@
       <c r="J350" s="6" t="s">
         <v>2637</v>
       </c>
-      <c r="K350" s="7" t="s">
+      <c r="K350" t="s">
         <v>1222</v>
       </c>
       <c r="L350" t="s">
@@ -24173,7 +25714,7 @@
       <c r="J351" s="6" t="s">
         <v>2638</v>
       </c>
-      <c r="K351" s="7" t="s">
+      <c r="K351" t="s">
         <v>1222</v>
       </c>
       <c r="L351" t="s">
@@ -24325,7 +25866,7 @@
       <c r="J355" s="6" t="s">
         <v>2642</v>
       </c>
-      <c r="K355" s="7" t="s">
+      <c r="K355" t="s">
         <v>1222</v>
       </c>
       <c r="L355" t="s">
@@ -24363,7 +25904,7 @@
       <c r="J356" s="6" t="s">
         <v>2643</v>
       </c>
-      <c r="K356" s="7" t="s">
+      <c r="K356" t="s">
         <v>1222</v>
       </c>
       <c r="L356" t="s">
@@ -24401,7 +25942,7 @@
       <c r="J357" s="6" t="s">
         <v>2644</v>
       </c>
-      <c r="K357" s="7" t="s">
+      <c r="K357" t="s">
         <v>1222</v>
       </c>
       <c r="L357" t="s">
@@ -24515,7 +26056,7 @@
       <c r="J360" s="6" t="s">
         <v>2590</v>
       </c>
-      <c r="K360" s="7" t="s">
+      <c r="K360" t="s">
         <v>1222</v>
       </c>
       <c r="L360" t="s">
@@ -24591,7 +26132,7 @@
       <c r="J362" s="6" t="s">
         <v>2648</v>
       </c>
-      <c r="K362" s="7" t="s">
+      <c r="K362" t="s">
         <v>1222</v>
       </c>
       <c r="L362" t="s">
@@ -24667,7 +26208,7 @@
       <c r="J364" s="6" t="s">
         <v>2650</v>
       </c>
-      <c r="K364" s="7" t="s">
+      <c r="K364" t="s">
         <v>1222</v>
       </c>
       <c r="L364" t="s">
@@ -24705,7 +26246,7 @@
       <c r="J365" s="6" t="s">
         <v>2651</v>
       </c>
-      <c r="K365" s="7" t="s">
+      <c r="K365" t="s">
         <v>1222</v>
       </c>
       <c r="L365" t="s">
@@ -24743,7 +26284,7 @@
       <c r="J366" s="6" t="s">
         <v>2652</v>
       </c>
-      <c r="K366" s="7" t="s">
+      <c r="K366" t="s">
         <v>1222</v>
       </c>
       <c r="L366" t="s">
@@ -24781,7 +26322,7 @@
       <c r="J367" s="6" t="s">
         <v>2653</v>
       </c>
-      <c r="K367" s="7" t="s">
+      <c r="K367" t="s">
         <v>1222</v>
       </c>
       <c r="L367" t="s">
@@ -24819,7 +26360,7 @@
       <c r="J368" s="6" t="s">
         <v>2654</v>
       </c>
-      <c r="K368" s="7" t="s">
+      <c r="K368" t="s">
         <v>1222</v>
       </c>
       <c r="L368" t="s">
@@ -24857,7 +26398,7 @@
       <c r="J369" s="6" t="s">
         <v>2616</v>
       </c>
-      <c r="K369" s="7" t="s">
+      <c r="K369" t="s">
         <v>1222</v>
       </c>
       <c r="L369" t="s">
@@ -24895,7 +26436,7 @@
       <c r="J370" s="6" t="s">
         <v>2655</v>
       </c>
-      <c r="K370" s="7" t="s">
+      <c r="K370" t="s">
         <v>1222</v>
       </c>
       <c r="L370" t="s">
@@ -24933,7 +26474,7 @@
       <c r="J371" s="6" t="s">
         <v>2656</v>
       </c>
-      <c r="K371" s="7" t="s">
+      <c r="K371" t="s">
         <v>1222</v>
       </c>
       <c r="L371" t="s">
@@ -24971,7 +26512,7 @@
       <c r="J372" s="6" t="s">
         <v>1832</v>
       </c>
-      <c r="K372" s="7" t="s">
+      <c r="K372" t="s">
         <v>1222</v>
       </c>
       <c r="L372" t="s">
@@ -25009,7 +26550,7 @@
       <c r="J373" s="6" t="s">
         <v>2657</v>
       </c>
-      <c r="K373" s="7" t="s">
+      <c r="K373" t="s">
         <v>1222</v>
       </c>
       <c r="L373" t="s">
@@ -25085,7 +26626,7 @@
       <c r="J375" s="6" t="s">
         <v>2621</v>
       </c>
-      <c r="K375" s="7" t="s">
+      <c r="K375" t="s">
         <v>1222</v>
       </c>
       <c r="L375" t="s">
@@ -25123,7 +26664,7 @@
       <c r="J376" s="6" t="s">
         <v>2659</v>
       </c>
-      <c r="K376" s="7" t="s">
+      <c r="K376" t="s">
         <v>1222</v>
       </c>
       <c r="L376" t="s">
@@ -25161,7 +26702,7 @@
       <c r="J377" s="6" t="s">
         <v>2660</v>
       </c>
-      <c r="K377" s="7" t="s">
+      <c r="K377" t="s">
         <v>1222</v>
       </c>
       <c r="L377" t="s">
@@ -25199,7 +26740,7 @@
       <c r="J378" s="6" t="s">
         <v>2661</v>
       </c>
-      <c r="K378" s="7" t="s">
+      <c r="K378" t="s">
         <v>1222</v>
       </c>
       <c r="L378" t="s">
@@ -25237,7 +26778,7 @@
       <c r="J379" s="6" t="s">
         <v>1847</v>
       </c>
-      <c r="K379" s="7" t="s">
+      <c r="K379" t="s">
         <v>1222</v>
       </c>
       <c r="L379" t="s">
@@ -25275,7 +26816,7 @@
       <c r="J380" s="6" t="s">
         <v>2662</v>
       </c>
-      <c r="K380" s="7" t="s">
+      <c r="K380" t="s">
         <v>1222</v>
       </c>
       <c r="L380" t="s">
@@ -25313,7 +26854,7 @@
       <c r="J381" s="6" t="s">
         <v>2663</v>
       </c>
-      <c r="K381" s="7" t="s">
+      <c r="K381" t="s">
         <v>1222</v>
       </c>
       <c r="L381" t="s">
@@ -25351,7 +26892,7 @@
       <c r="J382" s="6" t="s">
         <v>2620</v>
       </c>
-      <c r="K382" s="7" t="s">
+      <c r="K382" t="s">
         <v>1222</v>
       </c>
       <c r="L382" t="s">
@@ -25427,7 +26968,7 @@
       <c r="J384" s="6" t="s">
         <v>2665</v>
       </c>
-      <c r="K384" s="7" t="s">
+      <c r="K384" t="s">
         <v>1222</v>
       </c>
       <c r="L384" t="s">
@@ -25465,7 +27006,7 @@
       <c r="J385" s="6" t="s">
         <v>2666</v>
       </c>
-      <c r="K385" s="7" t="s">
+      <c r="K385" t="s">
         <v>1222</v>
       </c>
       <c r="L385" t="s">
@@ -25503,7 +27044,7 @@
       <c r="J386" s="6" t="s">
         <v>2660</v>
       </c>
-      <c r="K386" s="7" t="s">
+      <c r="K386" t="s">
         <v>1222</v>
       </c>
       <c r="L386" t="s">
@@ -25541,7 +27082,7 @@
       <c r="J387" s="6" t="s">
         <v>2667</v>
       </c>
-      <c r="K387" s="7" t="s">
+      <c r="K387" t="s">
         <v>1222</v>
       </c>
       <c r="L387" t="s">
@@ -25617,7 +27158,7 @@
       <c r="J389" s="6" t="s">
         <v>2669</v>
       </c>
-      <c r="K389" s="7" t="s">
+      <c r="K389" t="s">
         <v>1222</v>
       </c>
       <c r="L389" t="s">
@@ -25655,7 +27196,7 @@
       <c r="J390" s="6" t="s">
         <v>2670</v>
       </c>
-      <c r="K390" s="7" t="s">
+      <c r="K390" t="s">
         <v>1222</v>
       </c>
       <c r="L390" t="s">
@@ -25693,7 +27234,7 @@
       <c r="J391" s="6" t="s">
         <v>2671</v>
       </c>
-      <c r="K391" s="7" t="s">
+      <c r="K391" t="s">
         <v>1222</v>
       </c>
       <c r="L391" t="s">
@@ -25731,7 +27272,7 @@
       <c r="J392" s="6" t="s">
         <v>2672</v>
       </c>
-      <c r="K392" s="7" t="s">
+      <c r="K392" t="s">
         <v>1222</v>
       </c>
       <c r="L392" t="s">
@@ -25769,7 +27310,7 @@
       <c r="J393" s="6" t="s">
         <v>2673</v>
       </c>
-      <c r="K393" s="7" t="s">
+      <c r="K393" t="s">
         <v>1222</v>
       </c>
       <c r="L393" t="s">
@@ -25807,7 +27348,7 @@
       <c r="J394" s="6" t="s">
         <v>2674</v>
       </c>
-      <c r="K394" s="7" t="s">
+      <c r="K394" t="s">
         <v>1222</v>
       </c>
       <c r="L394" t="s">
@@ -25845,7 +27386,7 @@
       <c r="J395" s="6" t="s">
         <v>2675</v>
       </c>
-      <c r="K395" s="7" t="s">
+      <c r="K395" t="s">
         <v>1222</v>
       </c>
       <c r="L395" t="s">
@@ -25883,7 +27424,7 @@
       <c r="J396" s="6" t="s">
         <v>2676</v>
       </c>
-      <c r="K396" s="7" t="s">
+      <c r="K396" t="s">
         <v>1222</v>
       </c>
       <c r="L396" t="s">
@@ -25921,7 +27462,7 @@
       <c r="J397" s="6" t="s">
         <v>2656</v>
       </c>
-      <c r="K397" s="7" t="s">
+      <c r="K397" t="s">
         <v>1222</v>
       </c>
       <c r="L397" t="s">
@@ -25959,7 +27500,7 @@
       <c r="J398" s="6" t="s">
         <v>2677</v>
       </c>
-      <c r="K398" s="7" t="s">
+      <c r="K398" t="s">
         <v>1222</v>
       </c>
       <c r="L398" t="s">
@@ -25997,7 +27538,7 @@
       <c r="J399" s="6" t="s">
         <v>2678</v>
       </c>
-      <c r="K399" s="7" t="s">
+      <c r="K399" t="s">
         <v>1222</v>
       </c>
       <c r="L399" t="s">
@@ -26035,7 +27576,7 @@
       <c r="J400" s="6" t="s">
         <v>2679</v>
       </c>
-      <c r="K400" s="7" t="s">
+      <c r="K400" t="s">
         <v>1222</v>
       </c>
       <c r="L400" t="s">
@@ -26070,7 +27611,7 @@
       <c r="J401" s="6" t="s">
         <v>2680</v>
       </c>
-      <c r="K401" s="7" t="s">
+      <c r="K401" t="s">
         <v>1222</v>
       </c>
       <c r="L401" t="s">
@@ -26135,7 +27676,7 @@
         <v>2392</v>
       </c>
       <c r="D403" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="G403" t="s">
         <v>2454</v>
@@ -26188,7 +27729,7 @@
         <v>1224</v>
       </c>
       <c r="L404" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="M404" t="s">
         <v>63</v>
@@ -26264,7 +27805,7 @@
         <v>1223</v>
       </c>
       <c r="L406" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="M406" t="s">
         <v>63</v>
@@ -26340,7 +27881,7 @@
         <v>1223</v>
       </c>
       <c r="L408" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="M408" t="s">
         <v>63</v>
@@ -26401,7 +27942,7 @@
         <v>2392</v>
       </c>
       <c r="D410" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="G410" t="s">
         <v>2459</v>
@@ -26454,7 +27995,7 @@
         <v>1223</v>
       </c>
       <c r="L411" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="M411" t="s">
         <v>63</v>
@@ -26477,7 +28018,7 @@
         <v>2392</v>
       </c>
       <c r="D412" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="G412" t="s">
         <v>2461</v>
@@ -26568,7 +28109,7 @@
         <v>1223</v>
       </c>
       <c r="L414" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="M414" t="s">
         <v>63</v>
@@ -26606,7 +28147,7 @@
         <v>1223</v>
       </c>
       <c r="L415" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="M415" t="s">
         <v>1657</v>
@@ -26682,7 +28223,7 @@
         <v>1223</v>
       </c>
       <c r="L417" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="M417" t="s">
         <v>63</v>
@@ -26971,7 +28512,7 @@
         <v>2392</v>
       </c>
       <c r="D425" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="G425" t="s">
         <v>2461</v>
@@ -26986,7 +28527,7 @@
         <v>1223</v>
       </c>
       <c r="L425" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="M425" t="s">
         <v>135</v>
@@ -27196,7 +28737,7 @@
         <v>2392</v>
       </c>
       <c r="D431" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="G431" t="s">
         <v>2472</v>
@@ -27363,7 +28904,7 @@
         <v>1223</v>
       </c>
       <c r="L435" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="M435" t="s">
         <v>30</v>
@@ -27401,7 +28942,7 @@
         <v>1223</v>
       </c>
       <c r="L436" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="M436" t="s">
         <v>63</v>
@@ -27424,7 +28965,7 @@
         <v>2392</v>
       </c>
       <c r="D437" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="G437" t="s">
         <v>2454</v>
@@ -27439,7 +28980,7 @@
         <v>1223</v>
       </c>
       <c r="L437" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="M437" t="s">
         <v>63</v>
@@ -27515,7 +29056,7 @@
         <v>1223</v>
       </c>
       <c r="L439" t="s">
-        <v>2863</v>
+        <v>3187</v>
       </c>
       <c r="M439" t="s">
         <v>63</v>
@@ -27553,7 +29094,7 @@
         <v>1223</v>
       </c>
       <c r="L440" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
       <c r="M440" t="s">
         <v>63</v>
@@ -27778,7 +29319,7 @@
         <v>1224</v>
       </c>
       <c r="L446" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="M446" t="s">
         <v>1657</v>
@@ -27816,7 +29357,7 @@
         <v>1223</v>
       </c>
       <c r="L447" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="M447" t="s">
         <v>63</v>
@@ -27874,7 +29415,7 @@
         <v>2392</v>
       </c>
       <c r="D449" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="G449" t="s">
         <v>2480</v>
@@ -27892,7 +29433,7 @@
         <v>787</v>
       </c>
       <c r="M449" t="s">
-        <v>2838</v>
+        <v>3196</v>
       </c>
       <c r="N449" t="s">
         <v>24</v>
@@ -28003,7 +29544,7 @@
         <v>1223</v>
       </c>
       <c r="L452" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="M452" t="s">
         <v>63</v>
@@ -28064,7 +29605,7 @@
         <v>2392</v>
       </c>
       <c r="D454" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="G454" t="s">
         <v>2482</v>
@@ -28102,7 +29643,7 @@
         <v>2392</v>
       </c>
       <c r="D455" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="G455" t="s">
         <v>2483</v>
@@ -28155,7 +29696,7 @@
         <v>1224</v>
       </c>
       <c r="L456" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
       <c r="M456" t="s">
         <v>63</v>
@@ -28193,7 +29734,7 @@
         <v>1223</v>
       </c>
       <c r="L457" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="M457" t="s">
         <v>135</v>
@@ -28304,7 +29845,7 @@
         <v>1223</v>
       </c>
       <c r="L460" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="M460" t="s">
         <v>30</v>
@@ -28342,7 +29883,7 @@
         <v>1223</v>
       </c>
       <c r="L461" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
       <c r="M461" t="s">
         <v>63</v>
@@ -28532,7 +30073,7 @@
         <v>1223</v>
       </c>
       <c r="L466" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
       <c r="M466" t="s">
         <v>30</v>
@@ -28681,7 +30222,7 @@
         <v>1223</v>
       </c>
       <c r="L470" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
       <c r="M470" t="s">
         <v>63</v>
@@ -28742,7 +30283,7 @@
         <v>2392</v>
       </c>
       <c r="D472" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="G472" t="s">
         <v>2454</v>
@@ -28833,7 +30374,7 @@
         <v>1223</v>
       </c>
       <c r="L474" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="M474" t="s">
         <v>63</v>
@@ -29040,13 +30581,13 @@
         <v>2297</v>
       </c>
       <c r="B480" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="C480" t="s">
         <v>2392</v>
       </c>
       <c r="D480" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="G480" t="s">
         <v>2498</v>
@@ -29057,14 +30598,14 @@
       <c r="J480" s="6" t="s">
         <v>2819</v>
       </c>
-      <c r="K480" s="7" t="s">
+      <c r="K480" t="s">
         <v>1222</v>
       </c>
       <c r="L480" t="s">
         <v>787</v>
       </c>
       <c r="M480" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="N480" t="s">
         <v>24</v>
@@ -29137,7 +30678,7 @@
         <v>1223</v>
       </c>
       <c r="L482" t="s">
-        <v>2875</v>
+        <v>2873</v>
       </c>
       <c r="M482" t="s">
         <v>63</v>
@@ -29289,7 +30830,7 @@
         <v>1224</v>
       </c>
       <c r="L486" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
       <c r="M486" t="s">
         <v>30</v>
@@ -29312,7 +30853,7 @@
         <v>2392</v>
       </c>
       <c r="D487" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="G487" t="s">
         <v>2501</v>
@@ -29388,7 +30929,7 @@
         <v>2392</v>
       </c>
       <c r="D489" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="G489" t="s">
         <v>2461</v>
@@ -29403,7 +30944,7 @@
         <v>1223</v>
       </c>
       <c r="L489" t="s">
-        <v>2877</v>
+        <v>2875</v>
       </c>
       <c r="M489" t="s">
         <v>63</v>
@@ -29479,7 +31020,7 @@
         <v>1223</v>
       </c>
       <c r="L491" t="s">
-        <v>2878</v>
+        <v>2876</v>
       </c>
       <c r="M491" t="s">
         <v>63</v>
@@ -29540,7 +31081,7 @@
         <v>2392</v>
       </c>
       <c r="D493" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="G493" t="s">
         <v>2504</v>
@@ -29555,7 +31096,7 @@
         <v>1223</v>
       </c>
       <c r="L493" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="M493" t="s">
         <v>135</v>
@@ -29666,7 +31207,7 @@
         <v>1224</v>
       </c>
       <c r="L496" t="s">
-        <v>2880</v>
+        <v>2878</v>
       </c>
       <c r="M496" t="s">
         <v>63</v>
@@ -29841,7 +31382,7 @@
         <v>2392</v>
       </c>
       <c r="D501" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="G501" t="s">
         <v>2504</v>
@@ -29866,6 +31407,3788 @@
       </c>
       <c r="O501">
         <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B502" t="s">
+        <v>2970</v>
+      </c>
+      <c r="C502" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D502" t="s">
+        <v>3048</v>
+      </c>
+      <c r="G502" t="s">
+        <v>3186</v>
+      </c>
+      <c r="I502" s="6" t="s">
+        <v>3240</v>
+      </c>
+      <c r="J502" s="6" t="s">
+        <v>3313</v>
+      </c>
+      <c r="K502" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L502" t="s">
+        <v>787</v>
+      </c>
+      <c r="M502" t="s">
+        <v>30</v>
+      </c>
+      <c r="N502" t="s">
+        <v>24</v>
+      </c>
+      <c r="O502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B503" t="s">
+        <v>2971</v>
+      </c>
+      <c r="C503" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D503" t="s">
+        <v>3049</v>
+      </c>
+      <c r="G503" t="s">
+        <v>3185</v>
+      </c>
+      <c r="I503" s="6" t="s">
+        <v>3241</v>
+      </c>
+      <c r="J503" s="6" t="s">
+        <v>3314</v>
+      </c>
+      <c r="K503" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L503" t="s">
+        <v>787</v>
+      </c>
+      <c r="M503" t="s">
+        <v>30</v>
+      </c>
+      <c r="N503" t="s">
+        <v>24</v>
+      </c>
+      <c r="O503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B504" t="s">
+        <v>2972</v>
+      </c>
+      <c r="C504" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D504" t="s">
+        <v>3050</v>
+      </c>
+      <c r="G504" t="s">
+        <v>3184</v>
+      </c>
+      <c r="I504" s="6" t="s">
+        <v>3242</v>
+      </c>
+      <c r="J504" s="6" t="s">
+        <v>3315</v>
+      </c>
+      <c r="K504" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L504" t="s">
+        <v>787</v>
+      </c>
+      <c r="M504" t="s">
+        <v>30</v>
+      </c>
+      <c r="N504" t="s">
+        <v>24</v>
+      </c>
+      <c r="O504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B505" t="s">
+        <v>2973</v>
+      </c>
+      <c r="C505" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D505" t="s">
+        <v>3051</v>
+      </c>
+      <c r="G505" t="s">
+        <v>3183</v>
+      </c>
+      <c r="I505" s="6" t="s">
+        <v>3243</v>
+      </c>
+      <c r="J505" s="6" t="s">
+        <v>3316</v>
+      </c>
+      <c r="K505" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L505" t="s">
+        <v>787</v>
+      </c>
+      <c r="M505" t="s">
+        <v>30</v>
+      </c>
+      <c r="N505" t="s">
+        <v>24</v>
+      </c>
+      <c r="O505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B506" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C506" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D506" t="s">
+        <v>3052</v>
+      </c>
+      <c r="G506" t="s">
+        <v>3182</v>
+      </c>
+      <c r="I506" s="6" t="s">
+        <v>3244</v>
+      </c>
+      <c r="J506" s="6" t="s">
+        <v>3317</v>
+      </c>
+      <c r="K506" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L506" t="s">
+        <v>787</v>
+      </c>
+      <c r="M506" t="s">
+        <v>30</v>
+      </c>
+      <c r="N506" t="s">
+        <v>24</v>
+      </c>
+      <c r="O506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B507" t="s">
+        <v>2975</v>
+      </c>
+      <c r="C507" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D507" t="s">
+        <v>3053</v>
+      </c>
+      <c r="G507" t="s">
+        <v>3181</v>
+      </c>
+      <c r="I507" s="6" t="s">
+        <v>3245</v>
+      </c>
+      <c r="J507" s="6" t="s">
+        <v>3318</v>
+      </c>
+      <c r="K507" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L507" t="s">
+        <v>787</v>
+      </c>
+      <c r="M507" t="s">
+        <v>135</v>
+      </c>
+      <c r="N507" t="s">
+        <v>24</v>
+      </c>
+      <c r="O507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>2885</v>
+      </c>
+      <c r="B508" t="s">
+        <v>2976</v>
+      </c>
+      <c r="C508" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D508" t="s">
+        <v>3054</v>
+      </c>
+      <c r="G508" t="s">
+        <v>3180</v>
+      </c>
+      <c r="I508" s="6" t="s">
+        <v>3246</v>
+      </c>
+      <c r="J508" s="6" t="s">
+        <v>3319</v>
+      </c>
+      <c r="K508" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L508" t="s">
+        <v>3197</v>
+      </c>
+      <c r="M508" t="s">
+        <v>31</v>
+      </c>
+      <c r="N508" t="s">
+        <v>24</v>
+      </c>
+      <c r="O508">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="509" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B509" t="s">
+        <v>2977</v>
+      </c>
+      <c r="C509" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D509" t="s">
+        <v>3055</v>
+      </c>
+      <c r="G509" t="s">
+        <v>3179</v>
+      </c>
+      <c r="I509" s="6" t="s">
+        <v>3247</v>
+      </c>
+      <c r="J509" s="6" t="s">
+        <v>3320</v>
+      </c>
+      <c r="K509" t="s">
+        <v>2229</v>
+      </c>
+      <c r="L509" t="s">
+        <v>787</v>
+      </c>
+      <c r="M509" t="s">
+        <v>30</v>
+      </c>
+      <c r="N509" t="s">
+        <v>24</v>
+      </c>
+      <c r="O509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B510" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C510" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D510" t="s">
+        <v>3056</v>
+      </c>
+      <c r="G510" t="s">
+        <v>3178</v>
+      </c>
+      <c r="I510" s="6" t="s">
+        <v>3248</v>
+      </c>
+      <c r="J510" s="6" t="s">
+        <v>3321</v>
+      </c>
+      <c r="K510" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L510" t="s">
+        <v>787</v>
+      </c>
+      <c r="M510" t="s">
+        <v>30</v>
+      </c>
+      <c r="N510" t="s">
+        <v>24</v>
+      </c>
+      <c r="O510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B511" t="s">
+        <v>2979</v>
+      </c>
+      <c r="C511" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D511" t="s">
+        <v>3057</v>
+      </c>
+      <c r="G511" t="s">
+        <v>3177</v>
+      </c>
+      <c r="I511" s="6" t="s">
+        <v>3249</v>
+      </c>
+      <c r="J511" s="6" t="s">
+        <v>3322</v>
+      </c>
+      <c r="K511" t="s">
+        <v>2229</v>
+      </c>
+      <c r="L511" t="s">
+        <v>787</v>
+      </c>
+      <c r="M511" t="s">
+        <v>30</v>
+      </c>
+      <c r="N511" t="s">
+        <v>24</v>
+      </c>
+      <c r="O511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B512" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C512" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D512" t="s">
+        <v>3058</v>
+      </c>
+      <c r="G512" t="s">
+        <v>3176</v>
+      </c>
+      <c r="I512" s="6" t="s">
+        <v>3250</v>
+      </c>
+      <c r="J512" s="6" t="s">
+        <v>3323</v>
+      </c>
+      <c r="K512" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L512" t="s">
+        <v>787</v>
+      </c>
+      <c r="M512" t="s">
+        <v>30</v>
+      </c>
+      <c r="N512" t="s">
+        <v>24</v>
+      </c>
+      <c r="O512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B513" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C513" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D513" t="s">
+        <v>3188</v>
+      </c>
+      <c r="G513" t="s">
+        <v>3175</v>
+      </c>
+      <c r="I513" s="6" t="s">
+        <v>3251</v>
+      </c>
+      <c r="J513" s="6" t="s">
+        <v>3324</v>
+      </c>
+      <c r="K513" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L513" t="s">
+        <v>787</v>
+      </c>
+      <c r="M513" t="s">
+        <v>31</v>
+      </c>
+      <c r="N513" t="s">
+        <v>24</v>
+      </c>
+      <c r="O513">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>2891</v>
+      </c>
+      <c r="B514" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C514" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D514" t="s">
+        <v>3188</v>
+      </c>
+      <c r="G514" t="s">
+        <v>3175</v>
+      </c>
+      <c r="I514" s="6" t="s">
+        <v>3251</v>
+      </c>
+      <c r="J514" s="6" t="s">
+        <v>3325</v>
+      </c>
+      <c r="K514" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L514" t="s">
+        <v>787</v>
+      </c>
+      <c r="M514" t="s">
+        <v>135</v>
+      </c>
+      <c r="N514" t="s">
+        <v>24</v>
+      </c>
+      <c r="O514">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>2892</v>
+      </c>
+      <c r="B515" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C515" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D515" t="s">
+        <v>3059</v>
+      </c>
+      <c r="G515" t="s">
+        <v>3174</v>
+      </c>
+      <c r="I515" s="6" t="s">
+        <v>3252</v>
+      </c>
+      <c r="J515" s="6" t="s">
+        <v>3326</v>
+      </c>
+      <c r="K515" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L515" t="s">
+        <v>787</v>
+      </c>
+      <c r="M515" t="s">
+        <v>30</v>
+      </c>
+      <c r="N515" t="s">
+        <v>24</v>
+      </c>
+      <c r="O515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>2893</v>
+      </c>
+      <c r="B516" t="s">
+        <v>2983</v>
+      </c>
+      <c r="C516" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D516" t="s">
+        <v>3060</v>
+      </c>
+      <c r="G516" t="s">
+        <v>3173</v>
+      </c>
+      <c r="I516" s="6" t="s">
+        <v>3253</v>
+      </c>
+      <c r="J516" s="6" t="s">
+        <v>3327</v>
+      </c>
+      <c r="K516" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L516" t="s">
+        <v>787</v>
+      </c>
+      <c r="M516" t="s">
+        <v>30</v>
+      </c>
+      <c r="N516" t="s">
+        <v>24</v>
+      </c>
+      <c r="O516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B517" t="s">
+        <v>2975</v>
+      </c>
+      <c r="C517" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D517" t="s">
+        <v>3053</v>
+      </c>
+      <c r="G517" t="s">
+        <v>3167</v>
+      </c>
+      <c r="I517" s="6" t="s">
+        <v>3254</v>
+      </c>
+      <c r="J517" s="6" t="s">
+        <v>3328</v>
+      </c>
+      <c r="K517" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L517" t="s">
+        <v>787</v>
+      </c>
+      <c r="M517" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N517" t="s">
+        <v>24</v>
+      </c>
+      <c r="O517">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B518" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C518" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D518" t="s">
+        <v>3061</v>
+      </c>
+      <c r="G518" t="s">
+        <v>3172</v>
+      </c>
+      <c r="I518" s="6" t="s">
+        <v>3255</v>
+      </c>
+      <c r="J518" s="6" t="s">
+        <v>3329</v>
+      </c>
+      <c r="K518" t="s">
+        <v>2229</v>
+      </c>
+      <c r="L518" t="s">
+        <v>787</v>
+      </c>
+      <c r="M518" t="s">
+        <v>30</v>
+      </c>
+      <c r="N518" t="s">
+        <v>24</v>
+      </c>
+      <c r="O518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B519" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C519" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D519" t="s">
+        <v>3189</v>
+      </c>
+      <c r="G519" t="s">
+        <v>3169</v>
+      </c>
+      <c r="I519" s="6" t="s">
+        <v>3256</v>
+      </c>
+      <c r="J519" s="6" t="s">
+        <v>3330</v>
+      </c>
+      <c r="K519" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L519" t="s">
+        <v>787</v>
+      </c>
+      <c r="M519" t="s">
+        <v>31</v>
+      </c>
+      <c r="N519" t="s">
+        <v>24</v>
+      </c>
+      <c r="O519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>2897</v>
+      </c>
+      <c r="B520" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C520" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D520" t="s">
+        <v>3062</v>
+      </c>
+      <c r="G520" t="s">
+        <v>3171</v>
+      </c>
+      <c r="I520" s="6" t="s">
+        <v>3257</v>
+      </c>
+      <c r="J520" s="6" t="s">
+        <v>3331</v>
+      </c>
+      <c r="K520" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L520" t="s">
+        <v>787</v>
+      </c>
+      <c r="M520" t="s">
+        <v>63</v>
+      </c>
+      <c r="N520" t="s">
+        <v>24</v>
+      </c>
+      <c r="O520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>2897</v>
+      </c>
+      <c r="B521" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C521" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D521" t="s">
+        <v>3062</v>
+      </c>
+      <c r="G521" t="s">
+        <v>3171</v>
+      </c>
+      <c r="I521" s="6" t="s">
+        <v>3257</v>
+      </c>
+      <c r="J521" s="6" t="s">
+        <v>3332</v>
+      </c>
+      <c r="K521" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L521" t="s">
+        <v>787</v>
+      </c>
+      <c r="M521" t="s">
+        <v>63</v>
+      </c>
+      <c r="N521" t="s">
+        <v>24</v>
+      </c>
+      <c r="O521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B522" t="s">
+        <v>2987</v>
+      </c>
+      <c r="C522" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D522" t="s">
+        <v>3063</v>
+      </c>
+      <c r="G522" t="s">
+        <v>3170</v>
+      </c>
+      <c r="I522" s="6" t="s">
+        <v>3258</v>
+      </c>
+      <c r="J522" s="6" t="s">
+        <v>3333</v>
+      </c>
+      <c r="K522" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L522" t="s">
+        <v>787</v>
+      </c>
+      <c r="M522" t="s">
+        <v>30</v>
+      </c>
+      <c r="N522" t="s">
+        <v>24</v>
+      </c>
+      <c r="O522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B523" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C523" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D523" t="s">
+        <v>3190</v>
+      </c>
+      <c r="G523" t="s">
+        <v>3169</v>
+      </c>
+      <c r="I523" s="6" t="s">
+        <v>3259</v>
+      </c>
+      <c r="J523" s="6" t="s">
+        <v>3334</v>
+      </c>
+      <c r="K523" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L523" t="s">
+        <v>787</v>
+      </c>
+      <c r="M523" t="s">
+        <v>31</v>
+      </c>
+      <c r="N523" t="s">
+        <v>24</v>
+      </c>
+      <c r="O523">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B524" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C524" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D524" t="s">
+        <v>3191</v>
+      </c>
+      <c r="G524" t="s">
+        <v>3164</v>
+      </c>
+      <c r="I524" s="6" t="s">
+        <v>3260</v>
+      </c>
+      <c r="J524" s="6" t="s">
+        <v>3335</v>
+      </c>
+      <c r="K524" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L524" t="s">
+        <v>787</v>
+      </c>
+      <c r="M524" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N524" t="s">
+        <v>24</v>
+      </c>
+      <c r="O524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B525" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C525" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D525" t="s">
+        <v>3064</v>
+      </c>
+      <c r="G525" t="s">
+        <v>3168</v>
+      </c>
+      <c r="I525" s="6" t="s">
+        <v>3261</v>
+      </c>
+      <c r="J525" s="6" t="s">
+        <v>3336</v>
+      </c>
+      <c r="K525" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L525" t="s">
+        <v>787</v>
+      </c>
+      <c r="M525" t="s">
+        <v>31</v>
+      </c>
+      <c r="N525" t="s">
+        <v>24</v>
+      </c>
+      <c r="O525">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B526" t="s">
+        <v>2990</v>
+      </c>
+      <c r="C526" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D526" t="s">
+        <v>3053</v>
+      </c>
+      <c r="G526" t="s">
+        <v>3167</v>
+      </c>
+      <c r="I526" s="6" t="s">
+        <v>3254</v>
+      </c>
+      <c r="J526" s="6" t="s">
+        <v>3337</v>
+      </c>
+      <c r="K526" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L526" t="s">
+        <v>3198</v>
+      </c>
+      <c r="M526" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N526" t="s">
+        <v>24</v>
+      </c>
+      <c r="O526">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B527" t="s">
+        <v>2991</v>
+      </c>
+      <c r="C527" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D527" t="s">
+        <v>3065</v>
+      </c>
+      <c r="G527" t="s">
+        <v>3166</v>
+      </c>
+      <c r="I527" s="6" t="s">
+        <v>3262</v>
+      </c>
+      <c r="J527" s="6" t="s">
+        <v>3338</v>
+      </c>
+      <c r="K527" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L527" t="s">
+        <v>787</v>
+      </c>
+      <c r="M527" t="s">
+        <v>30</v>
+      </c>
+      <c r="N527" t="s">
+        <v>24</v>
+      </c>
+      <c r="O527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B528" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C528" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D528" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G528" t="s">
+        <v>3165</v>
+      </c>
+      <c r="I528" s="6" t="s">
+        <v>3263</v>
+      </c>
+      <c r="J528" s="6" t="s">
+        <v>3339</v>
+      </c>
+      <c r="K528" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L528" t="s">
+        <v>787</v>
+      </c>
+      <c r="M528" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N528" t="s">
+        <v>24</v>
+      </c>
+      <c r="O528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B529" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C529" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D529" t="s">
+        <v>3191</v>
+      </c>
+      <c r="G529" t="s">
+        <v>3164</v>
+      </c>
+      <c r="I529" s="6" t="s">
+        <v>3260</v>
+      </c>
+      <c r="J529" s="6" t="s">
+        <v>3340</v>
+      </c>
+      <c r="K529" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L529" t="s">
+        <v>787</v>
+      </c>
+      <c r="M529" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N529" t="s">
+        <v>24</v>
+      </c>
+      <c r="O529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B530" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C530" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D530" t="s">
+        <v>3067</v>
+      </c>
+      <c r="G530" t="s">
+        <v>3163</v>
+      </c>
+      <c r="I530" s="6" t="s">
+        <v>3264</v>
+      </c>
+      <c r="J530" s="6" t="s">
+        <v>3341</v>
+      </c>
+      <c r="K530" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L530" t="s">
+        <v>3199</v>
+      </c>
+      <c r="M530" t="s">
+        <v>135</v>
+      </c>
+      <c r="N530" t="s">
+        <v>24</v>
+      </c>
+      <c r="O530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B531" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C531" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D531" t="s">
+        <v>3068</v>
+      </c>
+      <c r="G531" t="s">
+        <v>3162</v>
+      </c>
+      <c r="I531" s="6" t="s">
+        <v>3265</v>
+      </c>
+      <c r="J531" s="6" t="s">
+        <v>1820</v>
+      </c>
+      <c r="K531" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L531" t="s">
+        <v>3200</v>
+      </c>
+      <c r="M531" t="s">
+        <v>63</v>
+      </c>
+      <c r="N531" t="s">
+        <v>24</v>
+      </c>
+      <c r="O531">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="532" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B532" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C532" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D532" t="s">
+        <v>3069</v>
+      </c>
+      <c r="G532" t="s">
+        <v>3161</v>
+      </c>
+      <c r="I532" s="6" t="s">
+        <v>3266</v>
+      </c>
+      <c r="J532" s="6" t="s">
+        <v>2761</v>
+      </c>
+      <c r="K532" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L532" t="s">
+        <v>787</v>
+      </c>
+      <c r="M532" t="s">
+        <v>135</v>
+      </c>
+      <c r="N532" t="s">
+        <v>24</v>
+      </c>
+      <c r="O532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>2907</v>
+      </c>
+      <c r="B533" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C533" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D533" t="s">
+        <v>3070</v>
+      </c>
+      <c r="G533" t="s">
+        <v>3161</v>
+      </c>
+      <c r="I533" s="6" t="s">
+        <v>3266</v>
+      </c>
+      <c r="J533" s="6" t="s">
+        <v>3342</v>
+      </c>
+      <c r="K533" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L533" t="s">
+        <v>787</v>
+      </c>
+      <c r="M533" t="s">
+        <v>31</v>
+      </c>
+      <c r="N533" t="s">
+        <v>24</v>
+      </c>
+      <c r="O533">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="534" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B534" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C534" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D534" t="s">
+        <v>3071</v>
+      </c>
+      <c r="G534" t="s">
+        <v>3160</v>
+      </c>
+      <c r="I534" s="6" t="s">
+        <v>3267</v>
+      </c>
+      <c r="J534" s="6" t="s">
+        <v>3343</v>
+      </c>
+      <c r="K534" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L534" t="s">
+        <v>3201</v>
+      </c>
+      <c r="M534" t="s">
+        <v>63</v>
+      </c>
+      <c r="N534" t="s">
+        <v>24</v>
+      </c>
+      <c r="O534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>2909</v>
+      </c>
+      <c r="B535" t="s">
+        <v>2998</v>
+      </c>
+      <c r="C535" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D535" t="s">
+        <v>3072</v>
+      </c>
+      <c r="G535" t="s">
+        <v>3159</v>
+      </c>
+      <c r="I535" s="6" t="s">
+        <v>1833</v>
+      </c>
+      <c r="J535" s="6" t="s">
+        <v>2721</v>
+      </c>
+      <c r="K535" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L535" t="s">
+        <v>3202</v>
+      </c>
+      <c r="M535" t="s">
+        <v>135</v>
+      </c>
+      <c r="N535" t="s">
+        <v>24</v>
+      </c>
+      <c r="O535">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="536" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B536" t="s">
+        <v>2999</v>
+      </c>
+      <c r="C536" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D536" t="s">
+        <v>3073</v>
+      </c>
+      <c r="G536" t="s">
+        <v>3158</v>
+      </c>
+      <c r="I536" s="6" t="s">
+        <v>3268</v>
+      </c>
+      <c r="J536" s="6" t="s">
+        <v>2776</v>
+      </c>
+      <c r="K536" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L536" t="s">
+        <v>3203</v>
+      </c>
+      <c r="M536" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N536" t="s">
+        <v>24</v>
+      </c>
+      <c r="O536">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="537" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>2911</v>
+      </c>
+      <c r="B537" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C537" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D537" t="s">
+        <v>3074</v>
+      </c>
+      <c r="G537" t="s">
+        <v>3157</v>
+      </c>
+      <c r="I537" s="6" t="s">
+        <v>3269</v>
+      </c>
+      <c r="J537" s="6" t="s">
+        <v>3344</v>
+      </c>
+      <c r="K537" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L537" t="s">
+        <v>787</v>
+      </c>
+      <c r="M537" t="s">
+        <v>31</v>
+      </c>
+      <c r="N537" t="s">
+        <v>24</v>
+      </c>
+      <c r="O537">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="538" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B538" t="s">
+        <v>3001</v>
+      </c>
+      <c r="C538" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D538" t="s">
+        <v>3075</v>
+      </c>
+      <c r="G538" t="s">
+        <v>3156</v>
+      </c>
+      <c r="I538" s="6" t="s">
+        <v>3270</v>
+      </c>
+      <c r="J538" s="6" t="s">
+        <v>3345</v>
+      </c>
+      <c r="K538" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L538" t="s">
+        <v>3204</v>
+      </c>
+      <c r="M538" t="s">
+        <v>63</v>
+      </c>
+      <c r="N538" t="s">
+        <v>24</v>
+      </c>
+      <c r="O538">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="539" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>2913</v>
+      </c>
+      <c r="B539" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C539" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D539" t="s">
+        <v>3076</v>
+      </c>
+      <c r="G539" t="s">
+        <v>3155</v>
+      </c>
+      <c r="I539" s="6" t="s">
+        <v>3271</v>
+      </c>
+      <c r="J539" s="6" t="s">
+        <v>2670</v>
+      </c>
+      <c r="K539" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L539" t="s">
+        <v>3205</v>
+      </c>
+      <c r="M539" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N539" t="s">
+        <v>24</v>
+      </c>
+      <c r="O539">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="540" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B540" t="s">
+        <v>3003</v>
+      </c>
+      <c r="C540" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D540" t="s">
+        <v>3077</v>
+      </c>
+      <c r="G540" t="s">
+        <v>3154</v>
+      </c>
+      <c r="I540" s="6" t="s">
+        <v>3272</v>
+      </c>
+      <c r="J540" s="6" t="s">
+        <v>3346</v>
+      </c>
+      <c r="K540" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L540" t="s">
+        <v>787</v>
+      </c>
+      <c r="M540" t="s">
+        <v>135</v>
+      </c>
+      <c r="N540" t="s">
+        <v>24</v>
+      </c>
+      <c r="O540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>2915</v>
+      </c>
+      <c r="B541" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C541" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D541" t="s">
+        <v>3078</v>
+      </c>
+      <c r="G541" t="s">
+        <v>3153</v>
+      </c>
+      <c r="I541" s="6" t="s">
+        <v>3273</v>
+      </c>
+      <c r="J541" s="6" t="s">
+        <v>3319</v>
+      </c>
+      <c r="K541" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L541" t="s">
+        <v>3206</v>
+      </c>
+      <c r="M541" t="s">
+        <v>31</v>
+      </c>
+      <c r="N541" t="s">
+        <v>24</v>
+      </c>
+      <c r="O541">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="542" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B542" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C542" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D542" t="s">
+        <v>3079</v>
+      </c>
+      <c r="G542" t="s">
+        <v>3152</v>
+      </c>
+      <c r="I542" s="6" t="s">
+        <v>3274</v>
+      </c>
+      <c r="J542" s="6" t="s">
+        <v>3347</v>
+      </c>
+      <c r="K542" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L542" t="s">
+        <v>3207</v>
+      </c>
+      <c r="M542" t="s">
+        <v>135</v>
+      </c>
+      <c r="N542" t="s">
+        <v>24</v>
+      </c>
+      <c r="O542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B543" t="s">
+        <v>3006</v>
+      </c>
+      <c r="C543" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D543" t="s">
+        <v>3080</v>
+      </c>
+      <c r="G543" t="s">
+        <v>3151</v>
+      </c>
+      <c r="I543" s="6" t="s">
+        <v>3275</v>
+      </c>
+      <c r="J543" s="6" t="s">
+        <v>3348</v>
+      </c>
+      <c r="K543" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L543" t="s">
+        <v>3208</v>
+      </c>
+      <c r="M543" t="s">
+        <v>63</v>
+      </c>
+      <c r="N543" t="s">
+        <v>24</v>
+      </c>
+      <c r="O543">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="544" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B544" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C544" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D544" t="s">
+        <v>3081</v>
+      </c>
+      <c r="G544" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I544" s="6" t="s">
+        <v>3276</v>
+      </c>
+      <c r="J544" s="6" t="s">
+        <v>3349</v>
+      </c>
+      <c r="K544" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L544" t="s">
+        <v>3209</v>
+      </c>
+      <c r="M544" t="s">
+        <v>31</v>
+      </c>
+      <c r="N544" t="s">
+        <v>24</v>
+      </c>
+      <c r="O544">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="545" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B545" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C545" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D545" t="s">
+        <v>3082</v>
+      </c>
+      <c r="G545" t="s">
+        <v>3150</v>
+      </c>
+      <c r="I545" s="6" t="s">
+        <v>3277</v>
+      </c>
+      <c r="J545" s="6" t="s">
+        <v>3350</v>
+      </c>
+      <c r="K545" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L545" t="s">
+        <v>3210</v>
+      </c>
+      <c r="M545" t="s">
+        <v>135</v>
+      </c>
+      <c r="N545" t="s">
+        <v>24</v>
+      </c>
+      <c r="O545">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B546" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C546" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D546" t="s">
+        <v>3083</v>
+      </c>
+      <c r="G546" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I546" s="6" t="s">
+        <v>3278</v>
+      </c>
+      <c r="J546" s="6" t="s">
+        <v>3351</v>
+      </c>
+      <c r="K546" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L546" t="s">
+        <v>787</v>
+      </c>
+      <c r="M546" t="s">
+        <v>31</v>
+      </c>
+      <c r="N546" t="s">
+        <v>24</v>
+      </c>
+      <c r="O546">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="547" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B547" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C547" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D547" t="s">
+        <v>3084</v>
+      </c>
+      <c r="G547" t="s">
+        <v>3149</v>
+      </c>
+      <c r="I547" s="6" t="s">
+        <v>3279</v>
+      </c>
+      <c r="J547" s="6" t="s">
+        <v>3352</v>
+      </c>
+      <c r="K547" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L547" t="s">
+        <v>3211</v>
+      </c>
+      <c r="M547" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N547" t="s">
+        <v>24</v>
+      </c>
+      <c r="O547">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="548" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B548" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C548" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D548" t="s">
+        <v>3083</v>
+      </c>
+      <c r="G548" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I548" s="6" t="s">
+        <v>3280</v>
+      </c>
+      <c r="J548" s="6" t="s">
+        <v>3353</v>
+      </c>
+      <c r="K548" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L548" t="s">
+        <v>3212</v>
+      </c>
+      <c r="M548" t="s">
+        <v>30</v>
+      </c>
+      <c r="N548" t="s">
+        <v>24</v>
+      </c>
+      <c r="O548">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="549" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>2923</v>
+      </c>
+      <c r="B549" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C549" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D549" t="s">
+        <v>3085</v>
+      </c>
+      <c r="G549" t="s">
+        <v>3148</v>
+      </c>
+      <c r="I549" s="6" t="s">
+        <v>3281</v>
+      </c>
+      <c r="J549" s="6" t="s">
+        <v>3335</v>
+      </c>
+      <c r="K549" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L549" t="s">
+        <v>787</v>
+      </c>
+      <c r="M549" t="s">
+        <v>31</v>
+      </c>
+      <c r="N549" t="s">
+        <v>24</v>
+      </c>
+      <c r="O549">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="550" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B550" t="s">
+        <v>3011</v>
+      </c>
+      <c r="C550" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D550" t="s">
+        <v>3086</v>
+      </c>
+      <c r="G550" t="s">
+        <v>3147</v>
+      </c>
+      <c r="I550" s="6" t="s">
+        <v>2689</v>
+      </c>
+      <c r="J550" s="6" t="s">
+        <v>3354</v>
+      </c>
+      <c r="K550" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L550" t="s">
+        <v>787</v>
+      </c>
+      <c r="M550" t="s">
+        <v>135</v>
+      </c>
+      <c r="N550" t="s">
+        <v>24</v>
+      </c>
+      <c r="O550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>2925</v>
+      </c>
+      <c r="B551" t="s">
+        <v>3012</v>
+      </c>
+      <c r="C551" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D551" t="s">
+        <v>3087</v>
+      </c>
+      <c r="G551" t="s">
+        <v>3148</v>
+      </c>
+      <c r="I551" s="6" t="s">
+        <v>3282</v>
+      </c>
+      <c r="J551" s="6" t="s">
+        <v>3335</v>
+      </c>
+      <c r="K551" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L551" t="s">
+        <v>787</v>
+      </c>
+      <c r="M551" t="s">
+        <v>31</v>
+      </c>
+      <c r="N551" t="s">
+        <v>24</v>
+      </c>
+      <c r="O551">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="552" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B552" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C552" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D552" t="s">
+        <v>3083</v>
+      </c>
+      <c r="G552" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I552" s="6" t="s">
+        <v>3280</v>
+      </c>
+      <c r="J552" s="6" t="s">
+        <v>3355</v>
+      </c>
+      <c r="K552" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L552" t="s">
+        <v>787</v>
+      </c>
+      <c r="M552" t="s">
+        <v>30</v>
+      </c>
+      <c r="N552" t="s">
+        <v>24</v>
+      </c>
+      <c r="O552">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="553" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B553" t="s">
+        <v>3011</v>
+      </c>
+      <c r="C553" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D553" t="s">
+        <v>3086</v>
+      </c>
+      <c r="G553" t="s">
+        <v>3147</v>
+      </c>
+      <c r="I553" s="6" t="s">
+        <v>2689</v>
+      </c>
+      <c r="J553" s="6" t="s">
+        <v>2771</v>
+      </c>
+      <c r="K553" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L553" t="s">
+        <v>3213</v>
+      </c>
+      <c r="M553" t="s">
+        <v>135</v>
+      </c>
+      <c r="N553" t="s">
+        <v>24</v>
+      </c>
+      <c r="O553">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>2927</v>
+      </c>
+      <c r="B554" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C554" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D554" t="s">
+        <v>3088</v>
+      </c>
+      <c r="G554" t="s">
+        <v>3146</v>
+      </c>
+      <c r="I554" s="6" t="s">
+        <v>3283</v>
+      </c>
+      <c r="J554" s="6" t="s">
+        <v>3356</v>
+      </c>
+      <c r="K554" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L554" t="s">
+        <v>3214</v>
+      </c>
+      <c r="M554" t="s">
+        <v>135</v>
+      </c>
+      <c r="N554" t="s">
+        <v>24</v>
+      </c>
+      <c r="O554">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="555" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B555" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C555" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D555" t="s">
+        <v>3089</v>
+      </c>
+      <c r="G555" t="s">
+        <v>3145</v>
+      </c>
+      <c r="I555" s="6" t="s">
+        <v>3284</v>
+      </c>
+      <c r="J555" s="6" t="s">
+        <v>3357</v>
+      </c>
+      <c r="K555" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L555" t="s">
+        <v>787</v>
+      </c>
+      <c r="M555" t="s">
+        <v>31</v>
+      </c>
+      <c r="N555" t="s">
+        <v>24</v>
+      </c>
+      <c r="O555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>2929</v>
+      </c>
+      <c r="B556" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C556" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D556" t="s">
+        <v>3090</v>
+      </c>
+      <c r="G556" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I556" s="6" t="s">
+        <v>3276</v>
+      </c>
+      <c r="J556" s="6" t="s">
+        <v>3358</v>
+      </c>
+      <c r="K556" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L556" t="s">
+        <v>3215</v>
+      </c>
+      <c r="M556" t="s">
+        <v>3196</v>
+      </c>
+      <c r="N556" t="s">
+        <v>24</v>
+      </c>
+      <c r="O556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B557" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C557" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D557" t="s">
+        <v>3091</v>
+      </c>
+      <c r="G557" t="s">
+        <v>3144</v>
+      </c>
+      <c r="I557" s="6" t="s">
+        <v>3285</v>
+      </c>
+      <c r="J557" s="6" t="s">
+        <v>3359</v>
+      </c>
+      <c r="K557" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L557" t="s">
+        <v>787</v>
+      </c>
+      <c r="M557" t="s">
+        <v>63</v>
+      </c>
+      <c r="N557" t="s">
+        <v>24</v>
+      </c>
+      <c r="O557">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="558" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B558" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C558" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D558" t="s">
+        <v>3092</v>
+      </c>
+      <c r="G558" t="s">
+        <v>3143</v>
+      </c>
+      <c r="I558" s="6" t="s">
+        <v>3286</v>
+      </c>
+      <c r="J558" s="6" t="s">
+        <v>3360</v>
+      </c>
+      <c r="K558" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L558" t="s">
+        <v>787</v>
+      </c>
+      <c r="M558" t="s">
+        <v>31</v>
+      </c>
+      <c r="N558" t="s">
+        <v>24</v>
+      </c>
+      <c r="O558">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="559" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B559" t="s">
+        <v>3018</v>
+      </c>
+      <c r="C559" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D559" t="s">
+        <v>3093</v>
+      </c>
+      <c r="G559" t="s">
+        <v>3142</v>
+      </c>
+      <c r="I559" s="6" t="s">
+        <v>3285</v>
+      </c>
+      <c r="J559" s="6" t="s">
+        <v>3361</v>
+      </c>
+      <c r="K559" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L559" t="s">
+        <v>3216</v>
+      </c>
+      <c r="M559" t="s">
+        <v>63</v>
+      </c>
+      <c r="N559" t="s">
+        <v>24</v>
+      </c>
+      <c r="O559">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="560" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B560" t="s">
+        <v>3019</v>
+      </c>
+      <c r="C560" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D560" t="s">
+        <v>3094</v>
+      </c>
+      <c r="G560" t="s">
+        <v>3141</v>
+      </c>
+      <c r="I560" s="6" t="s">
+        <v>3287</v>
+      </c>
+      <c r="J560" s="6" t="s">
+        <v>3362</v>
+      </c>
+      <c r="K560" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L560" t="s">
+        <v>3217</v>
+      </c>
+      <c r="M560" t="s">
+        <v>63</v>
+      </c>
+      <c r="N560" t="s">
+        <v>24</v>
+      </c>
+      <c r="O560">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="561" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B561" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C561" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D561" t="s">
+        <v>3095</v>
+      </c>
+      <c r="G561" t="s">
+        <v>3140</v>
+      </c>
+      <c r="I561" s="6" t="s">
+        <v>1795</v>
+      </c>
+      <c r="J561" s="6" t="s">
+        <v>3363</v>
+      </c>
+      <c r="K561" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L561" t="s">
+        <v>3218</v>
+      </c>
+      <c r="M561" t="s">
+        <v>135</v>
+      </c>
+      <c r="N561" t="s">
+        <v>24</v>
+      </c>
+      <c r="O561">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="562" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B562" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C562" t="s">
+        <v>3047</v>
+      </c>
+      <c r="G562" t="s">
+        <v>3139</v>
+      </c>
+      <c r="I562" s="6" t="s">
+        <v>3288</v>
+      </c>
+      <c r="J562" s="6" t="s">
+        <v>2526</v>
+      </c>
+      <c r="K562" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L562" t="s">
+        <v>3219</v>
+      </c>
+      <c r="M562" t="s">
+        <v>63</v>
+      </c>
+      <c r="N562" t="s">
+        <v>24</v>
+      </c>
+      <c r="O562">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B563" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C563" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D563" t="s">
+        <v>3095</v>
+      </c>
+      <c r="G563" t="s">
+        <v>3138</v>
+      </c>
+      <c r="I563" s="6" t="s">
+        <v>1795</v>
+      </c>
+      <c r="J563" s="6" t="s">
+        <v>2559</v>
+      </c>
+      <c r="K563" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L563" t="s">
+        <v>787</v>
+      </c>
+      <c r="M563" t="s">
+        <v>135</v>
+      </c>
+      <c r="N563" t="s">
+        <v>24</v>
+      </c>
+      <c r="O563">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="564" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B564" t="s">
+        <v>3022</v>
+      </c>
+      <c r="C564" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D564" t="s">
+        <v>3096</v>
+      </c>
+      <c r="G564" t="s">
+        <v>3137</v>
+      </c>
+      <c r="I564" s="6" t="s">
+        <v>3289</v>
+      </c>
+      <c r="J564" s="6" t="s">
+        <v>3364</v>
+      </c>
+      <c r="K564" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L564" t="s">
+        <v>787</v>
+      </c>
+      <c r="M564" t="s">
+        <v>30</v>
+      </c>
+      <c r="N564" t="s">
+        <v>24</v>
+      </c>
+      <c r="O564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B565" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C565" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D565" t="s">
+        <v>3090</v>
+      </c>
+      <c r="G565" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I565" s="6" t="s">
+        <v>3290</v>
+      </c>
+      <c r="J565" s="6" t="s">
+        <v>3365</v>
+      </c>
+      <c r="K565" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L565" t="s">
+        <v>3220</v>
+      </c>
+      <c r="M565" t="s">
+        <v>30</v>
+      </c>
+      <c r="N565" t="s">
+        <v>24</v>
+      </c>
+      <c r="O565">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="566" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B566" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C566" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D566" t="s">
+        <v>3097</v>
+      </c>
+      <c r="G566" t="s">
+        <v>3135</v>
+      </c>
+      <c r="I566" s="6" t="s">
+        <v>3291</v>
+      </c>
+      <c r="J566" s="6" t="s">
+        <v>3366</v>
+      </c>
+      <c r="K566" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L566" t="s">
+        <v>787</v>
+      </c>
+      <c r="M566" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N566" t="s">
+        <v>24</v>
+      </c>
+      <c r="O566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B567" t="s">
+        <v>3024</v>
+      </c>
+      <c r="C567" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D567" t="s">
+        <v>3192</v>
+      </c>
+      <c r="G567" t="s">
+        <v>3134</v>
+      </c>
+      <c r="I567" s="6" t="s">
+        <v>3292</v>
+      </c>
+      <c r="J567" s="6" t="s">
+        <v>3367</v>
+      </c>
+      <c r="K567" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L567" t="s">
+        <v>787</v>
+      </c>
+      <c r="M567" t="s">
+        <v>31</v>
+      </c>
+      <c r="N567" t="s">
+        <v>24</v>
+      </c>
+      <c r="O567">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="568" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B568" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C568" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D568" t="s">
+        <v>3193</v>
+      </c>
+      <c r="G568" t="s">
+        <v>3133</v>
+      </c>
+      <c r="I568" s="6" t="s">
+        <v>3293</v>
+      </c>
+      <c r="J568" s="6" t="s">
+        <v>2785</v>
+      </c>
+      <c r="K568" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L568" t="s">
+        <v>787</v>
+      </c>
+      <c r="M568" t="s">
+        <v>135</v>
+      </c>
+      <c r="N568" t="s">
+        <v>24</v>
+      </c>
+      <c r="O568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B569" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C569" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D569" t="s">
+        <v>3098</v>
+      </c>
+      <c r="G569" t="s">
+        <v>3132</v>
+      </c>
+      <c r="I569" s="6" t="s">
+        <v>3294</v>
+      </c>
+      <c r="J569" s="6" t="s">
+        <v>3368</v>
+      </c>
+      <c r="K569" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L569" t="s">
+        <v>787</v>
+      </c>
+      <c r="M569" t="s">
+        <v>135</v>
+      </c>
+      <c r="N569" t="s">
+        <v>24</v>
+      </c>
+      <c r="O569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B570" t="s">
+        <v>3027</v>
+      </c>
+      <c r="C570" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D570" t="s">
+        <v>3098</v>
+      </c>
+      <c r="G570" t="s">
+        <v>3132</v>
+      </c>
+      <c r="I570" s="6" t="s">
+        <v>3294</v>
+      </c>
+      <c r="J570" s="6" t="s">
+        <v>3369</v>
+      </c>
+      <c r="K570" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L570" t="s">
+        <v>787</v>
+      </c>
+      <c r="M570" t="s">
+        <v>31</v>
+      </c>
+      <c r="N570" t="s">
+        <v>24</v>
+      </c>
+      <c r="O570">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="571" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B571" t="s">
+        <v>3028</v>
+      </c>
+      <c r="C571" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D571" t="s">
+        <v>3099</v>
+      </c>
+      <c r="G571" t="s">
+        <v>3131</v>
+      </c>
+      <c r="I571" s="6" t="s">
+        <v>3295</v>
+      </c>
+      <c r="J571" s="6" t="s">
+        <v>3370</v>
+      </c>
+      <c r="K571" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L571" t="s">
+        <v>3221</v>
+      </c>
+      <c r="M571" t="s">
+        <v>63</v>
+      </c>
+      <c r="N571" t="s">
+        <v>24</v>
+      </c>
+      <c r="O571">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="572" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B572" t="s">
+        <v>3029</v>
+      </c>
+      <c r="C572" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D572" t="s">
+        <v>3100</v>
+      </c>
+      <c r="G572" t="s">
+        <v>3129</v>
+      </c>
+      <c r="I572" s="6" t="s">
+        <v>3296</v>
+      </c>
+      <c r="J572" s="6" t="s">
+        <v>3371</v>
+      </c>
+      <c r="K572" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L572" t="s">
+        <v>787</v>
+      </c>
+      <c r="M572" t="s">
+        <v>63</v>
+      </c>
+      <c r="N572" t="s">
+        <v>24</v>
+      </c>
+      <c r="O572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>2945</v>
+      </c>
+      <c r="B573" t="s">
+        <v>3030</v>
+      </c>
+      <c r="C573" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D573" t="s">
+        <v>3194</v>
+      </c>
+      <c r="G573" t="s">
+        <v>3130</v>
+      </c>
+      <c r="I573" s="6" t="s">
+        <v>3297</v>
+      </c>
+      <c r="J573" s="6" t="s">
+        <v>3372</v>
+      </c>
+      <c r="K573" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L573" t="s">
+        <v>787</v>
+      </c>
+      <c r="M573" t="s">
+        <v>31</v>
+      </c>
+      <c r="N573" t="s">
+        <v>24</v>
+      </c>
+      <c r="O573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B574" t="s">
+        <v>3029</v>
+      </c>
+      <c r="C574" t="s">
+        <v>3047</v>
+      </c>
+      <c r="G574" t="s">
+        <v>3129</v>
+      </c>
+      <c r="I574" s="6" t="s">
+        <v>3296</v>
+      </c>
+      <c r="J574" s="6" t="s">
+        <v>2652</v>
+      </c>
+      <c r="K574" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L574" t="s">
+        <v>787</v>
+      </c>
+      <c r="M574" t="s">
+        <v>63</v>
+      </c>
+      <c r="N574" t="s">
+        <v>24</v>
+      </c>
+      <c r="O574">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="575" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B575" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C575" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D575" t="s">
+        <v>3101</v>
+      </c>
+      <c r="G575" t="s">
+        <v>3128</v>
+      </c>
+      <c r="I575" s="6" t="s">
+        <v>3298</v>
+      </c>
+      <c r="J575" s="6" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K575" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L575" t="s">
+        <v>3222</v>
+      </c>
+      <c r="M575" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N575" t="s">
+        <v>24</v>
+      </c>
+      <c r="O575">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="576" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B576" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C576" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D576" t="s">
+        <v>3102</v>
+      </c>
+      <c r="G576" t="s">
+        <v>3127</v>
+      </c>
+      <c r="I576" s="6" t="s">
+        <v>3299</v>
+      </c>
+      <c r="J576" s="6" t="s">
+        <v>3355</v>
+      </c>
+      <c r="K576" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L576" t="s">
+        <v>787</v>
+      </c>
+      <c r="M576" t="s">
+        <v>30</v>
+      </c>
+      <c r="N576" t="s">
+        <v>24</v>
+      </c>
+      <c r="O576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B577" t="s">
+        <v>3028</v>
+      </c>
+      <c r="C577" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D577" t="s">
+        <v>3099</v>
+      </c>
+      <c r="G577" t="s">
+        <v>3126</v>
+      </c>
+      <c r="I577" s="6" t="s">
+        <v>3295</v>
+      </c>
+      <c r="J577" s="6" t="s">
+        <v>3374</v>
+      </c>
+      <c r="K577" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L577" t="s">
+        <v>787</v>
+      </c>
+      <c r="M577" t="s">
+        <v>135</v>
+      </c>
+      <c r="N577" t="s">
+        <v>24</v>
+      </c>
+      <c r="O577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B578" t="s">
+        <v>3033</v>
+      </c>
+      <c r="C578" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D578" t="s">
+        <v>3103</v>
+      </c>
+      <c r="G578" t="s">
+        <v>3114</v>
+      </c>
+      <c r="I578" s="6" t="s">
+        <v>3300</v>
+      </c>
+      <c r="J578" s="6" t="s">
+        <v>3375</v>
+      </c>
+      <c r="K578" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L578" t="s">
+        <v>3223</v>
+      </c>
+      <c r="M578" t="s">
+        <v>63</v>
+      </c>
+      <c r="N578" t="s">
+        <v>24</v>
+      </c>
+      <c r="O578">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="579" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B579" t="s">
+        <v>3034</v>
+      </c>
+      <c r="C579" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D579" t="s">
+        <v>3104</v>
+      </c>
+      <c r="G579" t="s">
+        <v>3125</v>
+      </c>
+      <c r="I579" s="6" t="s">
+        <v>3301</v>
+      </c>
+      <c r="J579" s="6" t="s">
+        <v>3376</v>
+      </c>
+      <c r="K579" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L579" t="s">
+        <v>787</v>
+      </c>
+      <c r="M579" t="s">
+        <v>135</v>
+      </c>
+      <c r="N579" t="s">
+        <v>24</v>
+      </c>
+      <c r="O579">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="580" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B580" t="s">
+        <v>3034</v>
+      </c>
+      <c r="C580" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D580" t="s">
+        <v>3104</v>
+      </c>
+      <c r="G580" t="s">
+        <v>3125</v>
+      </c>
+      <c r="I580" s="6" t="s">
+        <v>3301</v>
+      </c>
+      <c r="J580" s="6" t="s">
+        <v>2587</v>
+      </c>
+      <c r="K580" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L580" t="s">
+        <v>787</v>
+      </c>
+      <c r="M580" t="s">
+        <v>31</v>
+      </c>
+      <c r="N580" t="s">
+        <v>24</v>
+      </c>
+      <c r="O580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B581" t="s">
+        <v>3033</v>
+      </c>
+      <c r="C581" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D581" t="s">
+        <v>3105</v>
+      </c>
+      <c r="G581" t="s">
+        <v>3124</v>
+      </c>
+      <c r="I581" s="6" t="s">
+        <v>3302</v>
+      </c>
+      <c r="J581" s="6" t="s">
+        <v>3377</v>
+      </c>
+      <c r="K581" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L581" t="s">
+        <v>3224</v>
+      </c>
+      <c r="M581" t="s">
+        <v>63</v>
+      </c>
+      <c r="N581" t="s">
+        <v>24</v>
+      </c>
+      <c r="O581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B582" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C582" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D582" t="s">
+        <v>3105</v>
+      </c>
+      <c r="G582" t="s">
+        <v>3123</v>
+      </c>
+      <c r="I582" s="6" t="s">
+        <v>3302</v>
+      </c>
+      <c r="J582" s="6" t="s">
+        <v>3378</v>
+      </c>
+      <c r="K582" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L582" t="s">
+        <v>3225</v>
+      </c>
+      <c r="M582" t="s">
+        <v>63</v>
+      </c>
+      <c r="N582" t="s">
+        <v>24</v>
+      </c>
+      <c r="O582">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="583" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B583" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C583" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D583" t="s">
+        <v>3106</v>
+      </c>
+      <c r="G583" t="s">
+        <v>3121</v>
+      </c>
+      <c r="I583" s="6" t="s">
+        <v>3303</v>
+      </c>
+      <c r="J583" s="6" t="s">
+        <v>3379</v>
+      </c>
+      <c r="K583" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L583" t="s">
+        <v>787</v>
+      </c>
+      <c r="M583" t="s">
+        <v>30</v>
+      </c>
+      <c r="N583" t="s">
+        <v>24</v>
+      </c>
+      <c r="O583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B584" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C584" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D584" t="s">
+        <v>3106</v>
+      </c>
+      <c r="G584" t="s">
+        <v>3121</v>
+      </c>
+      <c r="I584" s="6" t="s">
+        <v>3303</v>
+      </c>
+      <c r="J584" s="6" t="s">
+        <v>3380</v>
+      </c>
+      <c r="K584" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L584" t="s">
+        <v>3226</v>
+      </c>
+      <c r="M584" t="s">
+        <v>30</v>
+      </c>
+      <c r="N584" t="s">
+        <v>24</v>
+      </c>
+      <c r="O584">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="585" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>2954</v>
+      </c>
+      <c r="B585" t="s">
+        <v>3033</v>
+      </c>
+      <c r="C585" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D585" t="s">
+        <v>3105</v>
+      </c>
+      <c r="G585" t="s">
+        <v>3123</v>
+      </c>
+      <c r="I585" s="6" t="s">
+        <v>3302</v>
+      </c>
+      <c r="J585" s="6" t="s">
+        <v>3381</v>
+      </c>
+      <c r="K585" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L585" t="s">
+        <v>3227</v>
+      </c>
+      <c r="M585" t="s">
+        <v>135</v>
+      </c>
+      <c r="N585" t="s">
+        <v>24</v>
+      </c>
+      <c r="O585">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>2955</v>
+      </c>
+      <c r="B586" t="s">
+        <v>3037</v>
+      </c>
+      <c r="C586" t="s">
+        <v>3047</v>
+      </c>
+      <c r="G586" t="s">
+        <v>3122</v>
+      </c>
+      <c r="I586" s="6" t="s">
+        <v>3304</v>
+      </c>
+      <c r="J586" s="6" t="s">
+        <v>3382</v>
+      </c>
+      <c r="K586" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L586" t="s">
+        <v>3228</v>
+      </c>
+      <c r="M586" t="s">
+        <v>63</v>
+      </c>
+      <c r="N586" t="s">
+        <v>24</v>
+      </c>
+      <c r="O586">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="587" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>2956</v>
+      </c>
+      <c r="B587" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C587" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D587" t="s">
+        <v>3106</v>
+      </c>
+      <c r="G587" t="s">
+        <v>3121</v>
+      </c>
+      <c r="I587" s="6" t="s">
+        <v>3305</v>
+      </c>
+      <c r="J587" s="6" t="s">
+        <v>3383</v>
+      </c>
+      <c r="K587" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L587" t="s">
+        <v>787</v>
+      </c>
+      <c r="M587" t="s">
+        <v>31</v>
+      </c>
+      <c r="N587" t="s">
+        <v>24</v>
+      </c>
+      <c r="O587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B588" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C588" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D588" t="s">
+        <v>3107</v>
+      </c>
+      <c r="G588" t="s">
+        <v>3120</v>
+      </c>
+      <c r="I588" s="6" t="s">
+        <v>3306</v>
+      </c>
+      <c r="J588" s="6" t="s">
+        <v>3384</v>
+      </c>
+      <c r="K588" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L588" t="s">
+        <v>3229</v>
+      </c>
+      <c r="M588" t="s">
+        <v>30</v>
+      </c>
+      <c r="N588" t="s">
+        <v>24</v>
+      </c>
+      <c r="O588">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="589" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B589" t="s">
+        <v>3039</v>
+      </c>
+      <c r="C589" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D589" t="s">
+        <v>3106</v>
+      </c>
+      <c r="G589" t="s">
+        <v>3121</v>
+      </c>
+      <c r="I589" s="6" t="s">
+        <v>3307</v>
+      </c>
+      <c r="J589" s="6" t="s">
+        <v>3385</v>
+      </c>
+      <c r="K589" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L589" t="s">
+        <v>3230</v>
+      </c>
+      <c r="M589" t="s">
+        <v>3196</v>
+      </c>
+      <c r="N589" t="s">
+        <v>24</v>
+      </c>
+      <c r="O589">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="590" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>2959</v>
+      </c>
+      <c r="B590" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C590" t="s">
+        <v>3047</v>
+      </c>
+      <c r="G590" t="s">
+        <v>3122</v>
+      </c>
+      <c r="I590" s="6" t="s">
+        <v>3304</v>
+      </c>
+      <c r="J590" s="6" t="s">
+        <v>3386</v>
+      </c>
+      <c r="K590" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L590" t="s">
+        <v>3231</v>
+      </c>
+      <c r="M590" t="s">
+        <v>63</v>
+      </c>
+      <c r="N590" t="s">
+        <v>24</v>
+      </c>
+      <c r="O590">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B591" t="s">
+        <v>3041</v>
+      </c>
+      <c r="C591" t="s">
+        <v>3047</v>
+      </c>
+      <c r="G591" t="s">
+        <v>3121</v>
+      </c>
+      <c r="I591" s="6" t="s">
+        <v>3307</v>
+      </c>
+      <c r="J591" s="6" t="s">
+        <v>3387</v>
+      </c>
+      <c r="K591" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L591" t="s">
+        <v>3230</v>
+      </c>
+      <c r="M591" t="s">
+        <v>30</v>
+      </c>
+      <c r="N591" t="s">
+        <v>24</v>
+      </c>
+      <c r="O591">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="592" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B592" t="s">
+        <v>3042</v>
+      </c>
+      <c r="C592" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D592" t="s">
+        <v>3107</v>
+      </c>
+      <c r="G592" t="s">
+        <v>3120</v>
+      </c>
+      <c r="I592" s="6" t="s">
+        <v>3308</v>
+      </c>
+      <c r="J592" s="6" t="s">
+        <v>3388</v>
+      </c>
+      <c r="K592" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L592" t="s">
+        <v>3232</v>
+      </c>
+      <c r="M592" t="s">
+        <v>135</v>
+      </c>
+      <c r="N592" t="s">
+        <v>24</v>
+      </c>
+      <c r="O592">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="593" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B593" t="s">
+        <v>3043</v>
+      </c>
+      <c r="C593" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D593" t="s">
+        <v>3108</v>
+      </c>
+      <c r="G593" t="s">
+        <v>3119</v>
+      </c>
+      <c r="I593" s="6" t="s">
+        <v>3309</v>
+      </c>
+      <c r="J593" s="6" t="s">
+        <v>3389</v>
+      </c>
+      <c r="K593" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L593" t="s">
+        <v>787</v>
+      </c>
+      <c r="M593" t="s">
+        <v>135</v>
+      </c>
+      <c r="N593" t="s">
+        <v>24</v>
+      </c>
+      <c r="O593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B594" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C594" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D594" t="s">
+        <v>3109</v>
+      </c>
+      <c r="G594" t="s">
+        <v>3117</v>
+      </c>
+      <c r="I594" s="6" t="s">
+        <v>3310</v>
+      </c>
+      <c r="J594" s="6" t="s">
+        <v>3390</v>
+      </c>
+      <c r="K594" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L594" t="s">
+        <v>3233</v>
+      </c>
+      <c r="M594" t="s">
+        <v>135</v>
+      </c>
+      <c r="N594" t="s">
+        <v>24</v>
+      </c>
+      <c r="O594">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B595" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C595" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D595" t="s">
+        <v>3109</v>
+      </c>
+      <c r="G595" t="s">
+        <v>3117</v>
+      </c>
+      <c r="I595" s="6" t="s">
+        <v>3304</v>
+      </c>
+      <c r="J595" s="6" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K595" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L595" t="s">
+        <v>3234</v>
+      </c>
+      <c r="M595" t="s">
+        <v>63</v>
+      </c>
+      <c r="N595" t="s">
+        <v>24</v>
+      </c>
+      <c r="O595">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="596" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B596" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C596" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D596" t="s">
+        <v>3110</v>
+      </c>
+      <c r="G596" t="s">
+        <v>3118</v>
+      </c>
+      <c r="I596" s="6" t="s">
+        <v>1773</v>
+      </c>
+      <c r="J596" s="6" t="s">
+        <v>3391</v>
+      </c>
+      <c r="K596" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L596" t="s">
+        <v>3235</v>
+      </c>
+      <c r="M596" t="s">
+        <v>31</v>
+      </c>
+      <c r="N596" t="s">
+        <v>24</v>
+      </c>
+      <c r="O596">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="597" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B597" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C597" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D597" t="s">
+        <v>3109</v>
+      </c>
+      <c r="G597" t="s">
+        <v>3117</v>
+      </c>
+      <c r="I597" s="6" t="s">
+        <v>3311</v>
+      </c>
+      <c r="J597" s="6" t="s">
+        <v>2632</v>
+      </c>
+      <c r="K597" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L597" t="s">
+        <v>3236</v>
+      </c>
+      <c r="M597" t="s">
+        <v>63</v>
+      </c>
+      <c r="N597" t="s">
+        <v>24</v>
+      </c>
+      <c r="O597">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="598" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B598" t="s">
+        <v>3037</v>
+      </c>
+      <c r="C598" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D598" t="s">
+        <v>3109</v>
+      </c>
+      <c r="G598" t="s">
+        <v>3116</v>
+      </c>
+      <c r="I598" s="6" t="s">
+        <v>3304</v>
+      </c>
+      <c r="J598" s="6" t="s">
+        <v>3392</v>
+      </c>
+      <c r="K598" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L598" t="s">
+        <v>3237</v>
+      </c>
+      <c r="M598" t="s">
+        <v>135</v>
+      </c>
+      <c r="N598" t="s">
+        <v>24</v>
+      </c>
+      <c r="O598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>2968</v>
+      </c>
+      <c r="B599" t="s">
+        <v>3195</v>
+      </c>
+      <c r="C599" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D599" t="s">
+        <v>3111</v>
+      </c>
+      <c r="G599" t="s">
+        <v>3115</v>
+      </c>
+      <c r="I599" s="6" t="s">
+        <v>3312</v>
+      </c>
+      <c r="J599" s="6" t="s">
+        <v>3393</v>
+      </c>
+      <c r="K599" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L599" t="s">
+        <v>787</v>
+      </c>
+      <c r="M599" t="s">
+        <v>63</v>
+      </c>
+      <c r="N599" t="s">
+        <v>24</v>
+      </c>
+      <c r="O599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B600" t="s">
+        <v>3033</v>
+      </c>
+      <c r="C600" t="s">
+        <v>3047</v>
+      </c>
+      <c r="G600" t="s">
+        <v>3114</v>
+      </c>
+      <c r="I600" s="6" t="s">
+        <v>3300</v>
+      </c>
+      <c r="J600" s="6" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K600" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L600" t="s">
+        <v>3238</v>
+      </c>
+      <c r="M600" t="s">
+        <v>63</v>
+      </c>
+      <c r="N600" t="s">
+        <v>24</v>
+      </c>
+      <c r="O600">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="601" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B601" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C601" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D601" t="s">
+        <v>3112</v>
+      </c>
+      <c r="G601" t="s">
+        <v>3113</v>
+      </c>
+      <c r="I601" s="6" t="s">
+        <v>1773</v>
+      </c>
+      <c r="J601" s="6" t="s">
+        <v>3394</v>
+      </c>
+      <c r="K601" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L601" t="s">
+        <v>3239</v>
+      </c>
+      <c r="M601" t="s">
+        <v>3196</v>
+      </c>
+      <c r="N601" t="s">
+        <v>24</v>
+      </c>
+      <c r="O601">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/patent.xlsx
+++ b/patent.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UPES\Research Paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A47F3A-C1B8-48F6-BCE5-D79A06F3B864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B04CADC-CF26-4764-B27F-9515708C3E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F00DE57-17D5-44C0-9358-E5EFB0815E0D}"/>
   </bookViews>
   <sheets>
     <sheet name="patent" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -35263,13 +35262,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId67"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C0558A-18AA-CA40-9AC7-0DABDE9C90B0}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>